--- a/three_boiling.xlsx
+++ b/three_boiling.xlsx
@@ -588,10 +588,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I217"/>
+  <dimension ref="A1:I218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -4563,6 +4563,14 @@
           <t>°F</t>
         </is>
       </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="17" t="inlineStr">
+        <is>
+          <t>Note: if using CoolingTowerSystem, ignore these injection water demands - they are re-solved there at the delivered water temp.</t>
+        </is>
+      </c>
+      <c r="B218" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/three_boiling.xlsx
+++ b/three_boiling.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -175,10 +175,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,8 +193,8 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -278,7 +281,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9031128" cy="5885021"/>
+    <ext cx="9144000" cy="5958572"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -586,20 +589,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I218"/>
+  <dimension ref="A1:I301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="130" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22.71428571428572" customWidth="1" min="1" max="1"/>
+    <col width="19.57142857142857" customWidth="1" min="2" max="2"/>
+    <col width="12.57142857142857" customWidth="1" min="3" max="3"/>
+    <col width="10.42857142857143" customWidth="1" min="4" max="4"/>
+    <col width="14.85714285714286" customWidth="1" min="5" max="5"/>
+    <col width="13.28571428571429" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11.71428571428571" customWidth="1" min="8" max="8"/>
+    <col width="13.28571428571429" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1627,15 +1630,15 @@
       <c r="I99" s="15" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="17" t="inlineStr">
+      <c r="D100" s="17" t="inlineStr">
         <is>
           <t>Pol % recovered in raw sugar (A sugar / feed)</t>
         </is>
       </c>
-      <c r="B100" s="18" t="n">
+      <c r="E100" s="18" t="n">
         <v>87.25646879646239</v>
       </c>
-      <c r="C100" s="19" t="inlineStr">
+      <c r="F100" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1644,7 +1647,7 @@
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>A PANS  [A Pans]</t>
+          <t>PAN FLOOR SYRUP  (Evaporator Syrup + Remelt)</t>
         </is>
       </c>
       <c r="B102" s="5" t="n"/>
@@ -1706,7 +1709,7 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Syrup</t>
+          <t>Evaporator Syrup</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
@@ -1715,31 +1718,31 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>177571.7011159295</v>
+        <v>162744</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>107365.7777253542</v>
+        <v>97646.39999999999</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>86843.82805180075</v>
+        <v>78117.12</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>70205.92339057531</v>
+        <v>65097.60000000001</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>60.4633379365214</v>
+        <v>60</v>
       </c>
       <c r="H104" s="10" t="n">
-        <v>80.8859488485713</v>
+        <v>80</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>2208.166957217254</v>
+        <v>2028.075484790573</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>B Magma</t>
+          <t>B Remelt</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
@@ -1748,31 +1751,31 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>32379.84352263255</v>
+        <v>11457.48309286809</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>29789.45604082195</v>
+        <v>7447.364010364257</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>27406.29955755619</v>
+        <v>6851.574889535116</v>
       </c>
       <c r="F105" s="13" t="n">
-        <v>2590.387481810601</v>
+        <v>4010.11908250383</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="H105" s="14" t="n">
         <v>92</v>
       </c>
       <c r="I105" s="13" t="n">
-        <v>347.3923052751845</v>
+        <v>139.5365526663698</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>A Molasses Top-off</t>
+          <t>C Remelt</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -1781,31 +1784,31 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>0</v>
+        <v>5163.871569999851</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0</v>
+        <v>3356.516520499903</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0</v>
+        <v>2752.34354680992</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0</v>
+        <v>1807.355049499949</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>70</v>
+        <v>64.99999999999999</v>
       </c>
       <c r="H106" s="10" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>0</v>
+        <v>62.88892869832576</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>Massecuite Out</t>
+          <t>Syrup (Pan Floor)</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
@@ -1814,72 +1817,68 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>149081.7758328002</v>
+        <v>179365.3546628679</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>137155.2337661762</v>
+        <v>108450.2805308642</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>114250.1276093569</v>
+        <v>87721.03843634504</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>11926.54206662401</v>
+        <v>70915.07413200376</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>92</v>
+        <v>60.46333793652931</v>
       </c>
       <c r="H107" s="14" t="n">
-        <v>83.29986721770452</v>
+        <v>80.88594884858806</v>
       </c>
       <c r="I107" s="13" t="n">
-        <v>1599.447562026517</v>
+        <v>2230.471673960632</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>Evaporated Water</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="n">
-        <v>60869.76880576191</v>
-      </c>
-      <c r="D108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="9" t="n">
-        <v>60869.76880576191</v>
-      </c>
-      <c r="G108" s="8" t="inlineStr"/>
-      <c r="H108" s="8" t="inlineStr"/>
-      <c r="I108" s="8" t="inlineStr"/>
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr"/>
+      <c r="C108" s="16" t="n">
+        <v>179365.3546628679</v>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>108450.2805308642</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>87721.03843634503</v>
+      </c>
+      <c r="F108" s="16" t="n">
+        <v>70915.07413200378</v>
+      </c>
+      <c r="G108" s="15" t="inlineStr"/>
+      <c r="H108" s="15" t="inlineStr"/>
+      <c r="I108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>Total In</t>
+          <t>Total Out</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr"/>
       <c r="C109" s="16" t="n">
-        <v>209951.5446385621</v>
+        <v>179365.3546628679</v>
       </c>
       <c r="D109" s="16" t="n">
-        <v>137155.2337661762</v>
+        <v>108450.2805308642</v>
       </c>
       <c r="E109" s="16" t="n">
-        <v>114250.1276093569</v>
+        <v>87721.03843634504</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>72796.31087238592</v>
+        <v>70915.07413200376</v>
       </c>
       <c r="G109" s="15" t="inlineStr"/>
       <c r="H109" s="15" t="inlineStr"/>
@@ -1888,236 +1887,246 @@
     <row r="110">
       <c r="A110" s="15" t="inlineStr">
         <is>
-          <t>Total Out</t>
+          <t>Net (In - Out)</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr"/>
       <c r="C110" s="16" t="n">
-        <v>209951.5446385621</v>
+        <v>0</v>
       </c>
       <c r="D110" s="16" t="n">
-        <v>137155.2337661762</v>
+        <v>-1.455191522836685e-11</v>
       </c>
       <c r="E110" s="16" t="n">
-        <v>114250.1276093569</v>
+        <v>-1.455191522836685e-11</v>
       </c>
       <c r="F110" s="16" t="n">
-        <v>72796.31087238592</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="G110" s="15" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr"/>
       <c r="I110" s="15" t="inlineStr"/>
     </row>
-    <row r="111">
-      <c r="A111" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B111" s="15" t="inlineStr"/>
-      <c r="C111" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="15" t="inlineStr"/>
-      <c r="H111" s="15" t="inlineStr"/>
-      <c r="I111" s="15" t="inlineStr"/>
-    </row>
-    <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>A CENTRIFUGALS  [A Centrifugals]</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="5" t="n"/>
-      <c r="D113" s="5" t="n"/>
-      <c r="E113" s="5" t="n"/>
-      <c r="F113" s="5" t="n"/>
-      <c r="G113" s="5" t="n"/>
-      <c r="H113" s="5" t="n"/>
-      <c r="I113" s="5" t="n"/>
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>A PANS  [A Pans]</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="5" t="n"/>
+      <c r="I112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Syrup</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>177571.7011159295</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>107365.7777253542</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>86843.82805180075</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>70205.92339057531</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>60.4633379365214</v>
+      </c>
+      <c r="H114" s="10" t="n">
+        <v>80.8859488485713</v>
+      </c>
+      <c r="I114" s="9" t="n">
+        <v>2208.166957217254</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>B Magma</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C115" s="9" t="n">
+      <c r="C115" s="13" t="n">
+        <v>32379.84352263255</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>29789.45604082195</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>27406.29955755619</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>2590.387481810601</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="H115" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="I115" s="13" t="n">
+        <v>347.3923052751845</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>A Molasses Top-off</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H116" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="n">
         <v>149081.7758328002</v>
       </c>
-      <c r="D115" s="9" t="n">
+      <c r="D117" s="13" t="n">
         <v>137155.2337661762</v>
       </c>
-      <c r="E115" s="9" t="n">
-        <v>114250.127609357</v>
-      </c>
-      <c r="F115" s="9" t="n">
+      <c r="E117" s="13" t="n">
+        <v>114250.1276093569</v>
+      </c>
+      <c r="F117" s="13" t="n">
         <v>11926.54206662401</v>
       </c>
-      <c r="G115" s="10" t="n">
+      <c r="G117" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="H115" s="10" t="n">
+      <c r="H117" s="14" t="n">
         <v>83.29986721770452</v>
       </c>
-      <c r="I115" s="9" t="n">
+      <c r="I117" s="13" t="n">
         <v>1599.447562026517</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="12" t="inlineStr">
-        <is>
-          <t>Wash Water</t>
-        </is>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C116" s="13" t="n">
-        <v>3310.247653066006</v>
-      </c>
-      <c r="D116" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="13" t="n">
-        <v>3310.247653066006</v>
-      </c>
-      <c r="G116" s="12" t="inlineStr"/>
-      <c r="H116" s="12" t="inlineStr"/>
-      <c r="I116" s="12" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>Sugar Out</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>Evaporated Water</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C117" s="9" t="n">
-        <v>68504.35116722419</v>
-      </c>
-      <c r="D117" s="9" t="n">
-        <v>68367.34246488973</v>
-      </c>
-      <c r="E117" s="9" t="n">
-        <v>68162.24043749507</v>
-      </c>
-      <c r="F117" s="9" t="n">
-        <v>137.0087023344531</v>
-      </c>
-      <c r="G117" s="10" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="H117" s="10" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="I117" s="9" t="n">
-        <v>708.2387381611449</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="12" t="inlineStr">
-        <is>
-          <t>Molasses Out</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C118" s="13" t="n">
-        <v>83887.67231864198</v>
-      </c>
-      <c r="D118" s="13" t="n">
-        <v>68787.89130128642</v>
-      </c>
-      <c r="E118" s="13" t="n">
-        <v>46087.8871718619</v>
-      </c>
-      <c r="F118" s="13" t="n">
-        <v>15099.78101735556</v>
-      </c>
-      <c r="G118" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="H118" s="14" t="n">
-        <v>67</v>
-      </c>
-      <c r="I118" s="13" t="n">
-        <v>943.6248347841348</v>
-      </c>
+      <c r="C118" s="9" t="n">
+        <v>60869.76880576191</v>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>60869.76880576191</v>
+      </c>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="15" t="inlineStr">
@@ -2127,16 +2136,16 @@
       </c>
       <c r="B119" s="15" t="inlineStr"/>
       <c r="C119" s="16" t="n">
-        <v>152392.0234858662</v>
+        <v>209951.5446385621</v>
       </c>
       <c r="D119" s="16" t="n">
         <v>137155.2337661762</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>114250.127609357</v>
+        <v>114250.1276093569</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>15236.78971969002</v>
+        <v>72796.31087238592</v>
       </c>
       <c r="G119" s="15" t="inlineStr"/>
       <c r="H119" s="15" t="inlineStr"/>
@@ -2150,16 +2159,16 @@
       </c>
       <c r="B120" s="15" t="inlineStr"/>
       <c r="C120" s="16" t="n">
-        <v>152392.0234858662</v>
+        <v>209951.5446385621</v>
       </c>
       <c r="D120" s="16" t="n">
         <v>137155.2337661762</v>
       </c>
       <c r="E120" s="16" t="n">
-        <v>114250.127609357</v>
+        <v>114250.1276093569</v>
       </c>
       <c r="F120" s="16" t="n">
-        <v>15236.78971969002</v>
+        <v>72796.31087238592</v>
       </c>
       <c r="G120" s="15" t="inlineStr"/>
       <c r="H120" s="15" t="inlineStr"/>
@@ -2179,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="16" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>0</v>
       </c>
       <c r="F121" s="16" t="n">
         <v>0</v>
@@ -2188,2412 +2197,4298 @@
       <c r="H121" s="15" t="inlineStr"/>
       <c r="I121" s="15" t="inlineStr"/>
     </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="n">
+        <v>21.696</v>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B124" s="21" t="n">
+        <v>69723.41309993333</v>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="17" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>A CENTRIFUGALS  [A Centrifugals]</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="5" t="n"/>
+      <c r="D126" s="5" t="n"/>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="5" t="n"/>
+      <c r="I126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>149081.7758328002</v>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>137155.2337661762</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>114250.127609357</v>
+      </c>
+      <c r="F128" s="9" t="n">
+        <v>11926.54206662401</v>
+      </c>
+      <c r="G128" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H128" s="10" t="n">
+        <v>83.29986721770452</v>
+      </c>
+      <c r="I128" s="9" t="n">
+        <v>1599.447562026517</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>Wash Water</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C129" s="13" t="n">
+        <v>3310.247653066006</v>
+      </c>
+      <c r="D129" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>3310.247653066006</v>
+      </c>
+      <c r="G129" s="12" t="inlineStr"/>
+      <c r="H129" s="12" t="inlineStr"/>
+      <c r="I129" s="12" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>Sugar Out</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>68504.35116722419</v>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>68367.34246488973</v>
+      </c>
+      <c r="E130" s="9" t="n">
+        <v>68162.24043749507</v>
+      </c>
+      <c r="F130" s="9" t="n">
+        <v>137.0087023344531</v>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H130" s="10" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="I130" s="9" t="n">
+        <v>708.2387381611449</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>Molasses Out</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C131" s="13" t="n">
+        <v>83887.67231864198</v>
+      </c>
+      <c r="D131" s="13" t="n">
+        <v>68787.89130128642</v>
+      </c>
+      <c r="E131" s="13" t="n">
+        <v>46087.8871718619</v>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>15099.78101735556</v>
+      </c>
+      <c r="G131" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="H131" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="I131" s="13" t="n">
+        <v>943.6248347841348</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="inlineStr"/>
+      <c r="C132" s="16" t="n">
+        <v>152392.0234858662</v>
+      </c>
+      <c r="D132" s="16" t="n">
+        <v>137155.2337661762</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>114250.127609357</v>
+      </c>
+      <c r="F132" s="16" t="n">
+        <v>15236.78971969002</v>
+      </c>
+      <c r="G132" s="15" t="inlineStr"/>
+      <c r="H132" s="15" t="inlineStr"/>
+      <c r="I132" s="15" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="inlineStr"/>
+      <c r="C133" s="16" t="n">
+        <v>152392.0234858662</v>
+      </c>
+      <c r="D133" s="16" t="n">
+        <v>137155.2337661762</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>114250.127609357</v>
+      </c>
+      <c r="F133" s="16" t="n">
+        <v>15236.78971969002</v>
+      </c>
+      <c r="G133" s="15" t="inlineStr"/>
+      <c r="H133" s="15" t="inlineStr"/>
+      <c r="I133" s="15" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr"/>
+      <c r="C134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>-1.455191522836685e-11</v>
+      </c>
+      <c r="F134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="15" t="inlineStr"/>
+      <c r="H134" s="15" t="inlineStr"/>
+      <c r="I134" s="15" t="inlineStr"/>
+    </row>
+    <row r="136" ht="17" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>A MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="5" t="n"/>
-      <c r="F123" s="5" t="n"/>
-      <c r="G123" s="5" t="n"/>
-      <c r="H123" s="5" t="n"/>
-      <c r="I123" s="5" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="5" t="n"/>
+      <c r="I136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G137" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>A Molasses (undiluted)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C125" s="9" t="n">
+      <c r="C138" s="9" t="n">
         <v>83887.67231864198</v>
       </c>
-      <c r="D125" s="9" t="n">
+      <c r="D138" s="9" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E125" s="9" t="n">
+      <c r="E138" s="9" t="n">
         <v>46087.8871718619</v>
       </c>
-      <c r="F125" s="9" t="n">
+      <c r="F138" s="9" t="n">
         <v>15099.78101735556</v>
       </c>
-      <c r="G125" s="10" t="n">
+      <c r="G138" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H125" s="10" t="n">
+      <c r="H138" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="I125" s="9" t="n">
+      <c r="I138" s="9" t="n">
         <v>943.6248347841348</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="12" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
         <is>
           <t>Dilution Water</t>
         </is>
       </c>
-      <c r="B126" s="12" t="inlineStr">
+      <c r="B139" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C126" s="13" t="n">
+      <c r="C139" s="13" t="n">
         <v>14380.74382605292</v>
       </c>
-      <c r="D126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="13" t="n">
+      <c r="D139" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="13" t="n">
         <v>14380.74382605292</v>
       </c>
-      <c r="G126" s="12" t="inlineStr"/>
-      <c r="H126" s="12" t="inlineStr"/>
-      <c r="I126" s="12" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="G139" s="12" t="inlineStr"/>
+      <c r="H139" s="12" t="inlineStr"/>
+      <c r="I139" s="12" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>A Molasses (diluted)</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C127" s="9" t="n">
+      <c r="C140" s="9" t="n">
         <v>98268.4161446949</v>
       </c>
-      <c r="D127" s="9" t="n">
+      <c r="D140" s="9" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E127" s="9" t="n">
+      <c r="E140" s="9" t="n">
         <v>46087.88717186191</v>
       </c>
-      <c r="F127" s="9" t="n">
+      <c r="F140" s="9" t="n">
         <v>29480.52484340848</v>
       </c>
-      <c r="G127" s="10" t="n">
+      <c r="G140" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H127" s="10" t="n">
+      <c r="H140" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="I127" s="9" t="n">
+      <c r="I140" s="9" t="n">
         <v>1169.357489403457</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="15" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B128" s="15" t="inlineStr"/>
-      <c r="C128" s="16" t="n">
+      <c r="B141" s="15" t="inlineStr"/>
+      <c r="C141" s="16" t="n">
         <v>98268.4161446949</v>
       </c>
-      <c r="D128" s="16" t="n">
+      <c r="D141" s="16" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E128" s="16" t="n">
+      <c r="E141" s="16" t="n">
         <v>46087.8871718619</v>
       </c>
-      <c r="F128" s="16" t="n">
+      <c r="F141" s="16" t="n">
         <v>29480.52484340848</v>
       </c>
-      <c r="G128" s="15" t="inlineStr"/>
-      <c r="H128" s="15" t="inlineStr"/>
-      <c r="I128" s="15" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="15" t="inlineStr">
+      <c r="G141" s="15" t="inlineStr"/>
+      <c r="H141" s="15" t="inlineStr"/>
+      <c r="I141" s="15" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B129" s="15" t="inlineStr"/>
-      <c r="C129" s="16" t="n">
+      <c r="B142" s="15" t="inlineStr"/>
+      <c r="C142" s="16" t="n">
         <v>98268.4161446949</v>
       </c>
-      <c r="D129" s="16" t="n">
+      <c r="D142" s="16" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E129" s="16" t="n">
+      <c r="E142" s="16" t="n">
         <v>46087.88717186191</v>
       </c>
-      <c r="F129" s="16" t="n">
+      <c r="F142" s="16" t="n">
         <v>29480.52484340848</v>
       </c>
-      <c r="G129" s="15" t="inlineStr"/>
-      <c r="H129" s="15" t="inlineStr"/>
-      <c r="I129" s="15" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="15" t="inlineStr">
+      <c r="G142" s="15" t="inlineStr"/>
+      <c r="H142" s="15" t="inlineStr"/>
+      <c r="I142" s="15" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B130" s="15" t="inlineStr"/>
-      <c r="C130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="16" t="n">
+      <c r="B143" s="15" t="inlineStr"/>
+      <c r="C143" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="16" t="n">
         <v>-7.275957614183426e-12</v>
       </c>
-      <c r="F130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="15" t="inlineStr"/>
-      <c r="H130" s="15" t="inlineStr"/>
-      <c r="I130" s="15" t="inlineStr"/>
-    </row>
-    <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
+      <c r="F143" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="15" t="inlineStr"/>
+      <c r="H143" s="15" t="inlineStr"/>
+      <c r="I143" s="15" t="inlineStr"/>
+    </row>
+    <row r="145" ht="17" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>B PANS  [B Pans]</t>
         </is>
       </c>
-      <c r="B132" s="5" t="n"/>
-      <c r="C132" s="5" t="n"/>
-      <c r="D132" s="5" t="n"/>
-      <c r="E132" s="5" t="n"/>
-      <c r="F132" s="5" t="n"/>
-      <c r="G132" s="5" t="n"/>
-      <c r="H132" s="5" t="n"/>
-      <c r="I132" s="5" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="5" t="n"/>
+      <c r="I145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E146" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G133" s="6" t="inlineStr">
+      <c r="G146" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="H146" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I146" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>C Magma</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C134" s="9" t="n">
+      <c r="C147" s="9" t="n">
         <v>14593.55008893615</v>
       </c>
-      <c r="D134" s="9" t="n">
+      <c r="D147" s="9" t="n">
         <v>13426.06608182126</v>
       </c>
-      <c r="E134" s="9" t="n">
+      <c r="E147" s="9" t="n">
         <v>11009.37418709343</v>
       </c>
-      <c r="F134" s="9" t="n">
+      <c r="F147" s="9" t="n">
         <v>1167.484007114894</v>
       </c>
-      <c r="G134" s="10" t="n">
+      <c r="G147" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H134" s="10" t="n">
+      <c r="H147" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="I134" s="9" t="n">
+      <c r="I147" s="9" t="n">
         <v>156.5692250489364</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="12" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
         <is>
           <t>A Molasses</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
+      <c r="B148" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C135" s="13" t="n">
+      <c r="C148" s="13" t="n">
         <v>95320.36366035405</v>
       </c>
-      <c r="D135" s="13" t="n">
+      <c r="D148" s="13" t="n">
         <v>66724.25456224784</v>
       </c>
-      <c r="E135" s="13" t="n">
+      <c r="E148" s="13" t="n">
         <v>44705.25055670605</v>
       </c>
-      <c r="F135" s="13" t="n">
+      <c r="F148" s="13" t="n">
         <v>28596.10909810622</v>
       </c>
-      <c r="G135" s="14" t="n">
+      <c r="G148" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H135" s="14" t="n">
+      <c r="H148" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="I135" s="13" t="n">
+      <c r="I148" s="13" t="n">
         <v>1134.276764721353</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C136" s="9" t="n">
+      <c r="C149" s="9" t="n">
         <v>85266.29855752031</v>
       </c>
-      <c r="D136" s="9" t="n">
+      <c r="D149" s="9" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E136" s="9" t="n">
+      <c r="E149" s="9" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F136" s="9" t="n">
+      <c r="F149" s="9" t="n">
         <v>5115.977913451221</v>
       </c>
-      <c r="G136" s="10" t="n">
+      <c r="G149" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="H136" s="10" t="n">
+      <c r="H149" s="10" t="n">
         <v>69.51266607056577</v>
       </c>
-      <c r="I136" s="9" t="n">
+      <c r="I149" s="9" t="n">
         <v>906.1508352228298</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="12" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="12" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B150" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C137" s="13" t="n">
+      <c r="C150" s="13" t="n">
         <v>24647.61519176989</v>
       </c>
-      <c r="D137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" s="13" t="n">
+      <c r="D150" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="13" t="n">
         <v>24647.61519176989</v>
       </c>
-      <c r="G137" s="12" t="inlineStr"/>
-      <c r="H137" s="12" t="inlineStr"/>
-      <c r="I137" s="12" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="inlineStr">
+      <c r="G150" s="12" t="inlineStr"/>
+      <c r="H150" s="12" t="inlineStr"/>
+      <c r="I150" s="12" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B138" s="15" t="inlineStr"/>
-      <c r="C138" s="16" t="n">
+      <c r="B151" s="15" t="inlineStr"/>
+      <c r="C151" s="16" t="n">
         <v>109913.9137492902</v>
       </c>
-      <c r="D138" s="16" t="n">
+      <c r="D151" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E138" s="16" t="n">
+      <c r="E151" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F138" s="16" t="n">
+      <c r="F151" s="16" t="n">
         <v>29763.59310522111</v>
       </c>
-      <c r="G138" s="15" t="inlineStr"/>
-      <c r="H138" s="15" t="inlineStr"/>
-      <c r="I138" s="15" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="15" t="inlineStr">
+      <c r="G151" s="15" t="inlineStr"/>
+      <c r="H151" s="15" t="inlineStr"/>
+      <c r="I151" s="15" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B139" s="15" t="inlineStr"/>
-      <c r="C139" s="16" t="n">
+      <c r="B152" s="15" t="inlineStr"/>
+      <c r="C152" s="16" t="n">
         <v>109913.9137492902</v>
       </c>
-      <c r="D139" s="16" t="n">
+      <c r="D152" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E139" s="16" t="n">
+      <c r="E152" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F139" s="16" t="n">
+      <c r="F152" s="16" t="n">
         <v>29763.59310522111</v>
       </c>
-      <c r="G139" s="15" t="inlineStr"/>
-      <c r="H139" s="15" t="inlineStr"/>
-      <c r="I139" s="15" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="inlineStr">
+      <c r="G152" s="15" t="inlineStr"/>
+      <c r="H152" s="15" t="inlineStr"/>
+      <c r="I152" s="15" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B140" s="15" t="inlineStr"/>
-      <c r="C140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="15" t="inlineStr"/>
-      <c r="H140" s="15" t="inlineStr"/>
-      <c r="I140" s="15" t="inlineStr"/>
-    </row>
-    <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="B153" s="15" t="inlineStr"/>
+      <c r="C153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="15" t="inlineStr"/>
+      <c r="H153" s="15" t="inlineStr"/>
+      <c r="I153" s="15" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B155" s="20" t="n">
+        <v>29.696</v>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B156" s="21" t="n">
+        <v>29613.16522157839</v>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="17" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t>B CENTRIFUGALS  [B Centrifugals]</t>
         </is>
       </c>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="n"/>
-      <c r="E142" s="5" t="n"/>
-      <c r="F142" s="5" t="n"/>
-      <c r="G142" s="5" t="n"/>
-      <c r="H142" s="5" t="n"/>
-      <c r="I142" s="5" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G143" s="6" t="inlineStr">
+      <c r="G159" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H143" s="6" t="inlineStr">
+      <c r="H159" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I143" s="6" t="inlineStr">
+      <c r="I159" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C144" s="9" t="n">
+      <c r="C160" s="9" t="n">
         <v>85266.29855752031</v>
       </c>
-      <c r="D144" s="9" t="n">
+      <c r="D160" s="9" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E144" s="9" t="n">
+      <c r="E160" s="9" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F144" s="9" t="n">
+      <c r="F160" s="9" t="n">
         <v>5115.977913451221</v>
       </c>
-      <c r="G144" s="10" t="n">
+      <c r="G160" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="H144" s="10" t="n">
+      <c r="H160" s="10" t="n">
         <v>69.51266607056577</v>
       </c>
-      <c r="I144" s="9" t="n">
+      <c r="I160" s="9" t="n">
         <v>906.1508352228298</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="12" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr">
+      <c r="B161" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C145" s="13" t="n">
+      <c r="C161" s="13" t="n">
         <v>6263.891436226622</v>
       </c>
-      <c r="D145" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="13" t="n">
+      <c r="D161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="13" t="n">
         <v>6263.891436226622</v>
       </c>
-      <c r="G145" s="12" t="inlineStr"/>
-      <c r="H145" s="12" t="inlineStr"/>
-      <c r="I145" s="12" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="G161" s="12" t="inlineStr"/>
+      <c r="H161" s="12" t="inlineStr"/>
+      <c r="I161" s="12" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C146" s="9" t="n">
+      <c r="C162" s="9" t="n">
         <v>39196.65268612767</v>
       </c>
-      <c r="D146" s="9" t="n">
+      <c r="D162" s="9" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E146" s="9" t="n">
+      <c r="E162" s="9" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F146" s="9" t="n">
+      <c r="F162" s="9" t="n">
         <v>1959.832634306382</v>
       </c>
-      <c r="G146" s="10" t="n">
+      <c r="G162" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="H146" s="10" t="n">
+      <c r="H162" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I146" s="9" t="n">
+      <c r="I162" s="9" t="n">
         <v>414.581749172197</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="12" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B147" s="12" t="inlineStr">
+      <c r="B163" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C147" s="13" t="n">
+      <c r="C163" s="13" t="n">
         <v>52333.53730761927</v>
       </c>
-      <c r="D147" s="13" t="n">
+      <c r="D163" s="13" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E147" s="13" t="n">
+      <c r="E163" s="13" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F147" s="13" t="n">
+      <c r="F163" s="13" t="n">
         <v>9420.036715371476</v>
       </c>
-      <c r="G147" s="14" t="n">
+      <c r="G163" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H147" s="14" t="n">
+      <c r="H163" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="I147" s="13" t="n">
+      <c r="I163" s="13" t="n">
         <v>588.6827483780042</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="15" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B148" s="15" t="inlineStr"/>
-      <c r="C148" s="16" t="n">
+      <c r="B164" s="15" t="inlineStr"/>
+      <c r="C164" s="16" t="n">
         <v>91530.18999374693</v>
       </c>
-      <c r="D148" s="16" t="n">
+      <c r="D164" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E148" s="16" t="n">
+      <c r="E164" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F148" s="16" t="n">
+      <c r="F164" s="16" t="n">
         <v>11379.86934967784</v>
       </c>
-      <c r="G148" s="15" t="inlineStr"/>
-      <c r="H148" s="15" t="inlineStr"/>
-      <c r="I148" s="15" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="15" t="inlineStr">
+      <c r="G164" s="15" t="inlineStr"/>
+      <c r="H164" s="15" t="inlineStr"/>
+      <c r="I164" s="15" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B149" s="15" t="inlineStr"/>
-      <c r="C149" s="16" t="n">
+      <c r="B165" s="15" t="inlineStr"/>
+      <c r="C165" s="16" t="n">
         <v>91530.18999374693</v>
       </c>
-      <c r="D149" s="16" t="n">
+      <c r="D165" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E149" s="16" t="n">
+      <c r="E165" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F149" s="16" t="n">
+      <c r="F165" s="16" t="n">
         <v>11379.86934967784</v>
       </c>
-      <c r="G149" s="15" t="inlineStr"/>
-      <c r="H149" s="15" t="inlineStr"/>
-      <c r="I149" s="15" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="inlineStr">
+      <c r="G165" s="15" t="inlineStr"/>
+      <c r="H165" s="15" t="inlineStr"/>
+      <c r="I165" s="15" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B150" s="15" t="inlineStr"/>
-      <c r="C150" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" s="16" t="n">
+      <c r="B166" s="15" t="inlineStr"/>
+      <c r="C166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="16" t="n">
         <v>7.275957614183426e-12</v>
       </c>
-      <c r="F150" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" s="15" t="inlineStr"/>
-      <c r="H150" s="15" t="inlineStr"/>
-      <c r="I150" s="15" t="inlineStr"/>
-    </row>
-    <row r="152" ht="17" customHeight="1">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="F166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="15" t="inlineStr"/>
+      <c r="H166" s="15" t="inlineStr"/>
+      <c r="I166" s="15" t="inlineStr"/>
+    </row>
+    <row r="168" ht="17" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>B MAGMA  (mingler target 92.0 Bx)</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="5" t="n"/>
+      <c r="I168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t>B Sugar</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>39196.65268612767</v>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E170" s="9" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F170" s="9" t="n">
+        <v>1959.832634306382</v>
+      </c>
+      <c r="G170" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H170" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I170" s="9" t="n">
+        <v>414.581749172197</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>Mingler Water</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C171" s="13" t="n">
+        <v>1278.151718025903</v>
+      </c>
+      <c r="D171" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="13" t="n">
+        <v>1278.151718025903</v>
+      </c>
+      <c r="G171" s="12" t="inlineStr"/>
+      <c r="H171" s="12" t="inlineStr"/>
+      <c r="I171" s="12" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>B Magma</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="n">
+        <v>40474.80440415357</v>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E172" s="9" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F172" s="9" t="n">
+        <v>3237.984352332285</v>
+      </c>
+      <c r="G172" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H172" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I172" s="9" t="n">
+        <v>434.2403816032381</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B173" s="15" t="inlineStr"/>
+      <c r="C173" s="16" t="n">
+        <v>40474.80440415357</v>
+      </c>
+      <c r="D173" s="16" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F173" s="16" t="n">
+        <v>3237.984352332285</v>
+      </c>
+      <c r="G173" s="15" t="inlineStr"/>
+      <c r="H173" s="15" t="inlineStr"/>
+      <c r="I173" s="15" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B174" s="15" t="inlineStr"/>
+      <c r="C174" s="16" t="n">
+        <v>40474.80440415357</v>
+      </c>
+      <c r="D174" s="16" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F174" s="16" t="n">
+        <v>3237.984352332285</v>
+      </c>
+      <c r="G174" s="15" t="inlineStr"/>
+      <c r="H174" s="15" t="inlineStr"/>
+      <c r="I174" s="15" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B175" s="15" t="inlineStr"/>
+      <c r="C175" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="15" t="inlineStr"/>
+      <c r="H175" s="15" t="inlineStr"/>
+      <c r="I175" s="15" t="inlineStr"/>
+    </row>
+    <row r="177" ht="17" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>B MAGMA DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="5" t="n"/>
+      <c r="I177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>Magma (total)</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="n">
+        <v>40474.80440415357</v>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E179" s="9" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F179" s="9" t="n">
+        <v>3237.984352332285</v>
+      </c>
+      <c r="G179" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H179" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I179" s="9" t="n">
+        <v>434.2403816032381</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>B Magma to A Footing</t>
+        </is>
+      </c>
+      <c r="B180" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C180" s="13" t="n">
+        <v>32379.84352332286</v>
+      </c>
+      <c r="D180" s="13" t="n">
+        <v>29789.45604145703</v>
+      </c>
+      <c r="E180" s="13" t="n">
+        <v>27406.29955814046</v>
+      </c>
+      <c r="F180" s="13" t="n">
+        <v>2590.387481865826</v>
+      </c>
+      <c r="G180" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="H180" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="I180" s="13" t="n">
+        <v>347.3923052825905</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>B Magma to Remelt</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="n">
+        <v>8094.960880830714</v>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>7447.364010364257</v>
+      </c>
+      <c r="E181" s="9" t="n">
+        <v>6851.574889535116</v>
+      </c>
+      <c r="F181" s="9" t="n">
+        <v>647.5968704664565</v>
+      </c>
+      <c r="G181" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H181" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I181" s="9" t="n">
+        <v>86.84807632064764</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B182" s="15" t="inlineStr"/>
+      <c r="C182" s="16" t="n">
+        <v>40474.80440415357</v>
+      </c>
+      <c r="D182" s="16" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F182" s="16" t="n">
+        <v>3237.984352332285</v>
+      </c>
+      <c r="G182" s="15" t="inlineStr"/>
+      <c r="H182" s="15" t="inlineStr"/>
+      <c r="I182" s="15" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B183" s="15" t="inlineStr"/>
+      <c r="C183" s="16" t="n">
+        <v>40474.80440415357</v>
+      </c>
+      <c r="D183" s="16" t="n">
+        <v>37236.82005182128</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>34257.87444767558</v>
+      </c>
+      <c r="F183" s="16" t="n">
+        <v>3237.984352332285</v>
+      </c>
+      <c r="G183" s="15" t="inlineStr"/>
+      <c r="H183" s="15" t="inlineStr"/>
+      <c r="I183" s="15" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B184" s="15" t="inlineStr"/>
+      <c r="C184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="15" t="inlineStr"/>
+      <c r="H184" s="15" t="inlineStr"/>
+      <c r="I184" s="15" t="inlineStr"/>
+    </row>
+    <row r="186" ht="17" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>B REMELT  (target 65.0 Bx)</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="5" t="n"/>
+      <c r="I186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>B Magma (to Remelt)</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="n">
+        <v>8094.960880830714</v>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>7447.364010364257</v>
+      </c>
+      <c r="E188" s="9" t="n">
+        <v>6851.574889535116</v>
+      </c>
+      <c r="F188" s="9" t="n">
+        <v>647.5968704664565</v>
+      </c>
+      <c r="G188" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H188" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I188" s="9" t="n">
+        <v>86.84807632064764</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>Remelt Water</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C189" s="13" t="n">
+        <v>3362.522212037374</v>
+      </c>
+      <c r="D189" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="13" t="n">
+        <v>3362.522212037374</v>
+      </c>
+      <c r="G189" s="12" t="inlineStr"/>
+      <c r="H189" s="12" t="inlineStr"/>
+      <c r="I189" s="12" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>B Remelt</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="n">
+        <v>11457.48309286809</v>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>7447.364010364257</v>
+      </c>
+      <c r="E190" s="9" t="n">
+        <v>6851.574889535116</v>
+      </c>
+      <c r="F190" s="9" t="n">
+        <v>4010.11908250383</v>
+      </c>
+      <c r="G190" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="H190" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I190" s="9" t="n">
+        <v>139.5365526663698</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B191" s="15" t="inlineStr"/>
+      <c r="C191" s="16" t="n">
+        <v>11457.48309286809</v>
+      </c>
+      <c r="D191" s="16" t="n">
+        <v>7447.364010364257</v>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>6851.574889535116</v>
+      </c>
+      <c r="F191" s="16" t="n">
+        <v>4010.11908250383</v>
+      </c>
+      <c r="G191" s="15" t="inlineStr"/>
+      <c r="H191" s="15" t="inlineStr"/>
+      <c r="I191" s="15" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr"/>
+      <c r="C192" s="16" t="n">
+        <v>11457.48309286809</v>
+      </c>
+      <c r="D192" s="16" t="n">
+        <v>7447.364010364257</v>
+      </c>
+      <c r="E192" s="16" t="n">
+        <v>6851.574889535116</v>
+      </c>
+      <c r="F192" s="16" t="n">
+        <v>4010.11908250383</v>
+      </c>
+      <c r="G192" s="15" t="inlineStr"/>
+      <c r="H192" s="15" t="inlineStr"/>
+      <c r="I192" s="15" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B193" s="15" t="inlineStr"/>
+      <c r="C193" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="15" t="inlineStr"/>
+      <c r="H193" s="15" t="inlineStr"/>
+      <c r="I193" s="15" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="17" t="inlineStr">
+        <is>
+          <t>Target remelt brix</t>
+        </is>
+      </c>
+      <c r="B194" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="C194" s="19" t="inlineStr">
+        <is>
+          <t>Bx</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="17" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
         <is>
           <t>B MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
-      <c r="B152" s="5" t="n"/>
-      <c r="C152" s="5" t="n"/>
-      <c r="D152" s="5" t="n"/>
-      <c r="E152" s="5" t="n"/>
-      <c r="F152" s="5" t="n"/>
-      <c r="G152" s="5" t="n"/>
-      <c r="H152" s="5" t="n"/>
-      <c r="I152" s="5" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="5" t="n"/>
+      <c r="I196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="B197" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C197" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D197" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E197" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G153" s="6" t="inlineStr">
+      <c r="G197" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H153" s="6" t="inlineStr">
+      <c r="H197" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I153" s="6" t="inlineStr">
+      <c r="I197" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="8" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>B Molasses (undiluted)</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C154" s="9" t="n">
+      <c r="C198" s="9" t="n">
         <v>52333.53730761927</v>
       </c>
-      <c r="D154" s="9" t="n">
+      <c r="D198" s="9" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E154" s="9" t="n">
+      <c r="E198" s="9" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F154" s="9" t="n">
+      <c r="F198" s="9" t="n">
         <v>9420.036715371476</v>
       </c>
-      <c r="G154" s="10" t="n">
+      <c r="G198" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H154" s="10" t="n">
+      <c r="H198" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I154" s="9" t="n">
+      <c r="I198" s="9" t="n">
         <v>588.6827483780042</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="12" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="12" t="inlineStr">
         <is>
           <t>Dilution Water</t>
         </is>
       </c>
-      <c r="B155" s="12" t="inlineStr">
+      <c r="B199" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C155" s="13" t="n">
+      <c r="C199" s="13" t="n">
         <v>8971.46353844901</v>
       </c>
-      <c r="D155" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="13" t="n">
+      <c r="D199" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="13" t="n">
         <v>8971.46353844901</v>
       </c>
-      <c r="G155" s="12" t="inlineStr"/>
-      <c r="H155" s="12" t="inlineStr"/>
-      <c r="I155" s="12" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="G199" s="12" t="inlineStr"/>
+      <c r="H199" s="12" t="inlineStr"/>
+      <c r="I199" s="12" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="inlineStr">
         <is>
           <t>B Molasses (diluted)</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C156" s="9" t="n">
+      <c r="C200" s="9" t="n">
         <v>61305.00084606828</v>
       </c>
-      <c r="D156" s="9" t="n">
+      <c r="D200" s="9" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E156" s="9" t="n">
+      <c r="E200" s="9" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F156" s="9" t="n">
+      <c r="F200" s="9" t="n">
         <v>18391.50025382049</v>
       </c>
-      <c r="G156" s="10" t="n">
+      <c r="G200" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H156" s="10" t="n">
+      <c r="H200" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I156" s="9" t="n">
+      <c r="I200" s="9" t="n">
         <v>729.5066379382704</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="15" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B157" s="15" t="inlineStr"/>
-      <c r="C157" s="16" t="n">
+      <c r="B201" s="15" t="inlineStr"/>
+      <c r="C201" s="16" t="n">
         <v>61305.00084606828</v>
       </c>
-      <c r="D157" s="16" t="n">
+      <c r="D201" s="16" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E157" s="16" t="n">
+      <c r="E201" s="16" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F157" s="16" t="n">
+      <c r="F201" s="16" t="n">
         <v>18391.50025382049</v>
       </c>
-      <c r="G157" s="15" t="inlineStr"/>
-      <c r="H157" s="15" t="inlineStr"/>
-      <c r="I157" s="15" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="15" t="inlineStr">
+      <c r="G201" s="15" t="inlineStr"/>
+      <c r="H201" s="15" t="inlineStr"/>
+      <c r="I201" s="15" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B158" s="15" t="inlineStr"/>
-      <c r="C158" s="16" t="n">
+      <c r="B202" s="15" t="inlineStr"/>
+      <c r="C202" s="16" t="n">
         <v>61305.00084606828</v>
       </c>
-      <c r="D158" s="16" t="n">
+      <c r="D202" s="16" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E158" s="16" t="n">
+      <c r="E202" s="16" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F158" s="16" t="n">
+      <c r="F202" s="16" t="n">
         <v>18391.50025382049</v>
       </c>
-      <c r="G158" s="15" t="inlineStr"/>
-      <c r="H158" s="15" t="inlineStr"/>
-      <c r="I158" s="15" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="15" t="inlineStr">
+      <c r="G202" s="15" t="inlineStr"/>
+      <c r="H202" s="15" t="inlineStr"/>
+      <c r="I202" s="15" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B159" s="15" t="inlineStr"/>
-      <c r="C159" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" s="15" t="inlineStr"/>
-      <c r="H159" s="15" t="inlineStr"/>
-      <c r="I159" s="15" t="inlineStr"/>
-    </row>
-    <row r="161" ht="17" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
+      <c r="B203" s="15" t="inlineStr"/>
+      <c r="C203" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" s="15" t="inlineStr"/>
+      <c r="H203" s="15" t="inlineStr"/>
+      <c r="I203" s="15" t="inlineStr"/>
+    </row>
+    <row r="205" ht="17" customHeight="1">
+      <c r="A205" s="4" t="inlineStr">
         <is>
           <t>GRAIN PANS  [Grain Pans]</t>
         </is>
       </c>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="5" t="n"/>
-      <c r="D161" s="5" t="n"/>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="n"/>
-      <c r="G161" s="5" t="n"/>
-      <c r="H161" s="5" t="n"/>
-      <c r="I161" s="5" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="B206" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
+      <c r="C206" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E206" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G162" s="6" t="inlineStr">
+      <c r="G206" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="H206" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
+      <c r="I206" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="8" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
         <is>
           <t>Syrup</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B207" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C163" s="9" t="n">
+      <c r="C207" s="9" t="n">
         <v>1793.653546625551</v>
       </c>
-      <c r="D163" s="9" t="n">
+      <c r="D207" s="9" t="n">
         <v>1084.502805306608</v>
       </c>
-      <c r="E163" s="9" t="n">
+      <c r="E207" s="9" t="n">
         <v>877.2103843616237</v>
       </c>
-      <c r="F163" s="9" t="n">
+      <c r="F207" s="9" t="n">
         <v>709.1507413189427</v>
       </c>
-      <c r="G163" s="10" t="n">
+      <c r="G207" s="10" t="n">
         <v>60.4633379365214</v>
       </c>
-      <c r="H163" s="10" t="n">
+      <c r="H207" s="10" t="n">
         <v>80.8859488485713</v>
       </c>
-      <c r="I163" s="9" t="n">
+      <c r="I207" s="9" t="n">
         <v>22.30471673956822</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="12" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="12" t="inlineStr">
         <is>
           <t>A Molasses</t>
         </is>
       </c>
-      <c r="B164" s="12" t="inlineStr">
+      <c r="B208" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C164" s="13" t="n">
+      <c r="C208" s="13" t="n">
         <v>2948.052484340847</v>
       </c>
-      <c r="D164" s="13" t="n">
+      <c r="D208" s="13" t="n">
         <v>2063.636739038593</v>
       </c>
-      <c r="E164" s="13" t="n">
+      <c r="E208" s="13" t="n">
         <v>1382.636615155857</v>
       </c>
-      <c r="F164" s="13" t="n">
+      <c r="F208" s="13" t="n">
         <v>884.415745302254</v>
       </c>
-      <c r="G164" s="14" t="n">
+      <c r="G208" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H164" s="14" t="n">
+      <c r="H208" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="I164" s="13" t="n">
+      <c r="I208" s="13" t="n">
         <v>35.08072468210372</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="8" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>B Molasses</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B209" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C165" s="9" t="n">
+      <c r="C209" s="9" t="n">
         <v>6130.500084606829</v>
       </c>
-      <c r="D165" s="9" t="n">
+      <c r="D209" s="9" t="n">
         <v>4291.35005922478</v>
       </c>
-      <c r="E165" s="9" t="n">
+      <c r="E209" s="9" t="n">
         <v>2145.67502961239</v>
       </c>
-      <c r="F165" s="9" t="n">
+      <c r="F209" s="9" t="n">
         <v>1839.150025382049</v>
       </c>
-      <c r="G165" s="10" t="n">
+      <c r="G209" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H165" s="10" t="n">
+      <c r="H209" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I165" s="9" t="n">
+      <c r="I209" s="9" t="n">
         <v>72.95066379382705</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="12" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="12" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B166" s="12" t="inlineStr">
+      <c r="B210" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C166" s="13" t="n">
+      <c r="C210" s="13" t="n">
         <v>8453.965458602252</v>
       </c>
-      <c r="D166" s="13" t="n">
+      <c r="D210" s="13" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E166" s="13" t="n">
+      <c r="E210" s="13" t="n">
         <v>4405.522029129871</v>
       </c>
-      <c r="F166" s="13" t="n">
+      <c r="F210" s="13" t="n">
         <v>1014.47585503227</v>
       </c>
-      <c r="G166" s="14" t="n">
+      <c r="G210" s="14" t="n">
         <v>88</v>
       </c>
-      <c r="H166" s="14" t="n">
+      <c r="H210" s="14" t="n">
         <v>59.21806822629064</v>
       </c>
-      <c r="I166" s="13" t="n">
+      <c r="I210" s="13" t="n">
         <v>92.4361833097628</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="8" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B211" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C167" s="9" t="n">
+      <c r="C211" s="9" t="n">
         <v>2418.240656970975</v>
       </c>
-      <c r="D167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="9" t="n">
+      <c r="D211" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="9" t="n">
         <v>2418.240656970975</v>
       </c>
-      <c r="G167" s="8" t="inlineStr"/>
-      <c r="H167" s="8" t="inlineStr"/>
-      <c r="I167" s="8" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="15" t="inlineStr">
+      <c r="G211" s="8" t="inlineStr"/>
+      <c r="H211" s="8" t="inlineStr"/>
+      <c r="I211" s="8" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B168" s="15" t="inlineStr"/>
-      <c r="C168" s="16" t="n">
+      <c r="B212" s="15" t="inlineStr"/>
+      <c r="C212" s="16" t="n">
         <v>10872.20611557323</v>
       </c>
-      <c r="D168" s="16" t="n">
+      <c r="D212" s="16" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E168" s="16" t="n">
+      <c r="E212" s="16" t="n">
         <v>4405.522029129871</v>
       </c>
-      <c r="F168" s="16" t="n">
+      <c r="F212" s="16" t="n">
         <v>3432.716512003245</v>
       </c>
-      <c r="G168" s="15" t="inlineStr"/>
-      <c r="H168" s="15" t="inlineStr"/>
-      <c r="I168" s="15" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="15" t="inlineStr">
+      <c r="G212" s="15" t="inlineStr"/>
+      <c r="H212" s="15" t="inlineStr"/>
+      <c r="I212" s="15" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B169" s="15" t="inlineStr"/>
-      <c r="C169" s="16" t="n">
+      <c r="B213" s="15" t="inlineStr"/>
+      <c r="C213" s="16" t="n">
         <v>10872.20611557323</v>
       </c>
-      <c r="D169" s="16" t="n">
+      <c r="D213" s="16" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E169" s="16" t="n">
+      <c r="E213" s="16" t="n">
         <v>4405.522029129871</v>
       </c>
-      <c r="F169" s="16" t="n">
+      <c r="F213" s="16" t="n">
         <v>3432.716512003245</v>
       </c>
-      <c r="G169" s="15" t="inlineStr"/>
-      <c r="H169" s="15" t="inlineStr"/>
-      <c r="I169" s="15" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="15" t="inlineStr">
+      <c r="G213" s="15" t="inlineStr"/>
+      <c r="H213" s="15" t="inlineStr"/>
+      <c r="I213" s="15" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B170" s="15" t="inlineStr"/>
-      <c r="C170" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="15" t="inlineStr"/>
-      <c r="H170" s="15" t="inlineStr"/>
-      <c r="I170" s="15" t="inlineStr"/>
-    </row>
-    <row r="172" ht="17" customHeight="1">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>C PANS  [C Pans]</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="5" t="n"/>
-      <c r="F172" s="5" t="n"/>
-      <c r="G172" s="5" t="n"/>
-      <c r="H172" s="5" t="n"/>
-      <c r="I172" s="5" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G173" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H173" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>Grain Massecuite</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C174" s="9" t="n">
-        <v>8453.965458602252</v>
-      </c>
-      <c r="D174" s="9" t="n">
-        <v>7439.489603569981</v>
-      </c>
-      <c r="E174" s="9" t="n">
-        <v>4405.52202912987</v>
-      </c>
-      <c r="F174" s="9" t="n">
-        <v>1014.47585503227</v>
-      </c>
-      <c r="G174" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="H174" s="10" t="n">
-        <v>59.21806822629064</v>
-      </c>
-      <c r="I174" s="9" t="n">
-        <v>92.4361833097628</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="12" t="inlineStr">
-        <is>
-          <t>B Molasses</t>
-        </is>
-      </c>
-      <c r="B175" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C175" s="13" t="n">
-        <v>55174.50076146145</v>
-      </c>
-      <c r="D175" s="13" t="n">
-        <v>38622.15053302301</v>
-      </c>
-      <c r="E175" s="13" t="n">
-        <v>19311.07526651151</v>
-      </c>
-      <c r="F175" s="13" t="n">
-        <v>16552.35022843844</v>
-      </c>
-      <c r="G175" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="H175" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="I175" s="13" t="n">
-        <v>656.5559741444433</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite Out</t>
-        </is>
-      </c>
-      <c r="B176" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C176" s="9" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D176" s="9" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E176" s="9" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F176" s="9" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G176" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H176" s="10" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I176" s="9" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="12" t="inlineStr">
-        <is>
-          <t>Evaporated Water</t>
-        </is>
-      </c>
-      <c r="B177" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C177" s="13" t="n">
-        <v>15396.38230740088</v>
-      </c>
-      <c r="D177" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" s="13" t="n">
-        <v>15396.38230740088</v>
-      </c>
-      <c r="G177" s="12" t="inlineStr"/>
-      <c r="H177" s="12" t="inlineStr"/>
-      <c r="I177" s="12" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="15" t="inlineStr">
-        <is>
-          <t>Total In</t>
-        </is>
-      </c>
-      <c r="B178" s="15" t="inlineStr"/>
-      <c r="C178" s="16" t="n">
-        <v>63628.4662200637</v>
-      </c>
-      <c r="D178" s="16" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E178" s="16" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F178" s="16" t="n">
-        <v>17566.82608347071</v>
-      </c>
-      <c r="G178" s="15" t="inlineStr"/>
-      <c r="H178" s="15" t="inlineStr"/>
-      <c r="I178" s="15" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="15" t="inlineStr">
-        <is>
-          <t>Total Out</t>
-        </is>
-      </c>
-      <c r="B179" s="15" t="inlineStr"/>
-      <c r="C179" s="16" t="n">
-        <v>63628.4662200637</v>
-      </c>
-      <c r="D179" s="16" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E179" s="16" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F179" s="16" t="n">
-        <v>17566.82608347071</v>
-      </c>
-      <c r="G179" s="15" t="inlineStr"/>
-      <c r="H179" s="15" t="inlineStr"/>
-      <c r="I179" s="15" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B180" s="15" t="inlineStr"/>
-      <c r="C180" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="15" t="inlineStr"/>
-      <c r="H180" s="15" t="inlineStr"/>
-      <c r="I180" s="15" t="inlineStr"/>
-    </row>
-    <row r="182" ht="17" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>C CRYSTALLIZERS  [C Crystallizers]</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="n"/>
-      <c r="C182" s="5" t="n"/>
-      <c r="D182" s="5" t="n"/>
-      <c r="E182" s="5" t="n"/>
-      <c r="F182" s="5" t="n"/>
-      <c r="G182" s="5" t="n"/>
-      <c r="H182" s="5" t="n"/>
-      <c r="I182" s="5" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D183" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F183" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G183" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H183" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite In  (T=173.0 °F)</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C184" s="9" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D184" s="9" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E184" s="9" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F184" s="9" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G184" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H184" s="10" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I184" s="9" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="12" t="inlineStr">
-        <is>
-          <t>Massecuite Out  (T=120.0 °F)</t>
-        </is>
-      </c>
-      <c r="B185" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C185" s="13" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D185" s="13" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E185" s="13" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F185" s="13" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G185" s="14" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H185" s="14" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I185" s="13" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="17" t="inlineStr">
-        <is>
-          <t>ML purity in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B186" s="20" t="inlineStr">
-        <is>
-          <t>33.0 -&gt; 30.0</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="17" t="inlineStr">
-        <is>
-          <t>Crystal content in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B187" s="20" t="inlineStr">
-        <is>
-          <t>26.4 -&gt; 29.3</t>
-        </is>
-      </c>
-      <c r="C187" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="17" t="inlineStr">
-        <is>
-          <t>Duty</t>
-        </is>
-      </c>
-      <c r="B188" s="21" t="n">
-        <v>1165803.366111661</v>
-      </c>
-      <c r="C188" s="19" t="inlineStr">
-        <is>
-          <t>BTU/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="17" t="inlineStr">
-        <is>
-          <t>Cooling Water</t>
-        </is>
-      </c>
-      <c r="B189" s="21" t="n">
-        <v>58290.16830558303</v>
-      </c>
-      <c r="C189" s="19" t="inlineStr">
-        <is>
-          <t>lb/hr  (116 gpm, 85 -&gt; 105 °F)</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="17" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>C REHEATERS  [C Reheaters]</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="n"/>
-      <c r="C191" s="5" t="n"/>
-      <c r="D191" s="5" t="n"/>
-      <c r="E191" s="5" t="n"/>
-      <c r="F191" s="5" t="n"/>
-      <c r="G191" s="5" t="n"/>
-      <c r="H191" s="5" t="n"/>
-      <c r="I191" s="5" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I192" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite In  (T=120.0 °F)</t>
-        </is>
-      </c>
-      <c r="B193" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C193" s="9" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D193" s="9" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E193" s="9" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F193" s="9" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G193" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H193" s="10" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I193" s="9" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="12" t="inlineStr">
-        <is>
-          <t>Massecuite Out  (T=130.0 °F)</t>
-        </is>
-      </c>
-      <c r="B194" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C194" s="13" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D194" s="13" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E194" s="13" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F194" s="13" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G194" s="14" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H194" s="14" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I194" s="13" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="17" t="inlineStr">
-        <is>
-          <t>ML purity in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B195" s="20" t="inlineStr">
-        <is>
-          <t>30.0 -&gt; 30.0</t>
-        </is>
-      </c>
-      <c r="C195" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="17" t="inlineStr">
-        <is>
-          <t>Crystal content in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B196" s="20" t="inlineStr">
-        <is>
-          <t>29.3 -&gt; 29.3</t>
-        </is>
-      </c>
-      <c r="C196" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="17" t="inlineStr">
-        <is>
-          <t>Duty</t>
-        </is>
-      </c>
-      <c r="B197" s="21" t="n">
-        <v>220059.8474932024</v>
-      </c>
-      <c r="C197" s="19" t="inlineStr">
-        <is>
-          <t>BTU/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="17" t="inlineStr">
-        <is>
-          <t>Hot Water</t>
-        </is>
-      </c>
-      <c r="B198" s="21" t="n">
-        <v>14670.65649954683</v>
-      </c>
-      <c r="C198" s="19" t="inlineStr">
-        <is>
-          <t>lb/hr  (29 gpm, 150 -&gt; 135 °F)</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="17" customHeight="1">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>C CENTRIFUGALS  [C Centrifugals]</t>
-        </is>
-      </c>
-      <c r="B200" s="5" t="n"/>
-      <c r="C200" s="5" t="n"/>
-      <c r="D200" s="5" t="n"/>
-      <c r="E200" s="5" t="n"/>
-      <c r="F200" s="5" t="n"/>
-      <c r="G200" s="5" t="n"/>
-      <c r="H200" s="5" t="n"/>
-      <c r="I200" s="5" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B201" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C201" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D201" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E201" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F201" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G201" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H201" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I201" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite</t>
-        </is>
-      </c>
-      <c r="B202" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C202" s="9" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D202" s="9" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E202" s="9" t="n">
-        <v>23716.59729564139</v>
-      </c>
-      <c r="F202" s="9" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G202" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H202" s="10" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I202" s="9" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="12" t="inlineStr">
-        <is>
-          <t>Wash Water</t>
-        </is>
-      </c>
-      <c r="B203" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C203" s="13" t="n">
-        <v>5139.960235525126</v>
-      </c>
-      <c r="D203" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F203" s="13" t="n">
-        <v>5139.960235525126</v>
-      </c>
-      <c r="G203" s="12" t="inlineStr"/>
-      <c r="H203" s="12" t="inlineStr"/>
-      <c r="I203" s="12" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="8" t="inlineStr">
-        <is>
-          <t>Sugar Out</t>
-        </is>
-      </c>
-      <c r="B204" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C204" s="9" t="n">
-        <v>17665.8764236837</v>
-      </c>
-      <c r="D204" s="9" t="n">
-        <v>16782.58260249951</v>
-      </c>
-      <c r="E204" s="9" t="n">
-        <v>13761.71773404961</v>
-      </c>
-      <c r="F204" s="9" t="n">
-        <v>883.2938211841865</v>
-      </c>
-      <c r="G204" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="H204" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="I204" s="9" t="n">
-        <v>186.8514132326083</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="12" t="inlineStr">
-        <is>
-          <t>Molasses Out</t>
-        </is>
-      </c>
-      <c r="B205" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C205" s="13" t="n">
-        <v>35706.16772450424</v>
-      </c>
-      <c r="D205" s="13" t="n">
-        <v>29279.05753409348</v>
-      </c>
-      <c r="E205" s="13" t="n">
-        <v>9954.879561591782</v>
-      </c>
-      <c r="F205" s="13" t="n">
-        <v>6427.110190410764</v>
-      </c>
-      <c r="G205" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="H205" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="I205" s="13" t="n">
-        <v>401.6469367731214</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="15" t="inlineStr">
-        <is>
-          <t>Total In</t>
-        </is>
-      </c>
-      <c r="B206" s="15" t="inlineStr"/>
-      <c r="C206" s="16" t="n">
-        <v>53372.04414818795</v>
-      </c>
-      <c r="D206" s="16" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E206" s="16" t="n">
-        <v>23716.59729564139</v>
-      </c>
-      <c r="F206" s="16" t="n">
-        <v>7310.404011594954</v>
-      </c>
-      <c r="G206" s="15" t="inlineStr"/>
-      <c r="H206" s="15" t="inlineStr"/>
-      <c r="I206" s="15" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="15" t="inlineStr">
-        <is>
-          <t>Total Out</t>
-        </is>
-      </c>
-      <c r="B207" s="15" t="inlineStr"/>
-      <c r="C207" s="16" t="n">
-        <v>53372.04414818795</v>
-      </c>
-      <c r="D207" s="16" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E207" s="16" t="n">
-        <v>23716.59729564139</v>
-      </c>
-      <c r="F207" s="16" t="n">
-        <v>7310.404011594954</v>
-      </c>
-      <c r="G207" s="15" t="inlineStr"/>
-      <c r="H207" s="15" t="inlineStr"/>
-      <c r="I207" s="15" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B208" s="15" t="inlineStr"/>
-      <c r="C208" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D208" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E208" s="16" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="F208" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" s="15" t="inlineStr"/>
-      <c r="H208" s="15" t="inlineStr"/>
-      <c r="I208" s="15" t="inlineStr"/>
-    </row>
-    <row r="210" ht="17" customHeight="1">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>PAN VAPOR CONDENSERS  (one per pan)</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="n"/>
-      <c r="C210" s="5" t="n"/>
-      <c r="D210" s="5" t="n"/>
-      <c r="E210" s="5" t="n"/>
-      <c r="F210" s="5" t="n"/>
-      <c r="G210" s="5" t="n"/>
-      <c r="H210" s="5" t="n"/>
-      <c r="I210" s="5" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>Condenser</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>Vapor (lb/hr)</t>
-        </is>
-      </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>Sat T (°F)</t>
-        </is>
-      </c>
-      <c r="D211" s="6" t="inlineStr">
-        <is>
-          <t>h_fg (BTU/lb)</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>Heat (MM BTU/hr)</t>
-        </is>
-      </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>Inj Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G211" s="6" t="inlineStr">
-        <is>
-          <t>Inj Water (GPM)</t>
-        </is>
-      </c>
-      <c r="H211" s="6" t="inlineStr">
-        <is>
-          <t>Water Out (°F)</t>
-        </is>
-      </c>
-      <c r="I211" s="6" t="inlineStr">
-        <is>
-          <t>Total Out (lb/hr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="8" t="inlineStr">
-        <is>
-          <t>A Pans</t>
-        </is>
-      </c>
-      <c r="B212" s="9" t="n">
-        <v>60869.76880576191</v>
-      </c>
-      <c r="C212" s="10" t="n">
-        <v>143.355890609762</v>
-      </c>
-      <c r="D212" s="10" t="n">
-        <v>1011.249247318053</v>
-      </c>
-      <c r="E212" s="22" t="n">
-        <v>61.55450788925062</v>
-      </c>
-      <c r="F212" s="9" t="n">
-        <v>1153659.084044764</v>
-      </c>
-      <c r="G212" s="9" t="n">
-        <v>2305.473789058282</v>
-      </c>
-      <c r="H212" s="10" t="n">
-        <v>143.355890609762</v>
-      </c>
-      <c r="I212" s="9" t="n">
-        <v>1214528.852850526</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="12" t="inlineStr">
-        <is>
-          <t>B Pans</t>
-        </is>
-      </c>
-      <c r="B213" s="13" t="n">
-        <v>24647.61519176989</v>
-      </c>
-      <c r="C213" s="14" t="n">
-        <v>133.0828737186033</v>
-      </c>
-      <c r="D213" s="14" t="n">
-        <v>1017.228576695272</v>
-      </c>
-      <c r="E213" s="23" t="n">
-        <v>25.07225852045684</v>
-      </c>
-      <c r="F213" s="13" t="n">
-        <v>581954.1817060956</v>
-      </c>
-      <c r="G213" s="13" t="n">
-        <v>1162.977981027369</v>
-      </c>
-      <c r="H213" s="14" t="n">
-        <v>133.0828737186033</v>
-      </c>
-      <c r="I213" s="13" t="n">
-        <v>606601.7968978655</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="8" t="inlineStr">
-        <is>
-          <t>Grain Pans</t>
-        </is>
-      </c>
-      <c r="B214" s="9" t="n">
-        <v>2418.240656970975</v>
-      </c>
-      <c r="C214" s="10" t="n">
-        <v>129.059477265374</v>
-      </c>
-      <c r="D214" s="10" t="n">
-        <v>1019.563890979194</v>
-      </c>
-      <c r="E214" s="22" t="n">
-        <v>2.46555085354541</v>
-      </c>
-      <c r="F214" s="9" t="n">
-        <v>63122.98643410428</v>
-      </c>
-      <c r="G214" s="9" t="n">
-        <v>126.1450568227504</v>
-      </c>
-      <c r="H214" s="10" t="n">
-        <v>129.059477265374</v>
-      </c>
-      <c r="I214" s="9" t="n">
-        <v>65541.22709107526</v>
-      </c>
+      <c r="B214" s="15" t="inlineStr"/>
+      <c r="C214" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="15" t="inlineStr"/>
+      <c r="H214" s="15" t="inlineStr"/>
+      <c r="I214" s="15" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="12" t="inlineStr">
-        <is>
-          <t>C Pans</t>
-        </is>
-      </c>
-      <c r="B215" s="13" t="n">
-        <v>15396.38230740088</v>
-      </c>
-      <c r="C215" s="14" t="n">
-        <v>119.6832047961655</v>
-      </c>
-      <c r="D215" s="14" t="n">
-        <v>1024.996584701115</v>
-      </c>
-      <c r="E215" s="23" t="n">
-        <v>15.78123928183858</v>
-      </c>
-      <c r="F215" s="13" t="n">
-        <v>531655.506546828</v>
-      </c>
-      <c r="G215" s="13" t="n">
-        <v>1062.461044258249</v>
-      </c>
-      <c r="H215" s="14" t="n">
-        <v>119.6832047961655</v>
-      </c>
-      <c r="I215" s="13" t="n">
-        <v>547051.8888542289</v>
+      <c r="A215" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B215" s="17" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="15" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B216" s="16" t="n">
-        <v>103332.0069619037</v>
-      </c>
-      <c r="C216" s="15" t="inlineStr"/>
-      <c r="D216" s="15" t="inlineStr"/>
-      <c r="E216" s="24" t="n">
-        <v>104.8735565450914</v>
-      </c>
-      <c r="F216" s="16" t="n">
-        <v>2330391.758731792</v>
-      </c>
-      <c r="G216" s="16" t="n">
-        <v>4657.057871166651</v>
-      </c>
-      <c r="H216" s="15" t="inlineStr"/>
-      <c r="I216" s="16" t="n">
-        <v>2433723.765693695</v>
+      <c r="A216" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B216" s="20" t="n">
+        <v>29.696</v>
+      </c>
+      <c r="C216" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="17" t="inlineStr">
         <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B217" s="21" t="n">
+        <v>2929.369521103218</v>
+      </c>
+      <c r="C217" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="17" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>C PANS  [C Pans]</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>Grain Massecuite</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="n">
+        <v>8453.965458602252</v>
+      </c>
+      <c r="D221" s="9" t="n">
+        <v>7439.489603569981</v>
+      </c>
+      <c r="E221" s="9" t="n">
+        <v>4405.52202912987</v>
+      </c>
+      <c r="F221" s="9" t="n">
+        <v>1014.47585503227</v>
+      </c>
+      <c r="G221" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="H221" s="10" t="n">
+        <v>59.21806822629064</v>
+      </c>
+      <c r="I221" s="9" t="n">
+        <v>92.4361833097628</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="12" t="inlineStr">
+        <is>
+          <t>B Molasses</t>
+        </is>
+      </c>
+      <c r="B222" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C222" s="13" t="n">
+        <v>55174.50076146145</v>
+      </c>
+      <c r="D222" s="13" t="n">
+        <v>38622.15053302301</v>
+      </c>
+      <c r="E222" s="13" t="n">
+        <v>19311.07526651151</v>
+      </c>
+      <c r="F222" s="13" t="n">
+        <v>16552.35022843844</v>
+      </c>
+      <c r="G222" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="H222" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I222" s="13" t="n">
+        <v>656.5559741444433</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite Out</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D223" s="9" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E223" s="9" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F223" s="9" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G223" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H223" s="10" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I223" s="9" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="12" t="inlineStr">
+        <is>
+          <t>Evaporated Water</t>
+        </is>
+      </c>
+      <c r="B224" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C224" s="13" t="n">
+        <v>15396.38230740088</v>
+      </c>
+      <c r="D224" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="13" t="n">
+        <v>15396.38230740088</v>
+      </c>
+      <c r="G224" s="12" t="inlineStr"/>
+      <c r="H224" s="12" t="inlineStr"/>
+      <c r="I224" s="12" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B225" s="15" t="inlineStr"/>
+      <c r="C225" s="16" t="n">
+        <v>63628.4662200637</v>
+      </c>
+      <c r="D225" s="16" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E225" s="16" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F225" s="16" t="n">
+        <v>17566.82608347071</v>
+      </c>
+      <c r="G225" s="15" t="inlineStr"/>
+      <c r="H225" s="15" t="inlineStr"/>
+      <c r="I225" s="15" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B226" s="15" t="inlineStr"/>
+      <c r="C226" s="16" t="n">
+        <v>63628.4662200637</v>
+      </c>
+      <c r="D226" s="16" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E226" s="16" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F226" s="16" t="n">
+        <v>17566.82608347071</v>
+      </c>
+      <c r="G226" s="15" t="inlineStr"/>
+      <c r="H226" s="15" t="inlineStr"/>
+      <c r="I226" s="15" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B227" s="15" t="inlineStr"/>
+      <c r="C227" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="15" t="inlineStr"/>
+      <c r="H227" s="15" t="inlineStr"/>
+      <c r="I227" s="15" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B228" s="17" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B229" s="20" t="n">
+        <v>21.696</v>
+      </c>
+      <c r="C229" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B230" s="21" t="n">
+        <v>18016.87108692931</v>
+      </c>
+      <c r="C230" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="17" customHeight="1">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>C CRYSTALLIZERS  [C Crystallizers]</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite In  (T=173.0 °F)</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D234" s="9" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E234" s="9" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F234" s="9" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G234" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H234" s="10" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I234" s="9" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out  (T=120.0 °F)</t>
+        </is>
+      </c>
+      <c r="B235" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C235" s="13" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D235" s="13" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E235" s="13" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F235" s="13" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G235" s="14" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H235" s="14" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I235" s="13" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="17" t="inlineStr">
+        <is>
+          <t>ML purity in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B236" s="17" t="inlineStr">
+        <is>
+          <t>33.0 -&gt; 30.0</t>
+        </is>
+      </c>
+      <c r="C236" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="17" t="inlineStr">
+        <is>
+          <t>Crystal content in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B237" s="17" t="inlineStr">
+        <is>
+          <t>26.4 -&gt; 29.3</t>
+        </is>
+      </c>
+      <c r="C237" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="17" t="inlineStr">
+        <is>
+          <t>Duty</t>
+        </is>
+      </c>
+      <c r="B238" s="21" t="n">
+        <v>1165803.366111661</v>
+      </c>
+      <c r="C238" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="17" t="inlineStr">
+        <is>
+          <t>Cooling Water</t>
+        </is>
+      </c>
+      <c r="B239" s="21" t="n">
+        <v>58290.16830558303</v>
+      </c>
+      <c r="C239" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr  (116 gpm, 85 -&gt; 105 °F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="17" customHeight="1">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>C REHEATERS  [C Reheaters]</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="5" t="n"/>
+      <c r="I241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I242" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite In  (T=120.0 °F)</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C243" s="9" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D243" s="9" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E243" s="9" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F243" s="9" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G243" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H243" s="10" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I243" s="9" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out  (T=130.0 °F)</t>
+        </is>
+      </c>
+      <c r="B244" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C244" s="13" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D244" s="13" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E244" s="13" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F244" s="13" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G244" s="14" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H244" s="14" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I244" s="13" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="17" t="inlineStr">
+        <is>
+          <t>ML purity in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B245" s="17" t="inlineStr">
+        <is>
+          <t>30.0 -&gt; 30.0</t>
+        </is>
+      </c>
+      <c r="C245" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="17" t="inlineStr">
+        <is>
+          <t>Crystal content in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B246" s="17" t="inlineStr">
+        <is>
+          <t>29.3 -&gt; 29.3</t>
+        </is>
+      </c>
+      <c r="C246" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t>Duty</t>
+        </is>
+      </c>
+      <c r="B247" s="21" t="n">
+        <v>220059.8474932024</v>
+      </c>
+      <c r="C247" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="17" t="inlineStr">
+        <is>
+          <t>Hot Water</t>
+        </is>
+      </c>
+      <c r="B248" s="21" t="n">
+        <v>14670.65649954683</v>
+      </c>
+      <c r="C248" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr  (29 gpm, 150 -&gt; 135 °F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="17" customHeight="1">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>C CENTRIFUGALS  [C Centrifugals]</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D251" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G251" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H251" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I251" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C252" s="9" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D252" s="9" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E252" s="9" t="n">
+        <v>23716.59729564139</v>
+      </c>
+      <c r="F252" s="9" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G252" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H252" s="10" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I252" s="9" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="12" t="inlineStr">
+        <is>
+          <t>Wash Water</t>
+        </is>
+      </c>
+      <c r="B253" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C253" s="13" t="n">
+        <v>5139.960235525126</v>
+      </c>
+      <c r="D253" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="13" t="n">
+        <v>5139.960235525126</v>
+      </c>
+      <c r="G253" s="12" t="inlineStr"/>
+      <c r="H253" s="12" t="inlineStr"/>
+      <c r="I253" s="12" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="8" t="inlineStr">
+        <is>
+          <t>Sugar Out</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C254" s="9" t="n">
+        <v>17665.8764236837</v>
+      </c>
+      <c r="D254" s="9" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E254" s="9" t="n">
+        <v>13761.71773404961</v>
+      </c>
+      <c r="F254" s="9" t="n">
+        <v>883.2938211841865</v>
+      </c>
+      <c r="G254" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H254" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I254" s="9" t="n">
+        <v>186.8514132326083</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="12" t="inlineStr">
+        <is>
+          <t>Molasses Out</t>
+        </is>
+      </c>
+      <c r="B255" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C255" s="13" t="n">
+        <v>35706.16772450424</v>
+      </c>
+      <c r="D255" s="13" t="n">
+        <v>29279.05753409348</v>
+      </c>
+      <c r="E255" s="13" t="n">
+        <v>9954.879561591782</v>
+      </c>
+      <c r="F255" s="13" t="n">
+        <v>6427.110190410764</v>
+      </c>
+      <c r="G255" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="H255" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I255" s="13" t="n">
+        <v>401.6469367731214</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B256" s="15" t="inlineStr"/>
+      <c r="C256" s="16" t="n">
+        <v>53372.04414818795</v>
+      </c>
+      <c r="D256" s="16" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E256" s="16" t="n">
+        <v>23716.59729564139</v>
+      </c>
+      <c r="F256" s="16" t="n">
+        <v>7310.404011594954</v>
+      </c>
+      <c r="G256" s="15" t="inlineStr"/>
+      <c r="H256" s="15" t="inlineStr"/>
+      <c r="I256" s="15" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B257" s="15" t="inlineStr"/>
+      <c r="C257" s="16" t="n">
+        <v>53372.04414818795</v>
+      </c>
+      <c r="D257" s="16" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E257" s="16" t="n">
+        <v>23716.59729564139</v>
+      </c>
+      <c r="F257" s="16" t="n">
+        <v>7310.404011594954</v>
+      </c>
+      <c r="G257" s="15" t="inlineStr"/>
+      <c r="H257" s="15" t="inlineStr"/>
+      <c r="I257" s="15" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B258" s="15" t="inlineStr"/>
+      <c r="C258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" s="16" t="n">
+        <v>-3.637978807091713e-12</v>
+      </c>
+      <c r="F258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="15" t="inlineStr"/>
+      <c r="H258" s="15" t="inlineStr"/>
+      <c r="I258" s="15" t="inlineStr"/>
+    </row>
+    <row r="260" ht="17" customHeight="1">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>C MAGMA  (mingler target 92.0 Bx)</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D261" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E261" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G261" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I261" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
+        <is>
+          <t>C Sugar</t>
+        </is>
+      </c>
+      <c r="B262" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="n">
+        <v>17665.8764236837</v>
+      </c>
+      <c r="D262" s="9" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E262" s="9" t="n">
+        <v>13761.71773404961</v>
+      </c>
+      <c r="F262" s="9" t="n">
+        <v>883.2938211841865</v>
+      </c>
+      <c r="G262" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H262" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I262" s="9" t="n">
+        <v>186.8514132326083</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
+        <is>
+          <t>Mingler Water</t>
+        </is>
+      </c>
+      <c r="B263" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C263" s="13" t="n">
+        <v>576.0611877288138</v>
+      </c>
+      <c r="D263" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="13" t="n">
+        <v>576.0611877288138</v>
+      </c>
+      <c r="G263" s="12" t="inlineStr"/>
+      <c r="H263" s="12" t="inlineStr"/>
+      <c r="I263" s="12" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>C Magma</t>
+        </is>
+      </c>
+      <c r="B264" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="n">
+        <v>18241.93761141252</v>
+      </c>
+      <c r="D264" s="9" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E264" s="9" t="n">
+        <v>13761.7177340496</v>
+      </c>
+      <c r="F264" s="9" t="n">
+        <v>1459.355008913</v>
+      </c>
+      <c r="G264" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H264" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I264" s="9" t="n">
+        <v>195.7115313137704</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B265" s="15" t="inlineStr"/>
+      <c r="C265" s="16" t="n">
+        <v>18241.93761141252</v>
+      </c>
+      <c r="D265" s="16" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E265" s="16" t="n">
+        <v>13761.71773404961</v>
+      </c>
+      <c r="F265" s="16" t="n">
+        <v>1459.355008913</v>
+      </c>
+      <c r="G265" s="15" t="inlineStr"/>
+      <c r="H265" s="15" t="inlineStr"/>
+      <c r="I265" s="15" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B266" s="15" t="inlineStr"/>
+      <c r="C266" s="16" t="n">
+        <v>18241.93761141252</v>
+      </c>
+      <c r="D266" s="16" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E266" s="16" t="n">
+        <v>13761.7177340496</v>
+      </c>
+      <c r="F266" s="16" t="n">
+        <v>1459.355008913</v>
+      </c>
+      <c r="G266" s="15" t="inlineStr"/>
+      <c r="H266" s="15" t="inlineStr"/>
+      <c r="I266" s="15" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B267" s="15" t="inlineStr"/>
+      <c r="C267" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" s="16" t="n">
+        <v>5.456968210637569e-12</v>
+      </c>
+      <c r="F267" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="15" t="inlineStr"/>
+      <c r="H267" s="15" t="inlineStr"/>
+      <c r="I267" s="15" t="inlineStr"/>
+    </row>
+    <row r="269" ht="17" customHeight="1">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>C MAGMA DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E270" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H270" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I270" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>Magma (total)</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="n">
+        <v>18241.93761141252</v>
+      </c>
+      <c r="D271" s="9" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E271" s="9" t="n">
+        <v>13761.7177340496</v>
+      </c>
+      <c r="F271" s="9" t="n">
+        <v>1459.355008913</v>
+      </c>
+      <c r="G271" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H271" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I271" s="9" t="n">
+        <v>195.7115313137704</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="12" t="inlineStr">
+        <is>
+          <t>C Magma to B Footing</t>
+        </is>
+      </c>
+      <c r="B272" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C272" s="13" t="n">
+        <v>14593.55008913001</v>
+      </c>
+      <c r="D272" s="13" t="n">
+        <v>13426.06608199961</v>
+      </c>
+      <c r="E272" s="13" t="n">
+        <v>11009.37418723968</v>
+      </c>
+      <c r="F272" s="13" t="n">
+        <v>1167.484007130401</v>
+      </c>
+      <c r="G272" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="H272" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="I272" s="13" t="n">
+        <v>156.5692250510163</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>C Magma to Remelt</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C273" s="9" t="n">
+        <v>3648.387522282503</v>
+      </c>
+      <c r="D273" s="9" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E273" s="9" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F273" s="9" t="n">
+        <v>291.8710017826002</v>
+      </c>
+      <c r="G273" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H273" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I273" s="9" t="n">
+        <v>39.14230626275408</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B274" s="15" t="inlineStr"/>
+      <c r="C274" s="16" t="n">
+        <v>18241.93761141252</v>
+      </c>
+      <c r="D274" s="16" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E274" s="16" t="n">
+        <v>13761.7177340496</v>
+      </c>
+      <c r="F274" s="16" t="n">
+        <v>1459.355008913</v>
+      </c>
+      <c r="G274" s="15" t="inlineStr"/>
+      <c r="H274" s="15" t="inlineStr"/>
+      <c r="I274" s="15" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B275" s="15" t="inlineStr"/>
+      <c r="C275" s="16" t="n">
+        <v>18241.93761141252</v>
+      </c>
+      <c r="D275" s="16" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E275" s="16" t="n">
+        <v>13761.7177340496</v>
+      </c>
+      <c r="F275" s="16" t="n">
+        <v>1459.355008913</v>
+      </c>
+      <c r="G275" s="15" t="inlineStr"/>
+      <c r="H275" s="15" t="inlineStr"/>
+      <c r="I275" s="15" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B276" s="15" t="inlineStr"/>
+      <c r="C276" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="15" t="inlineStr"/>
+      <c r="H276" s="15" t="inlineStr"/>
+      <c r="I276" s="15" t="inlineStr"/>
+    </row>
+    <row r="278" ht="17" customHeight="1">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>C REMELT  (target 65.0 Bx)</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C279" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D279" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E279" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F279" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G279" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H279" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I279" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="8" t="inlineStr">
+        <is>
+          <t>C Magma (to Remelt)</t>
+        </is>
+      </c>
+      <c r="B280" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C280" s="9" t="n">
+        <v>3648.387522282503</v>
+      </c>
+      <c r="D280" s="9" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E280" s="9" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F280" s="9" t="n">
+        <v>291.8710017826002</v>
+      </c>
+      <c r="G280" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="H280" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I280" s="9" t="n">
+        <v>39.14230626275408</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="12" t="inlineStr">
+        <is>
+          <t>Remelt Water</t>
+        </is>
+      </c>
+      <c r="B281" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C281" s="13" t="n">
+        <v>1515.484047717348</v>
+      </c>
+      <c r="D281" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="13" t="n">
+        <v>1515.484047717348</v>
+      </c>
+      <c r="G281" s="12" t="inlineStr"/>
+      <c r="H281" s="12" t="inlineStr"/>
+      <c r="I281" s="12" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="8" t="inlineStr">
+        <is>
+          <t>C Remelt</t>
+        </is>
+      </c>
+      <c r="B282" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C282" s="9" t="n">
+        <v>5163.871569999851</v>
+      </c>
+      <c r="D282" s="9" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E282" s="9" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F282" s="9" t="n">
+        <v>1807.355049499949</v>
+      </c>
+      <c r="G282" s="10" t="n">
+        <v>64.99999999999999</v>
+      </c>
+      <c r="H282" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I282" s="9" t="n">
+        <v>62.88892869832576</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B283" s="15" t="inlineStr"/>
+      <c r="C283" s="16" t="n">
+        <v>5163.871569999851</v>
+      </c>
+      <c r="D283" s="16" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E283" s="16" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F283" s="16" t="n">
+        <v>1807.355049499948</v>
+      </c>
+      <c r="G283" s="15" t="inlineStr"/>
+      <c r="H283" s="15" t="inlineStr"/>
+      <c r="I283" s="15" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B284" s="15" t="inlineStr"/>
+      <c r="C284" s="16" t="n">
+        <v>5163.871569999851</v>
+      </c>
+      <c r="D284" s="16" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E284" s="16" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F284" s="16" t="n">
+        <v>1807.355049499949</v>
+      </c>
+      <c r="G284" s="15" t="inlineStr"/>
+      <c r="H284" s="15" t="inlineStr"/>
+      <c r="I284" s="15" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B285" s="15" t="inlineStr"/>
+      <c r="C285" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" s="16" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="E285" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="16" t="n">
+        <v>-4.547473508864641e-13</v>
+      </c>
+      <c r="G285" s="15" t="inlineStr"/>
+      <c r="H285" s="15" t="inlineStr"/>
+      <c r="I285" s="15" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="17" t="inlineStr">
+        <is>
+          <t>Target remelt brix</t>
+        </is>
+      </c>
+      <c r="B286" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="C286" s="19" t="inlineStr">
+        <is>
+          <t>Bx</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="17" customHeight="1">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>PAN VAPOR CONDENSERS  (one per pan)</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="5" t="n"/>
+      <c r="I288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>Condenser</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>Vapor (lb/hr)</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>Sat T (°F)</t>
+        </is>
+      </c>
+      <c r="D289" s="6" t="inlineStr">
+        <is>
+          <t>h_fg (BTU/lb)</t>
+        </is>
+      </c>
+      <c r="E289" s="6" t="inlineStr">
+        <is>
+          <t>Heat (MM BTU/hr)</t>
+        </is>
+      </c>
+      <c r="F289" s="6" t="inlineStr">
+        <is>
+          <t>Inj Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G289" s="6" t="inlineStr">
+        <is>
+          <t>Inj Water (GPM)</t>
+        </is>
+      </c>
+      <c r="H289" s="6" t="inlineStr">
+        <is>
+          <t>Water Out (°F)</t>
+        </is>
+      </c>
+      <c r="I289" s="6" t="inlineStr">
+        <is>
+          <t>Total Out (lb/hr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>A Pans</t>
+        </is>
+      </c>
+      <c r="B290" s="9" t="n">
+        <v>60869.76880576191</v>
+      </c>
+      <c r="C290" s="10" t="n">
+        <v>143.355890609762</v>
+      </c>
+      <c r="D290" s="10" t="n">
+        <v>1011.249247318053</v>
+      </c>
+      <c r="E290" s="23" t="n">
+        <v>61.85885673327943</v>
+      </c>
+      <c r="F290" s="9" t="n">
+        <v>1279241.390309365</v>
+      </c>
+      <c r="G290" s="9" t="n">
+        <v>2556.437630514318</v>
+      </c>
+      <c r="H290" s="10" t="n">
+        <v>138.355890609762</v>
+      </c>
+      <c r="I290" s="9" t="n">
+        <v>1340111.159115126</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="12" t="inlineStr">
+        <is>
+          <t>B Pans</t>
+        </is>
+      </c>
+      <c r="B291" s="13" t="n">
+        <v>24647.61519176989</v>
+      </c>
+      <c r="C291" s="14" t="n">
+        <v>133.0828737186033</v>
+      </c>
+      <c r="D291" s="14" t="n">
+        <v>1017.228576695272</v>
+      </c>
+      <c r="E291" s="24" t="n">
+        <v>25.19549659641569</v>
+      </c>
+      <c r="F291" s="13" t="n">
+        <v>661596.5166543564</v>
+      </c>
+      <c r="G291" s="13" t="n">
+        <v>1322.135325048674</v>
+      </c>
+      <c r="H291" s="14" t="n">
+        <v>128.0828737186033</v>
+      </c>
+      <c r="I291" s="13" t="n">
+        <v>686244.1318461263</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>Grain Pans</t>
+        </is>
+      </c>
+      <c r="B292" s="9" t="n">
+        <v>2418.240656970975</v>
+      </c>
+      <c r="C292" s="10" t="n">
+        <v>129.059477265374</v>
+      </c>
+      <c r="D292" s="10" t="n">
+        <v>1019.563890979194</v>
+      </c>
+      <c r="E292" s="23" t="n">
+        <v>2.477642056830265</v>
+      </c>
+      <c r="F292" s="9" t="n">
+        <v>72744.5708436963</v>
+      </c>
+      <c r="G292" s="9" t="n">
+        <v>145.3728434126625</v>
+      </c>
+      <c r="H292" s="10" t="n">
+        <v>124.059477265374</v>
+      </c>
+      <c r="I292" s="9" t="n">
+        <v>75162.81150066727</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="12" t="inlineStr">
+        <is>
+          <t>C Pans</t>
+        </is>
+      </c>
+      <c r="B293" s="13" t="n">
+        <v>15396.38230740088</v>
+      </c>
+      <c r="C293" s="14" t="n">
+        <v>119.6832047961655</v>
+      </c>
+      <c r="D293" s="14" t="n">
+        <v>1024.996584701115</v>
+      </c>
+      <c r="E293" s="24" t="n">
+        <v>15.85822119337558</v>
+      </c>
+      <c r="F293" s="13" t="n">
+        <v>642470.1056582071</v>
+      </c>
+      <c r="G293" s="13" t="n">
+        <v>1283.913080851733</v>
+      </c>
+      <c r="H293" s="14" t="n">
+        <v>114.6832047961655</v>
+      </c>
+      <c r="I293" s="13" t="n">
+        <v>657866.487965608</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="15" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B294" s="16" t="n">
+        <v>103332.0069619037</v>
+      </c>
+      <c r="C294" s="15" t="inlineStr"/>
+      <c r="D294" s="15" t="inlineStr"/>
+      <c r="E294" s="25" t="n">
+        <v>105.390216579901</v>
+      </c>
+      <c r="F294" s="16" t="n">
+        <v>2656052.583465625</v>
+      </c>
+      <c r="G294" s="16" t="n">
+        <v>5307.858879827387</v>
+      </c>
+      <c r="H294" s="15" t="inlineStr"/>
+      <c r="I294" s="16" t="n">
+        <v>2759384.590427528</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="17" t="inlineStr">
+        <is>
           <t>Injection water supply temp</t>
         </is>
       </c>
-      <c r="B217" s="25" t="n">
+      <c r="B295" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="C217" s="19" t="inlineStr">
+      <c r="C295" s="19" t="inlineStr">
         <is>
           <t>°F</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="17" t="inlineStr">
+    <row r="296">
+      <c r="A296" s="26" t="inlineStr">
         <is>
           <t>Note: if using CoolingTowerSystem, ignore these injection water demands - they are re-solved there at the delivered water temp.</t>
         </is>
       </c>
-      <c r="B218" s="20" t="inlineStr"/>
+      <c r="B296" s="17" t="inlineStr"/>
+    </row>
+    <row r="298" ht="17" customHeight="1">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>CONDENSATE RETURN</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="5" t="n"/>
+      <c r="I298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="17" t="inlineStr">
+        <is>
+          <t>Clean condensate (Exhaust steam pans)</t>
+        </is>
+      </c>
+      <c r="B299" s="21" t="n">
+        <v>117180.8790713368</v>
+      </c>
+      <c r="C299" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="17" t="inlineStr">
+        <is>
+          <t>Dirty condensate (V1-V4 steam pans)</t>
+        </is>
+      </c>
+      <c r="B300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C300" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="17" t="inlineStr">
+        <is>
+          <t>Total condensate</t>
+        </is>
+      </c>
+      <c r="B301" s="21" t="n">
+        <v>117180.8790713368</v>
+      </c>
+      <c r="C301" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A191:I191"/>
+  <mergeCells count="26">
+    <mergeCell ref="A196:I196"/>
     <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A177:I177"/>
+    <mergeCell ref="A158:I158"/>
+    <mergeCell ref="A136:I136"/>
+    <mergeCell ref="A145:I145"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A113:I113"/>
-    <mergeCell ref="A142:I142"/>
-    <mergeCell ref="A152:I152"/>
+    <mergeCell ref="A298:I298"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A161:I161"/>
-    <mergeCell ref="A172:I172"/>
-    <mergeCell ref="A123:I123"/>
-    <mergeCell ref="A182:I182"/>
+    <mergeCell ref="A269:I269"/>
+    <mergeCell ref="A278:I278"/>
+    <mergeCell ref="A219:I219"/>
+    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A112:I112"/>
+    <mergeCell ref="A288:I288"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A232:I232"/>
+    <mergeCell ref="A186:I186"/>
+    <mergeCell ref="A260:I260"/>
+    <mergeCell ref="A250:I250"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A132:I132"/>
-    <mergeCell ref="A200:I200"/>
-    <mergeCell ref="A210:I210"/>
-    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A241:I241"/>
+    <mergeCell ref="A168:I168"/>
+    <mergeCell ref="A205:I205"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="42" min="0" max="16383" man="1"/>
+    <brk id="70" min="0" max="16383" man="1"/>
+    <brk id="110" min="0" max="16383" man="1"/>
+    <brk id="203" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/three_boiling.xlsx
+++ b/three_boiling.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.71428571428572" customWidth="1" min="1" max="1"/>
@@ -2239,4214 +2239,4394 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>Heating surface</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="n">
+        <v>22500</v>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>ft²</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>dT (calandria - masse)</t>
+        </is>
+      </c>
+      <c r="B126" s="22" t="n">
+        <v>49.61793058241602</v>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>Overall U (back-calc)</t>
+        </is>
+      </c>
+      <c r="B127" s="22" t="n">
+        <v>59.77441617197176</v>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr·ft²·°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="17" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>A CENTRIFUGALS  [A Centrifugals]</t>
         </is>
       </c>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="5" t="n"/>
-      <c r="D126" s="5" t="n"/>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="5" t="n"/>
-      <c r="I126" s="5" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="5" t="n"/>
+      <c r="I129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G127" s="6" t="inlineStr">
+      <c r="G130" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="H130" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
+      <c r="I130" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C128" s="9" t="n">
+      <c r="C131" s="9" t="n">
         <v>149081.7758328002</v>
       </c>
-      <c r="D128" s="9" t="n">
+      <c r="D131" s="9" t="n">
         <v>137155.2337661762</v>
       </c>
-      <c r="E128" s="9" t="n">
+      <c r="E131" s="9" t="n">
         <v>114250.127609357</v>
       </c>
-      <c r="F128" s="9" t="n">
+      <c r="F131" s="9" t="n">
         <v>11926.54206662401</v>
       </c>
-      <c r="G128" s="10" t="n">
+      <c r="G131" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H128" s="10" t="n">
+      <c r="H131" s="10" t="n">
         <v>83.29986721770452</v>
       </c>
-      <c r="I128" s="9" t="n">
+      <c r="I131" s="9" t="n">
         <v>1599.447562026517</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="12" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C129" s="13" t="n">
+      <c r="C132" s="13" t="n">
         <v>3310.247653066006</v>
       </c>
-      <c r="D129" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="13" t="n">
+      <c r="D132" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="13" t="n">
         <v>3310.247653066006</v>
       </c>
-      <c r="G129" s="12" t="inlineStr"/>
-      <c r="H129" s="12" t="inlineStr"/>
-      <c r="I129" s="12" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
+      <c r="G132" s="12" t="inlineStr"/>
+      <c r="H132" s="12" t="inlineStr"/>
+      <c r="I132" s="12" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C130" s="9" t="n">
+      <c r="C133" s="9" t="n">
         <v>68504.35116722419</v>
       </c>
-      <c r="D130" s="9" t="n">
+      <c r="D133" s="9" t="n">
         <v>68367.34246488973</v>
       </c>
-      <c r="E130" s="9" t="n">
+      <c r="E133" s="9" t="n">
         <v>68162.24043749507</v>
       </c>
-      <c r="F130" s="9" t="n">
+      <c r="F133" s="9" t="n">
         <v>137.0087023344531</v>
       </c>
-      <c r="G130" s="10" t="n">
+      <c r="G133" s="10" t="n">
         <v>99.8</v>
       </c>
-      <c r="H130" s="10" t="n">
+      <c r="H133" s="10" t="n">
         <v>99.7</v>
       </c>
-      <c r="I130" s="9" t="n">
+      <c r="I133" s="9" t="n">
         <v>708.2387381611449</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="12" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
+      <c r="B134" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C131" s="13" t="n">
+      <c r="C134" s="13" t="n">
         <v>83887.67231864198</v>
       </c>
-      <c r="D131" s="13" t="n">
+      <c r="D134" s="13" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E131" s="13" t="n">
+      <c r="E134" s="13" t="n">
         <v>46087.8871718619</v>
       </c>
-      <c r="F131" s="13" t="n">
+      <c r="F134" s="13" t="n">
         <v>15099.78101735556</v>
       </c>
-      <c r="G131" s="14" t="n">
+      <c r="G134" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H131" s="14" t="n">
+      <c r="H134" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="I131" s="13" t="n">
+      <c r="I134" s="13" t="n">
         <v>943.6248347841348</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="15" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B132" s="15" t="inlineStr"/>
-      <c r="C132" s="16" t="n">
+      <c r="B135" s="15" t="inlineStr"/>
+      <c r="C135" s="16" t="n">
         <v>152392.0234858662</v>
       </c>
-      <c r="D132" s="16" t="n">
+      <c r="D135" s="16" t="n">
         <v>137155.2337661762</v>
       </c>
-      <c r="E132" s="16" t="n">
+      <c r="E135" s="16" t="n">
         <v>114250.127609357</v>
       </c>
-      <c r="F132" s="16" t="n">
+      <c r="F135" s="16" t="n">
         <v>15236.78971969002</v>
       </c>
-      <c r="G132" s="15" t="inlineStr"/>
-      <c r="H132" s="15" t="inlineStr"/>
-      <c r="I132" s="15" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="15" t="inlineStr">
+      <c r="G135" s="15" t="inlineStr"/>
+      <c r="H135" s="15" t="inlineStr"/>
+      <c r="I135" s="15" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B133" s="15" t="inlineStr"/>
-      <c r="C133" s="16" t="n">
+      <c r="B136" s="15" t="inlineStr"/>
+      <c r="C136" s="16" t="n">
         <v>152392.0234858662</v>
       </c>
-      <c r="D133" s="16" t="n">
+      <c r="D136" s="16" t="n">
         <v>137155.2337661762</v>
       </c>
-      <c r="E133" s="16" t="n">
+      <c r="E136" s="16" t="n">
         <v>114250.127609357</v>
       </c>
-      <c r="F133" s="16" t="n">
+      <c r="F136" s="16" t="n">
         <v>15236.78971969002</v>
       </c>
-      <c r="G133" s="15" t="inlineStr"/>
-      <c r="H133" s="15" t="inlineStr"/>
-      <c r="I133" s="15" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
+      <c r="G136" s="15" t="inlineStr"/>
+      <c r="H136" s="15" t="inlineStr"/>
+      <c r="I136" s="15" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B134" s="15" t="inlineStr"/>
-      <c r="C134" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="16" t="n">
+      <c r="B137" s="15" t="inlineStr"/>
+      <c r="C137" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="16" t="n">
         <v>-1.455191522836685e-11</v>
       </c>
-      <c r="F134" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="15" t="inlineStr"/>
-      <c r="H134" s="15" t="inlineStr"/>
-      <c r="I134" s="15" t="inlineStr"/>
-    </row>
-    <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="F137" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="15" t="inlineStr"/>
+      <c r="H137" s="15" t="inlineStr"/>
+      <c r="I137" s="15" t="inlineStr"/>
+    </row>
+    <row r="139" ht="17" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>A MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="n"/>
-      <c r="E136" s="5" t="n"/>
-      <c r="F136" s="5" t="n"/>
-      <c r="G136" s="5" t="n"/>
-      <c r="H136" s="5" t="n"/>
-      <c r="I136" s="5" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="5" t="n"/>
+      <c r="I139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D140" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E140" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
+      <c r="G140" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="H140" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I137" s="6" t="inlineStr">
+      <c r="I140" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>A Molasses (undiluted)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C138" s="9" t="n">
+      <c r="C141" s="9" t="n">
         <v>83887.67231864198</v>
       </c>
-      <c r="D138" s="9" t="n">
+      <c r="D141" s="9" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E138" s="9" t="n">
+      <c r="E141" s="9" t="n">
         <v>46087.8871718619</v>
       </c>
-      <c r="F138" s="9" t="n">
+      <c r="F141" s="9" t="n">
         <v>15099.78101735556</v>
       </c>
-      <c r="G138" s="10" t="n">
+      <c r="G141" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H138" s="10" t="n">
+      <c r="H141" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="I138" s="9" t="n">
+      <c r="I141" s="9" t="n">
         <v>943.6248347841348</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="12" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="12" t="inlineStr">
         <is>
           <t>Dilution Water</t>
         </is>
       </c>
-      <c r="B139" s="12" t="inlineStr">
+      <c r="B142" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C139" s="13" t="n">
+      <c r="C142" s="13" t="n">
         <v>14380.74382605292</v>
       </c>
-      <c r="D139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="13" t="n">
+      <c r="D142" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="13" t="n">
         <v>14380.74382605292</v>
       </c>
-      <c r="G139" s="12" t="inlineStr"/>
-      <c r="H139" s="12" t="inlineStr"/>
-      <c r="I139" s="12" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="G142" s="12" t="inlineStr"/>
+      <c r="H142" s="12" t="inlineStr"/>
+      <c r="I142" s="12" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t>A Molasses (diluted)</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C140" s="9" t="n">
+      <c r="C143" s="9" t="n">
         <v>98268.4161446949</v>
       </c>
-      <c r="D140" s="9" t="n">
+      <c r="D143" s="9" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E140" s="9" t="n">
+      <c r="E143" s="9" t="n">
         <v>46087.88717186191</v>
       </c>
-      <c r="F140" s="9" t="n">
+      <c r="F143" s="9" t="n">
         <v>29480.52484340848</v>
       </c>
-      <c r="G140" s="10" t="n">
+      <c r="G143" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H140" s="10" t="n">
+      <c r="H143" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="I140" s="9" t="n">
+      <c r="I143" s="9" t="n">
         <v>1169.357489403457</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="15" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B141" s="15" t="inlineStr"/>
-      <c r="C141" s="16" t="n">
+      <c r="B144" s="15" t="inlineStr"/>
+      <c r="C144" s="16" t="n">
         <v>98268.4161446949</v>
       </c>
-      <c r="D141" s="16" t="n">
+      <c r="D144" s="16" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E141" s="16" t="n">
+      <c r="E144" s="16" t="n">
         <v>46087.8871718619</v>
       </c>
-      <c r="F141" s="16" t="n">
+      <c r="F144" s="16" t="n">
         <v>29480.52484340848</v>
       </c>
-      <c r="G141" s="15" t="inlineStr"/>
-      <c r="H141" s="15" t="inlineStr"/>
-      <c r="I141" s="15" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="15" t="inlineStr">
+      <c r="G144" s="15" t="inlineStr"/>
+      <c r="H144" s="15" t="inlineStr"/>
+      <c r="I144" s="15" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B142" s="15" t="inlineStr"/>
-      <c r="C142" s="16" t="n">
+      <c r="B145" s="15" t="inlineStr"/>
+      <c r="C145" s="16" t="n">
         <v>98268.4161446949</v>
       </c>
-      <c r="D142" s="16" t="n">
+      <c r="D145" s="16" t="n">
         <v>68787.89130128642</v>
       </c>
-      <c r="E142" s="16" t="n">
+      <c r="E145" s="16" t="n">
         <v>46087.88717186191</v>
       </c>
-      <c r="F142" s="16" t="n">
+      <c r="F145" s="16" t="n">
         <v>29480.52484340848</v>
       </c>
-      <c r="G142" s="15" t="inlineStr"/>
-      <c r="H142" s="15" t="inlineStr"/>
-      <c r="I142" s="15" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="15" t="inlineStr">
+      <c r="G145" s="15" t="inlineStr"/>
+      <c r="H145" s="15" t="inlineStr"/>
+      <c r="I145" s="15" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B143" s="15" t="inlineStr"/>
-      <c r="C143" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="16" t="n">
+      <c r="B146" s="15" t="inlineStr"/>
+      <c r="C146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="16" t="n">
         <v>-7.275957614183426e-12</v>
       </c>
-      <c r="F143" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="15" t="inlineStr"/>
-      <c r="H143" s="15" t="inlineStr"/>
-      <c r="I143" s="15" t="inlineStr"/>
-    </row>
-    <row r="145" ht="17" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="F146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="15" t="inlineStr"/>
+      <c r="H146" s="15" t="inlineStr"/>
+      <c r="I146" s="15" t="inlineStr"/>
+    </row>
+    <row r="148" ht="17" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>B PANS  [B Pans]</t>
         </is>
       </c>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="5" t="n"/>
-      <c r="F145" s="5" t="n"/>
-      <c r="G145" s="5" t="n"/>
-      <c r="H145" s="5" t="n"/>
-      <c r="I145" s="5" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="inlineStr">
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="5" t="n"/>
+      <c r="I148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G146" s="6" t="inlineStr">
+      <c r="G149" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H146" s="6" t="inlineStr">
+      <c r="H149" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I146" s="6" t="inlineStr">
+      <c r="I149" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="8" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>C Magma</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C147" s="9" t="n">
+      <c r="C150" s="9" t="n">
         <v>14593.55008893615</v>
       </c>
-      <c r="D147" s="9" t="n">
+      <c r="D150" s="9" t="n">
         <v>13426.06608182126</v>
       </c>
-      <c r="E147" s="9" t="n">
+      <c r="E150" s="9" t="n">
         <v>11009.37418709343</v>
       </c>
-      <c r="F147" s="9" t="n">
+      <c r="F150" s="9" t="n">
         <v>1167.484007114894</v>
       </c>
-      <c r="G147" s="10" t="n">
+      <c r="G150" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H147" s="10" t="n">
+      <c r="H150" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="I147" s="9" t="n">
+      <c r="I150" s="9" t="n">
         <v>156.5692250489364</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="12" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
         <is>
           <t>A Molasses</t>
         </is>
       </c>
-      <c r="B148" s="12" t="inlineStr">
+      <c r="B151" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C148" s="13" t="n">
+      <c r="C151" s="13" t="n">
         <v>95320.36366035405</v>
       </c>
-      <c r="D148" s="13" t="n">
+      <c r="D151" s="13" t="n">
         <v>66724.25456224784</v>
       </c>
-      <c r="E148" s="13" t="n">
+      <c r="E151" s="13" t="n">
         <v>44705.25055670605</v>
       </c>
-      <c r="F148" s="13" t="n">
+      <c r="F151" s="13" t="n">
         <v>28596.10909810622</v>
       </c>
-      <c r="G148" s="14" t="n">
+      <c r="G151" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H148" s="14" t="n">
+      <c r="H151" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="I148" s="13" t="n">
+      <c r="I151" s="13" t="n">
         <v>1134.276764721353</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C149" s="9" t="n">
+      <c r="C152" s="9" t="n">
         <v>85266.29855752031</v>
       </c>
-      <c r="D149" s="9" t="n">
+      <c r="D152" s="9" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E149" s="9" t="n">
+      <c r="E152" s="9" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F149" s="9" t="n">
+      <c r="F152" s="9" t="n">
         <v>5115.977913451221</v>
       </c>
-      <c r="G149" s="10" t="n">
+      <c r="G152" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="H149" s="10" t="n">
+      <c r="H152" s="10" t="n">
         <v>69.51266607056577</v>
       </c>
-      <c r="I149" s="9" t="n">
+      <c r="I152" s="9" t="n">
         <v>906.1508352228298</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="12" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B150" s="12" t="inlineStr">
+      <c r="B153" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C150" s="13" t="n">
+      <c r="C153" s="13" t="n">
         <v>24647.61519176989</v>
       </c>
-      <c r="D150" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" s="13" t="n">
+      <c r="D153" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="13" t="n">
         <v>24647.61519176989</v>
       </c>
-      <c r="G150" s="12" t="inlineStr"/>
-      <c r="H150" s="12" t="inlineStr"/>
-      <c r="I150" s="12" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="15" t="inlineStr">
+      <c r="G153" s="12" t="inlineStr"/>
+      <c r="H153" s="12" t="inlineStr"/>
+      <c r="I153" s="12" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B151" s="15" t="inlineStr"/>
-      <c r="C151" s="16" t="n">
+      <c r="B154" s="15" t="inlineStr"/>
+      <c r="C154" s="16" t="n">
         <v>109913.9137492902</v>
       </c>
-      <c r="D151" s="16" t="n">
+      <c r="D154" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E151" s="16" t="n">
+      <c r="E154" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F151" s="16" t="n">
+      <c r="F154" s="16" t="n">
         <v>29763.59310522111</v>
       </c>
-      <c r="G151" s="15" t="inlineStr"/>
-      <c r="H151" s="15" t="inlineStr"/>
-      <c r="I151" s="15" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="15" t="inlineStr">
+      <c r="G154" s="15" t="inlineStr"/>
+      <c r="H154" s="15" t="inlineStr"/>
+      <c r="I154" s="15" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B152" s="15" t="inlineStr"/>
-      <c r="C152" s="16" t="n">
+      <c r="B155" s="15" t="inlineStr"/>
+      <c r="C155" s="16" t="n">
         <v>109913.9137492902</v>
       </c>
-      <c r="D152" s="16" t="n">
+      <c r="D155" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E152" s="16" t="n">
+      <c r="E155" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F152" s="16" t="n">
+      <c r="F155" s="16" t="n">
         <v>29763.59310522111</v>
       </c>
-      <c r="G152" s="15" t="inlineStr"/>
-      <c r="H152" s="15" t="inlineStr"/>
-      <c r="I152" s="15" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="15" t="inlineStr">
+      <c r="G155" s="15" t="inlineStr"/>
+      <c r="H155" s="15" t="inlineStr"/>
+      <c r="I155" s="15" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B153" s="15" t="inlineStr"/>
-      <c r="C153" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" s="15" t="inlineStr"/>
-      <c r="H153" s="15" t="inlineStr"/>
-      <c r="I153" s="15" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="17" t="inlineStr">
+      <c r="B156" s="15" t="inlineStr"/>
+      <c r="C156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="15" t="inlineStr"/>
+      <c r="H156" s="15" t="inlineStr"/>
+      <c r="I156" s="15" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="inlineStr">
         <is>
           <t>Calandria steam type</t>
         </is>
       </c>
-      <c r="B154" s="17" t="inlineStr">
+      <c r="B157" s="17" t="inlineStr">
         <is>
           <t>Exhaust</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="17" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
         <is>
           <t>Calandria pressure</t>
         </is>
       </c>
-      <c r="B155" s="20" t="n">
+      <c r="B158" s="20" t="n">
         <v>29.696</v>
       </c>
-      <c r="C155" s="19" t="inlineStr">
+      <c r="C158" s="19" t="inlineStr">
         <is>
           <t>psia</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="17" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="17" t="inlineStr">
         <is>
           <t>Calandria steam flow</t>
         </is>
       </c>
-      <c r="B156" s="21" t="n">
+      <c r="B159" s="21" t="n">
         <v>29613.16522157839</v>
       </c>
-      <c r="C156" s="19" t="inlineStr">
+      <c r="C159" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="17" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t>Heating surface</t>
+        </is>
+      </c>
+      <c r="B160" s="21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>ft²</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="17" t="inlineStr">
+        <is>
+          <t>dT (calandria - masse)</t>
+        </is>
+      </c>
+      <c r="B161" s="22" t="n">
+        <v>70.71991260127336</v>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t>Overall U (back-calc)</t>
+        </is>
+      </c>
+      <c r="B162" s="22" t="n">
+        <v>52.79780986234915</v>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr·ft²·°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="17" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>B CENTRIFUGALS  [B Centrifugals]</t>
         </is>
       </c>
-      <c r="B158" s="5" t="n"/>
-      <c r="C158" s="5" t="n"/>
-      <c r="D158" s="5" t="n"/>
-      <c r="E158" s="5" t="n"/>
-      <c r="F158" s="5" t="n"/>
-      <c r="G158" s="5" t="n"/>
-      <c r="H158" s="5" t="n"/>
-      <c r="I158" s="5" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="6" t="inlineStr">
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="5" t="n"/>
+      <c r="I164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
+      <c r="C165" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D165" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E165" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr">
+      <c r="G165" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="H165" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr">
+      <c r="I165" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="8" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C160" s="9" t="n">
+      <c r="C166" s="9" t="n">
         <v>85266.29855752031</v>
       </c>
-      <c r="D160" s="9" t="n">
+      <c r="D166" s="9" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E160" s="9" t="n">
+      <c r="E166" s="9" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F160" s="9" t="n">
+      <c r="F166" s="9" t="n">
         <v>5115.977913451221</v>
       </c>
-      <c r="G160" s="10" t="n">
+      <c r="G166" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="H160" s="10" t="n">
+      <c r="H166" s="10" t="n">
         <v>69.51266607056577</v>
       </c>
-      <c r="I160" s="9" t="n">
+      <c r="I166" s="9" t="n">
         <v>906.1508352228298</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="12" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B161" s="12" t="inlineStr">
+      <c r="B167" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C161" s="13" t="n">
+      <c r="C167" s="13" t="n">
         <v>6263.891436226622</v>
       </c>
-      <c r="D161" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="13" t="n">
+      <c r="D167" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="13" t="n">
         <v>6263.891436226622</v>
       </c>
-      <c r="G161" s="12" t="inlineStr"/>
-      <c r="H161" s="12" t="inlineStr"/>
-      <c r="I161" s="12" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="8" t="inlineStr">
+      <c r="G167" s="12" t="inlineStr"/>
+      <c r="H167" s="12" t="inlineStr"/>
+      <c r="I167" s="12" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C162" s="9" t="n">
+      <c r="C168" s="9" t="n">
         <v>39196.65268612767</v>
       </c>
-      <c r="D162" s="9" t="n">
+      <c r="D168" s="9" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E162" s="9" t="n">
+      <c r="E168" s="9" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F162" s="9" t="n">
+      <c r="F168" s="9" t="n">
         <v>1959.832634306382</v>
       </c>
-      <c r="G162" s="10" t="n">
+      <c r="G168" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="H162" s="10" t="n">
+      <c r="H168" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I162" s="9" t="n">
+      <c r="I168" s="9" t="n">
         <v>414.581749172197</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="12" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B163" s="12" t="inlineStr">
+      <c r="B169" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C163" s="13" t="n">
+      <c r="C169" s="13" t="n">
         <v>52333.53730761927</v>
       </c>
-      <c r="D163" s="13" t="n">
+      <c r="D169" s="13" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E163" s="13" t="n">
+      <c r="E169" s="13" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F163" s="13" t="n">
+      <c r="F169" s="13" t="n">
         <v>9420.036715371476</v>
       </c>
-      <c r="G163" s="14" t="n">
+      <c r="G169" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H163" s="14" t="n">
+      <c r="H169" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="I163" s="13" t="n">
+      <c r="I169" s="13" t="n">
         <v>588.6827483780042</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="15" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B164" s="15" t="inlineStr"/>
-      <c r="C164" s="16" t="n">
+      <c r="B170" s="15" t="inlineStr"/>
+      <c r="C170" s="16" t="n">
         <v>91530.18999374693</v>
       </c>
-      <c r="D164" s="16" t="n">
+      <c r="D170" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E164" s="16" t="n">
+      <c r="E170" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F164" s="16" t="n">
+      <c r="F170" s="16" t="n">
         <v>11379.86934967784</v>
       </c>
-      <c r="G164" s="15" t="inlineStr"/>
-      <c r="H164" s="15" t="inlineStr"/>
-      <c r="I164" s="15" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="15" t="inlineStr">
+      <c r="G170" s="15" t="inlineStr"/>
+      <c r="H170" s="15" t="inlineStr"/>
+      <c r="I170" s="15" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B165" s="15" t="inlineStr"/>
-      <c r="C165" s="16" t="n">
+      <c r="B171" s="15" t="inlineStr"/>
+      <c r="C171" s="16" t="n">
         <v>91530.18999374693</v>
       </c>
-      <c r="D165" s="16" t="n">
+      <c r="D171" s="16" t="n">
         <v>80150.32064406908</v>
       </c>
-      <c r="E165" s="16" t="n">
+      <c r="E171" s="16" t="n">
         <v>55714.62474379948</v>
       </c>
-      <c r="F165" s="16" t="n">
+      <c r="F171" s="16" t="n">
         <v>11379.86934967784</v>
       </c>
-      <c r="G165" s="15" t="inlineStr"/>
-      <c r="H165" s="15" t="inlineStr"/>
-      <c r="I165" s="15" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="15" t="inlineStr">
+      <c r="G171" s="15" t="inlineStr"/>
+      <c r="H171" s="15" t="inlineStr"/>
+      <c r="I171" s="15" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B166" s="15" t="inlineStr"/>
-      <c r="C166" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" s="16" t="n">
+      <c r="B172" s="15" t="inlineStr"/>
+      <c r="C172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="16" t="n">
         <v>7.275957614183426e-12</v>
       </c>
-      <c r="F166" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="15" t="inlineStr"/>
-      <c r="H166" s="15" t="inlineStr"/>
-      <c r="I166" s="15" t="inlineStr"/>
-    </row>
-    <row r="168" ht="17" customHeight="1">
-      <c r="A168" s="4" t="inlineStr">
+      <c r="F172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="15" t="inlineStr"/>
+      <c r="H172" s="15" t="inlineStr"/>
+      <c r="I172" s="15" t="inlineStr"/>
+    </row>
+    <row r="174" ht="17" customHeight="1">
+      <c r="A174" s="4" t="inlineStr">
         <is>
           <t>B MAGMA  (mingler target 92.0 Bx)</t>
         </is>
       </c>
-      <c r="B168" s="5" t="n"/>
-      <c r="C168" s="5" t="n"/>
-      <c r="D168" s="5" t="n"/>
-      <c r="E168" s="5" t="n"/>
-      <c r="F168" s="5" t="n"/>
-      <c r="G168" s="5" t="n"/>
-      <c r="H168" s="5" t="n"/>
-      <c r="I168" s="5" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="6" t="inlineStr">
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="5" t="n"/>
+      <c r="I174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E175" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G169" s="6" t="inlineStr">
+      <c r="G175" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H169" s="6" t="inlineStr">
+      <c r="H175" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I169" s="6" t="inlineStr">
+      <c r="I175" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="8" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>B Sugar</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C170" s="9" t="n">
+      <c r="C176" s="9" t="n">
         <v>39196.65268612767</v>
       </c>
-      <c r="D170" s="9" t="n">
+      <c r="D176" s="9" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E170" s="9" t="n">
+      <c r="E176" s="9" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F170" s="9" t="n">
+      <c r="F176" s="9" t="n">
         <v>1959.832634306382</v>
       </c>
-      <c r="G170" s="10" t="n">
+      <c r="G176" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="H170" s="10" t="n">
+      <c r="H176" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I170" s="9" t="n">
+      <c r="I176" s="9" t="n">
         <v>414.581749172197</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="12" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="12" t="inlineStr">
         <is>
           <t>Mingler Water</t>
         </is>
       </c>
-      <c r="B171" s="12" t="inlineStr">
+      <c r="B177" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C171" s="13" t="n">
+      <c r="C177" s="13" t="n">
         <v>1278.151718025903</v>
       </c>
-      <c r="D171" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="13" t="n">
+      <c r="D177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="13" t="n">
         <v>1278.151718025903</v>
       </c>
-      <c r="G171" s="12" t="inlineStr"/>
-      <c r="H171" s="12" t="inlineStr"/>
-      <c r="I171" s="12" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="8" t="inlineStr">
+      <c r="G177" s="12" t="inlineStr"/>
+      <c r="H177" s="12" t="inlineStr"/>
+      <c r="I177" s="12" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>B Magma</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C172" s="9" t="n">
+      <c r="C178" s="9" t="n">
         <v>40474.80440415357</v>
       </c>
-      <c r="D172" s="9" t="n">
+      <c r="D178" s="9" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E172" s="9" t="n">
+      <c r="E178" s="9" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F172" s="9" t="n">
+      <c r="F178" s="9" t="n">
         <v>3237.984352332285</v>
       </c>
-      <c r="G172" s="10" t="n">
+      <c r="G178" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H172" s="10" t="n">
+      <c r="H178" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I172" s="9" t="n">
+      <c r="I178" s="9" t="n">
         <v>434.2403816032381</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="15" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B173" s="15" t="inlineStr"/>
-      <c r="C173" s="16" t="n">
+      <c r="B179" s="15" t="inlineStr"/>
+      <c r="C179" s="16" t="n">
         <v>40474.80440415357</v>
       </c>
-      <c r="D173" s="16" t="n">
+      <c r="D179" s="16" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E173" s="16" t="n">
+      <c r="E179" s="16" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F173" s="16" t="n">
+      <c r="F179" s="16" t="n">
         <v>3237.984352332285</v>
       </c>
-      <c r="G173" s="15" t="inlineStr"/>
-      <c r="H173" s="15" t="inlineStr"/>
-      <c r="I173" s="15" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="15" t="inlineStr">
+      <c r="G179" s="15" t="inlineStr"/>
+      <c r="H179" s="15" t="inlineStr"/>
+      <c r="I179" s="15" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B174" s="15" t="inlineStr"/>
-      <c r="C174" s="16" t="n">
+      <c r="B180" s="15" t="inlineStr"/>
+      <c r="C180" s="16" t="n">
         <v>40474.80440415357</v>
       </c>
-      <c r="D174" s="16" t="n">
+      <c r="D180" s="16" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E174" s="16" t="n">
+      <c r="E180" s="16" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F174" s="16" t="n">
+      <c r="F180" s="16" t="n">
         <v>3237.984352332285</v>
       </c>
-      <c r="G174" s="15" t="inlineStr"/>
-      <c r="H174" s="15" t="inlineStr"/>
-      <c r="I174" s="15" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="15" t="inlineStr">
+      <c r="G180" s="15" t="inlineStr"/>
+      <c r="H180" s="15" t="inlineStr"/>
+      <c r="I180" s="15" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B175" s="15" t="inlineStr"/>
-      <c r="C175" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" s="15" t="inlineStr"/>
-      <c r="H175" s="15" t="inlineStr"/>
-      <c r="I175" s="15" t="inlineStr"/>
-    </row>
-    <row r="177" ht="17" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="B181" s="15" t="inlineStr"/>
+      <c r="C181" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="15" t="inlineStr"/>
+      <c r="H181" s="15" t="inlineStr"/>
+      <c r="I181" s="15" t="inlineStr"/>
+    </row>
+    <row r="183" ht="17" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t>B MAGMA DISTRIBUTION</t>
         </is>
       </c>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="5" t="n"/>
-      <c r="D177" s="5" t="n"/>
-      <c r="E177" s="5" t="n"/>
-      <c r="F177" s="5" t="n"/>
-      <c r="G177" s="5" t="n"/>
-      <c r="H177" s="5" t="n"/>
-      <c r="I177" s="5" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="5" t="n"/>
+      <c r="I183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E184" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G178" s="6" t="inlineStr">
+      <c r="G184" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I178" s="6" t="inlineStr">
+      <c r="I184" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t>Magma (total)</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C179" s="9" t="n">
+      <c r="C185" s="9" t="n">
         <v>40474.80440415357</v>
       </c>
-      <c r="D179" s="9" t="n">
+      <c r="D185" s="9" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E179" s="9" t="n">
+      <c r="E185" s="9" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F179" s="9" t="n">
+      <c r="F185" s="9" t="n">
         <v>3237.984352332285</v>
       </c>
-      <c r="G179" s="10" t="n">
+      <c r="G185" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H179" s="10" t="n">
+      <c r="H185" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I179" s="9" t="n">
+      <c r="I185" s="9" t="n">
         <v>434.2403816032381</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="12" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="12" t="inlineStr">
         <is>
           <t>B Magma to A Footing</t>
         </is>
       </c>
-      <c r="B180" s="12" t="inlineStr">
+      <c r="B186" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C180" s="13" t="n">
+      <c r="C186" s="13" t="n">
         <v>32379.84352332286</v>
       </c>
-      <c r="D180" s="13" t="n">
+      <c r="D186" s="13" t="n">
         <v>29789.45604145703</v>
       </c>
-      <c r="E180" s="13" t="n">
+      <c r="E186" s="13" t="n">
         <v>27406.29955814046</v>
       </c>
-      <c r="F180" s="13" t="n">
+      <c r="F186" s="13" t="n">
         <v>2590.387481865826</v>
       </c>
-      <c r="G180" s="14" t="n">
+      <c r="G186" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="H180" s="14" t="n">
+      <c r="H186" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="I180" s="13" t="n">
+      <c r="I186" s="13" t="n">
         <v>347.3923052825905</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="8" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
         <is>
           <t>B Magma to Remelt</t>
         </is>
       </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C181" s="9" t="n">
+      <c r="C187" s="9" t="n">
         <v>8094.960880830714</v>
       </c>
-      <c r="D181" s="9" t="n">
+      <c r="D187" s="9" t="n">
         <v>7447.364010364257</v>
       </c>
-      <c r="E181" s="9" t="n">
+      <c r="E187" s="9" t="n">
         <v>6851.574889535116</v>
       </c>
-      <c r="F181" s="9" t="n">
+      <c r="F187" s="9" t="n">
         <v>647.5968704664565</v>
       </c>
-      <c r="G181" s="10" t="n">
+      <c r="G187" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H181" s="10" t="n">
+      <c r="H187" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I181" s="9" t="n">
+      <c r="I187" s="9" t="n">
         <v>86.84807632064764</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="15" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B182" s="15" t="inlineStr"/>
-      <c r="C182" s="16" t="n">
+      <c r="B188" s="15" t="inlineStr"/>
+      <c r="C188" s="16" t="n">
         <v>40474.80440415357</v>
       </c>
-      <c r="D182" s="16" t="n">
+      <c r="D188" s="16" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E182" s="16" t="n">
+      <c r="E188" s="16" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F182" s="16" t="n">
+      <c r="F188" s="16" t="n">
         <v>3237.984352332285</v>
       </c>
-      <c r="G182" s="15" t="inlineStr"/>
-      <c r="H182" s="15" t="inlineStr"/>
-      <c r="I182" s="15" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="15" t="inlineStr">
+      <c r="G188" s="15" t="inlineStr"/>
+      <c r="H188" s="15" t="inlineStr"/>
+      <c r="I188" s="15" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B183" s="15" t="inlineStr"/>
-      <c r="C183" s="16" t="n">
+      <c r="B189" s="15" t="inlineStr"/>
+      <c r="C189" s="16" t="n">
         <v>40474.80440415357</v>
       </c>
-      <c r="D183" s="16" t="n">
+      <c r="D189" s="16" t="n">
         <v>37236.82005182128</v>
       </c>
-      <c r="E183" s="16" t="n">
+      <c r="E189" s="16" t="n">
         <v>34257.87444767558</v>
       </c>
-      <c r="F183" s="16" t="n">
+      <c r="F189" s="16" t="n">
         <v>3237.984352332285</v>
       </c>
-      <c r="G183" s="15" t="inlineStr"/>
-      <c r="H183" s="15" t="inlineStr"/>
-      <c r="I183" s="15" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="15" t="inlineStr">
+      <c r="G189" s="15" t="inlineStr"/>
+      <c r="H189" s="15" t="inlineStr"/>
+      <c r="I189" s="15" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B184" s="15" t="inlineStr"/>
-      <c r="C184" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" s="15" t="inlineStr"/>
-      <c r="H184" s="15" t="inlineStr"/>
-      <c r="I184" s="15" t="inlineStr"/>
-    </row>
-    <row r="186" ht="17" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
+      <c r="B190" s="15" t="inlineStr"/>
+      <c r="C190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="15" t="inlineStr"/>
+      <c r="H190" s="15" t="inlineStr"/>
+      <c r="I190" s="15" t="inlineStr"/>
+    </row>
+    <row r="192" ht="17" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>B REMELT  (target 65.0 Bx)</t>
         </is>
       </c>
-      <c r="B186" s="5" t="n"/>
-      <c r="C186" s="5" t="n"/>
-      <c r="D186" s="5" t="n"/>
-      <c r="E186" s="5" t="n"/>
-      <c r="F186" s="5" t="n"/>
-      <c r="G186" s="5" t="n"/>
-      <c r="H186" s="5" t="n"/>
-      <c r="I186" s="5" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="5" t="n"/>
+      <c r="I192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="B193" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C193" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D193" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E193" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G187" s="6" t="inlineStr">
+      <c r="G193" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="H193" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I193" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="8" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
         <is>
           <t>B Magma (to Remelt)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C188" s="9" t="n">
+      <c r="C194" s="9" t="n">
         <v>8094.960880830714</v>
       </c>
-      <c r="D188" s="9" t="n">
+      <c r="D194" s="9" t="n">
         <v>7447.364010364257</v>
       </c>
-      <c r="E188" s="9" t="n">
+      <c r="E194" s="9" t="n">
         <v>6851.574889535116</v>
       </c>
-      <c r="F188" s="9" t="n">
+      <c r="F194" s="9" t="n">
         <v>647.5968704664565</v>
       </c>
-      <c r="G188" s="10" t="n">
+      <c r="G194" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H188" s="10" t="n">
+      <c r="H194" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I188" s="9" t="n">
+      <c r="I194" s="9" t="n">
         <v>86.84807632064764</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="12" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="12" t="inlineStr">
         <is>
           <t>Remelt Water</t>
         </is>
       </c>
-      <c r="B189" s="12" t="inlineStr">
+      <c r="B195" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C189" s="13" t="n">
+      <c r="C195" s="13" t="n">
         <v>3362.522212037374</v>
       </c>
-      <c r="D189" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E189" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" s="13" t="n">
+      <c r="D195" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="13" t="n">
         <v>3362.522212037374</v>
       </c>
-      <c r="G189" s="12" t="inlineStr"/>
-      <c r="H189" s="12" t="inlineStr"/>
-      <c r="I189" s="12" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="8" t="inlineStr">
+      <c r="G195" s="12" t="inlineStr"/>
+      <c r="H195" s="12" t="inlineStr"/>
+      <c r="I195" s="12" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="inlineStr">
         <is>
           <t>B Remelt</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C190" s="9" t="n">
+      <c r="C196" s="9" t="n">
         <v>11457.48309286809</v>
       </c>
-      <c r="D190" s="9" t="n">
+      <c r="D196" s="9" t="n">
         <v>7447.364010364257</v>
       </c>
-      <c r="E190" s="9" t="n">
+      <c r="E196" s="9" t="n">
         <v>6851.574889535116</v>
       </c>
-      <c r="F190" s="9" t="n">
+      <c r="F196" s="9" t="n">
         <v>4010.11908250383</v>
       </c>
-      <c r="G190" s="10" t="n">
+      <c r="G196" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="H190" s="10" t="n">
+      <c r="H196" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I190" s="9" t="n">
+      <c r="I196" s="9" t="n">
         <v>139.5365526663698</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="15" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B191" s="15" t="inlineStr"/>
-      <c r="C191" s="16" t="n">
+      <c r="B197" s="15" t="inlineStr"/>
+      <c r="C197" s="16" t="n">
         <v>11457.48309286809</v>
       </c>
-      <c r="D191" s="16" t="n">
+      <c r="D197" s="16" t="n">
         <v>7447.364010364257</v>
       </c>
-      <c r="E191" s="16" t="n">
+      <c r="E197" s="16" t="n">
         <v>6851.574889535116</v>
       </c>
-      <c r="F191" s="16" t="n">
+      <c r="F197" s="16" t="n">
         <v>4010.11908250383</v>
       </c>
-      <c r="G191" s="15" t="inlineStr"/>
-      <c r="H191" s="15" t="inlineStr"/>
-      <c r="I191" s="15" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="15" t="inlineStr">
+      <c r="G197" s="15" t="inlineStr"/>
+      <c r="H197" s="15" t="inlineStr"/>
+      <c r="I197" s="15" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B192" s="15" t="inlineStr"/>
-      <c r="C192" s="16" t="n">
+      <c r="B198" s="15" t="inlineStr"/>
+      <c r="C198" s="16" t="n">
         <v>11457.48309286809</v>
       </c>
-      <c r="D192" s="16" t="n">
+      <c r="D198" s="16" t="n">
         <v>7447.364010364257</v>
       </c>
-      <c r="E192" s="16" t="n">
+      <c r="E198" s="16" t="n">
         <v>6851.574889535116</v>
       </c>
-      <c r="F192" s="16" t="n">
+      <c r="F198" s="16" t="n">
         <v>4010.11908250383</v>
       </c>
-      <c r="G192" s="15" t="inlineStr"/>
-      <c r="H192" s="15" t="inlineStr"/>
-      <c r="I192" s="15" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="15" t="inlineStr">
+      <c r="G198" s="15" t="inlineStr"/>
+      <c r="H198" s="15" t="inlineStr"/>
+      <c r="I198" s="15" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B193" s="15" t="inlineStr"/>
-      <c r="C193" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" s="15" t="inlineStr"/>
-      <c r="H193" s="15" t="inlineStr"/>
-      <c r="I193" s="15" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="17" t="inlineStr">
+      <c r="B199" s="15" t="inlineStr"/>
+      <c r="C199" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="15" t="inlineStr"/>
+      <c r="H199" s="15" t="inlineStr"/>
+      <c r="I199" s="15" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="17" t="inlineStr">
         <is>
           <t>Target remelt brix</t>
         </is>
       </c>
-      <c r="B194" s="22" t="n">
+      <c r="B200" s="22" t="n">
         <v>65</v>
       </c>
-      <c r="C194" s="19" t="inlineStr">
+      <c r="C200" s="19" t="inlineStr">
         <is>
           <t>Bx</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="17" customHeight="1">
-      <c r="A196" s="4" t="inlineStr">
+    <row r="202" ht="17" customHeight="1">
+      <c r="A202" s="4" t="inlineStr">
         <is>
           <t>B MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
-      <c r="E196" s="5" t="n"/>
-      <c r="F196" s="5" t="n"/>
-      <c r="G196" s="5" t="n"/>
-      <c r="H196" s="5" t="n"/>
-      <c r="I196" s="5" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="6" t="inlineStr">
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B197" s="6" t="inlineStr">
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C197" s="6" t="inlineStr">
+      <c r="C203" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D203" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E203" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G197" s="6" t="inlineStr">
+      <c r="G203" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H197" s="6" t="inlineStr">
+      <c r="H203" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I197" s="6" t="inlineStr">
+      <c r="I203" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="8" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
         <is>
           <t>B Molasses (undiluted)</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C198" s="9" t="n">
+      <c r="C204" s="9" t="n">
         <v>52333.53730761927</v>
       </c>
-      <c r="D198" s="9" t="n">
+      <c r="D204" s="9" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E198" s="9" t="n">
+      <c r="E204" s="9" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F198" s="9" t="n">
+      <c r="F204" s="9" t="n">
         <v>9420.036715371476</v>
       </c>
-      <c r="G198" s="10" t="n">
+      <c r="G204" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H198" s="10" t="n">
+      <c r="H204" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I198" s="9" t="n">
+      <c r="I204" s="9" t="n">
         <v>588.6827483780042</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="12" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="12" t="inlineStr">
         <is>
           <t>Dilution Water</t>
         </is>
       </c>
-      <c r="B199" s="12" t="inlineStr">
+      <c r="B205" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C199" s="13" t="n">
+      <c r="C205" s="13" t="n">
         <v>8971.46353844901</v>
       </c>
-      <c r="D199" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" s="13" t="n">
+      <c r="D205" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="13" t="n">
         <v>8971.46353844901</v>
       </c>
-      <c r="G199" s="12" t="inlineStr"/>
-      <c r="H199" s="12" t="inlineStr"/>
-      <c r="I199" s="12" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="8" t="inlineStr">
+      <c r="G205" s="12" t="inlineStr"/>
+      <c r="H205" s="12" t="inlineStr"/>
+      <c r="I205" s="12" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
         <is>
           <t>B Molasses (diluted)</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C200" s="9" t="n">
+      <c r="C206" s="9" t="n">
         <v>61305.00084606828</v>
       </c>
-      <c r="D200" s="9" t="n">
+      <c r="D206" s="9" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E200" s="9" t="n">
+      <c r="E206" s="9" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F200" s="9" t="n">
+      <c r="F206" s="9" t="n">
         <v>18391.50025382049</v>
       </c>
-      <c r="G200" s="10" t="n">
+      <c r="G206" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H200" s="10" t="n">
+      <c r="H206" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I200" s="9" t="n">
+      <c r="I206" s="9" t="n">
         <v>729.5066379382704</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="15" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B201" s="15" t="inlineStr"/>
-      <c r="C201" s="16" t="n">
+      <c r="B207" s="15" t="inlineStr"/>
+      <c r="C207" s="16" t="n">
         <v>61305.00084606828</v>
       </c>
-      <c r="D201" s="16" t="n">
+      <c r="D207" s="16" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E201" s="16" t="n">
+      <c r="E207" s="16" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F201" s="16" t="n">
+      <c r="F207" s="16" t="n">
         <v>18391.50025382049</v>
       </c>
-      <c r="G201" s="15" t="inlineStr"/>
-      <c r="H201" s="15" t="inlineStr"/>
-      <c r="I201" s="15" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="15" t="inlineStr">
+      <c r="G207" s="15" t="inlineStr"/>
+      <c r="H207" s="15" t="inlineStr"/>
+      <c r="I207" s="15" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B202" s="15" t="inlineStr"/>
-      <c r="C202" s="16" t="n">
+      <c r="B208" s="15" t="inlineStr"/>
+      <c r="C208" s="16" t="n">
         <v>61305.00084606828</v>
       </c>
-      <c r="D202" s="16" t="n">
+      <c r="D208" s="16" t="n">
         <v>42913.50059224779</v>
       </c>
-      <c r="E202" s="16" t="n">
+      <c r="E208" s="16" t="n">
         <v>21456.7502961239</v>
       </c>
-      <c r="F202" s="16" t="n">
+      <c r="F208" s="16" t="n">
         <v>18391.50025382049</v>
       </c>
-      <c r="G202" s="15" t="inlineStr"/>
-      <c r="H202" s="15" t="inlineStr"/>
-      <c r="I202" s="15" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="15" t="inlineStr">
+      <c r="G208" s="15" t="inlineStr"/>
+      <c r="H208" s="15" t="inlineStr"/>
+      <c r="I208" s="15" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B203" s="15" t="inlineStr"/>
-      <c r="C203" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D203" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F203" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" s="15" t="inlineStr"/>
-      <c r="H203" s="15" t="inlineStr"/>
-      <c r="I203" s="15" t="inlineStr"/>
-    </row>
-    <row r="205" ht="17" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
+      <c r="B209" s="15" t="inlineStr"/>
+      <c r="C209" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="15" t="inlineStr"/>
+      <c r="H209" s="15" t="inlineStr"/>
+      <c r="I209" s="15" t="inlineStr"/>
+    </row>
+    <row r="211" ht="17" customHeight="1">
+      <c r="A211" s="4" t="inlineStr">
         <is>
           <t>GRAIN PANS  [Grain Pans]</t>
         </is>
       </c>
-      <c r="B205" s="5" t="n"/>
-      <c r="C205" s="5" t="n"/>
-      <c r="D205" s="5" t="n"/>
-      <c r="E205" s="5" t="n"/>
-      <c r="F205" s="5" t="n"/>
-      <c r="G205" s="5" t="n"/>
-      <c r="H205" s="5" t="n"/>
-      <c r="I205" s="5" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="6" t="inlineStr">
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B206" s="6" t="inlineStr">
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C206" s="6" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G206" s="6" t="inlineStr">
+      <c r="G212" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H206" s="6" t="inlineStr">
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I206" s="6" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="8" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>Syrup</t>
         </is>
       </c>
-      <c r="B207" s="8" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C207" s="9" t="n">
+      <c r="C213" s="9" t="n">
         <v>1793.653546625551</v>
       </c>
-      <c r="D207" s="9" t="n">
+      <c r="D213" s="9" t="n">
         <v>1084.502805306608</v>
       </c>
-      <c r="E207" s="9" t="n">
+      <c r="E213" s="9" t="n">
         <v>877.2103843616237</v>
       </c>
-      <c r="F207" s="9" t="n">
+      <c r="F213" s="9" t="n">
         <v>709.1507413189427</v>
       </c>
-      <c r="G207" s="10" t="n">
+      <c r="G213" s="10" t="n">
         <v>60.4633379365214</v>
       </c>
-      <c r="H207" s="10" t="n">
+      <c r="H213" s="10" t="n">
         <v>80.8859488485713</v>
       </c>
-      <c r="I207" s="9" t="n">
+      <c r="I213" s="9" t="n">
         <v>22.30471673956822</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="12" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="12" t="inlineStr">
         <is>
           <t>A Molasses</t>
         </is>
       </c>
-      <c r="B208" s="12" t="inlineStr">
+      <c r="B214" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C208" s="13" t="n">
+      <c r="C214" s="13" t="n">
         <v>2948.052484340847</v>
       </c>
-      <c r="D208" s="13" t="n">
+      <c r="D214" s="13" t="n">
         <v>2063.636739038593</v>
       </c>
-      <c r="E208" s="13" t="n">
+      <c r="E214" s="13" t="n">
         <v>1382.636615155857</v>
       </c>
-      <c r="F208" s="13" t="n">
+      <c r="F214" s="13" t="n">
         <v>884.415745302254</v>
       </c>
-      <c r="G208" s="14" t="n">
+      <c r="G214" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H208" s="14" t="n">
+      <c r="H214" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="I208" s="13" t="n">
+      <c r="I214" s="13" t="n">
         <v>35.08072468210372</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="8" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
         <is>
           <t>B Molasses</t>
         </is>
       </c>
-      <c r="B209" s="8" t="inlineStr">
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C209" s="9" t="n">
+      <c r="C215" s="9" t="n">
         <v>6130.500084606829</v>
       </c>
-      <c r="D209" s="9" t="n">
+      <c r="D215" s="9" t="n">
         <v>4291.35005922478</v>
       </c>
-      <c r="E209" s="9" t="n">
+      <c r="E215" s="9" t="n">
         <v>2145.67502961239</v>
       </c>
-      <c r="F209" s="9" t="n">
+      <c r="F215" s="9" t="n">
         <v>1839.150025382049</v>
       </c>
-      <c r="G209" s="10" t="n">
+      <c r="G215" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H209" s="10" t="n">
+      <c r="H215" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I209" s="9" t="n">
+      <c r="I215" s="9" t="n">
         <v>72.95066379382705</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="12" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="12" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B210" s="12" t="inlineStr">
+      <c r="B216" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C210" s="13" t="n">
+      <c r="C216" s="13" t="n">
         <v>8453.965458602252</v>
       </c>
-      <c r="D210" s="13" t="n">
+      <c r="D216" s="13" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E210" s="13" t="n">
+      <c r="E216" s="13" t="n">
         <v>4405.522029129871</v>
       </c>
-      <c r="F210" s="13" t="n">
+      <c r="F216" s="13" t="n">
         <v>1014.47585503227</v>
       </c>
-      <c r="G210" s="14" t="n">
+      <c r="G216" s="14" t="n">
         <v>88</v>
       </c>
-      <c r="H210" s="14" t="n">
+      <c r="H216" s="14" t="n">
         <v>59.21806822629064</v>
       </c>
-      <c r="I210" s="13" t="n">
+      <c r="I216" s="13" t="n">
         <v>92.4361833097628</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="8" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B211" s="8" t="inlineStr">
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C211" s="9" t="n">
+      <c r="C217" s="9" t="n">
         <v>2418.240656970975</v>
       </c>
-      <c r="D211" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E211" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" s="9" t="n">
+      <c r="D217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="9" t="n">
         <v>2418.240656970975</v>
       </c>
-      <c r="G211" s="8" t="inlineStr"/>
-      <c r="H211" s="8" t="inlineStr"/>
-      <c r="I211" s="8" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="15" t="inlineStr">
+      <c r="G217" s="8" t="inlineStr"/>
+      <c r="H217" s="8" t="inlineStr"/>
+      <c r="I217" s="8" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B212" s="15" t="inlineStr"/>
-      <c r="C212" s="16" t="n">
+      <c r="B218" s="15" t="inlineStr"/>
+      <c r="C218" s="16" t="n">
         <v>10872.20611557323</v>
       </c>
-      <c r="D212" s="16" t="n">
+      <c r="D218" s="16" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E212" s="16" t="n">
+      <c r="E218" s="16" t="n">
         <v>4405.522029129871</v>
       </c>
-      <c r="F212" s="16" t="n">
+      <c r="F218" s="16" t="n">
         <v>3432.716512003245</v>
       </c>
-      <c r="G212" s="15" t="inlineStr"/>
-      <c r="H212" s="15" t="inlineStr"/>
-      <c r="I212" s="15" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="15" t="inlineStr">
+      <c r="G218" s="15" t="inlineStr"/>
+      <c r="H218" s="15" t="inlineStr"/>
+      <c r="I218" s="15" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B213" s="15" t="inlineStr"/>
-      <c r="C213" s="16" t="n">
+      <c r="B219" s="15" t="inlineStr"/>
+      <c r="C219" s="16" t="n">
         <v>10872.20611557323</v>
       </c>
-      <c r="D213" s="16" t="n">
+      <c r="D219" s="16" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E213" s="16" t="n">
+      <c r="E219" s="16" t="n">
         <v>4405.522029129871</v>
       </c>
-      <c r="F213" s="16" t="n">
+      <c r="F219" s="16" t="n">
         <v>3432.716512003245</v>
       </c>
-      <c r="G213" s="15" t="inlineStr"/>
-      <c r="H213" s="15" t="inlineStr"/>
-      <c r="I213" s="15" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="15" t="inlineStr">
+      <c r="G219" s="15" t="inlineStr"/>
+      <c r="H219" s="15" t="inlineStr"/>
+      <c r="I219" s="15" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B214" s="15" t="inlineStr"/>
-      <c r="C214" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D214" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E214" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F214" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" s="15" t="inlineStr"/>
-      <c r="H214" s="15" t="inlineStr"/>
-      <c r="I214" s="15" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="17" t="inlineStr">
+      <c r="B220" s="15" t="inlineStr"/>
+      <c r="C220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="15" t="inlineStr"/>
+      <c r="H220" s="15" t="inlineStr"/>
+      <c r="I220" s="15" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="17" t="inlineStr">
         <is>
           <t>Calandria steam type</t>
         </is>
       </c>
-      <c r="B215" s="17" t="inlineStr">
+      <c r="B221" s="17" t="inlineStr">
         <is>
           <t>Exhaust</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="17" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="17" t="inlineStr">
         <is>
           <t>Calandria pressure</t>
         </is>
       </c>
-      <c r="B216" s="20" t="n">
+      <c r="B222" s="20" t="n">
         <v>29.696</v>
       </c>
-      <c r="C216" s="19" t="inlineStr">
+      <c r="C222" s="19" t="inlineStr">
         <is>
           <t>psia</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="17" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="17" t="inlineStr">
         <is>
           <t>Calandria steam flow</t>
         </is>
       </c>
-      <c r="B217" s="21" t="n">
+      <c r="B223" s="21" t="n">
         <v>2929.369521103218</v>
       </c>
-      <c r="C217" s="19" t="inlineStr">
+      <c r="C223" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="17" customHeight="1">
-      <c r="A219" s="4" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="17" t="inlineStr">
+        <is>
+          <t>Heating surface</t>
+        </is>
+      </c>
+      <c r="B224" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C224" s="19" t="inlineStr">
+        <is>
+          <t>ft²</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="17" t="inlineStr">
+        <is>
+          <t>dT (calandria - masse)</t>
+        </is>
+      </c>
+      <c r="B225" s="22" t="n">
+        <v>71.90017475342529</v>
+      </c>
+      <c r="C225" s="19" t="inlineStr">
+        <is>
+          <t>°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="17" t="inlineStr">
+        <is>
+          <t>Overall U (back-calc)</t>
+        </is>
+      </c>
+      <c r="B226" s="22" t="n">
+        <v>12.84272001521226</v>
+      </c>
+      <c r="C226" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr·ft²·°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="17" customHeight="1">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t>C PANS  [C Pans]</t>
         </is>
       </c>
-      <c r="B219" s="5" t="n"/>
-      <c r="C219" s="5" t="n"/>
-      <c r="D219" s="5" t="n"/>
-      <c r="E219" s="5" t="n"/>
-      <c r="F219" s="5" t="n"/>
-      <c r="G219" s="5" t="n"/>
-      <c r="H219" s="5" t="n"/>
-      <c r="I219" s="5" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B220" s="6" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="C229" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="D229" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E229" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G220" s="6" t="inlineStr">
+      <c r="G229" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H220" s="6" t="inlineStr">
+      <c r="H229" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I220" s="6" t="inlineStr">
+      <c r="I229" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="8" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
         <is>
           <t>Grain Massecuite</t>
         </is>
       </c>
-      <c r="B221" s="8" t="inlineStr">
+      <c r="B230" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C221" s="9" t="n">
+      <c r="C230" s="9" t="n">
         <v>8453.965458602252</v>
       </c>
-      <c r="D221" s="9" t="n">
+      <c r="D230" s="9" t="n">
         <v>7439.489603569981</v>
       </c>
-      <c r="E221" s="9" t="n">
+      <c r="E230" s="9" t="n">
         <v>4405.52202912987</v>
       </c>
-      <c r="F221" s="9" t="n">
+      <c r="F230" s="9" t="n">
         <v>1014.47585503227</v>
       </c>
-      <c r="G221" s="10" t="n">
+      <c r="G230" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="H221" s="10" t="n">
+      <c r="H230" s="10" t="n">
         <v>59.21806822629064</v>
       </c>
-      <c r="I221" s="9" t="n">
+      <c r="I230" s="9" t="n">
         <v>92.4361833097628</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="12" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
         <is>
           <t>B Molasses</t>
         </is>
       </c>
-      <c r="B222" s="12" t="inlineStr">
+      <c r="B231" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C222" s="13" t="n">
+      <c r="C231" s="13" t="n">
         <v>55174.50076146145</v>
       </c>
-      <c r="D222" s="13" t="n">
+      <c r="D231" s="13" t="n">
         <v>38622.15053302301</v>
       </c>
-      <c r="E222" s="13" t="n">
+      <c r="E231" s="13" t="n">
         <v>19311.07526651151</v>
       </c>
-      <c r="F222" s="13" t="n">
+      <c r="F231" s="13" t="n">
         <v>16552.35022843844</v>
       </c>
-      <c r="G222" s="14" t="n">
+      <c r="G231" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H222" s="14" t="n">
+      <c r="H231" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="I222" s="13" t="n">
+      <c r="I231" s="13" t="n">
         <v>656.5559741444433</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="8" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B223" s="8" t="inlineStr">
+      <c r="B232" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C223" s="9" t="n">
+      <c r="C232" s="9" t="n">
         <v>48232.08391266282</v>
       </c>
-      <c r="D223" s="9" t="n">
+      <c r="D232" s="9" t="n">
         <v>46061.64013659299</v>
       </c>
-      <c r="E223" s="9" t="n">
+      <c r="E232" s="9" t="n">
         <v>23716.59729564138</v>
       </c>
-      <c r="F223" s="9" t="n">
+      <c r="F232" s="9" t="n">
         <v>2170.443776069827</v>
       </c>
-      <c r="G223" s="10" t="n">
+      <c r="G232" s="10" t="n">
         <v>95.5</v>
       </c>
-      <c r="H223" s="10" t="n">
+      <c r="H232" s="10" t="n">
         <v>51.48882502948496</v>
       </c>
-      <c r="I223" s="9" t="n">
+      <c r="I232" s="9" t="n">
         <v>508.9394939081455</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="12" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="12" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B224" s="12" t="inlineStr">
+      <c r="B233" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C224" s="13" t="n">
+      <c r="C233" s="13" t="n">
         <v>15396.38230740088</v>
       </c>
-      <c r="D224" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E224" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F224" s="13" t="n">
+      <c r="D233" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="13" t="n">
         <v>15396.38230740088</v>
       </c>
-      <c r="G224" s="12" t="inlineStr"/>
-      <c r="H224" s="12" t="inlineStr"/>
-      <c r="I224" s="12" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="15" t="inlineStr">
+      <c r="G233" s="12" t="inlineStr"/>
+      <c r="H233" s="12" t="inlineStr"/>
+      <c r="I233" s="12" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B225" s="15" t="inlineStr"/>
-      <c r="C225" s="16" t="n">
+      <c r="B234" s="15" t="inlineStr"/>
+      <c r="C234" s="16" t="n">
         <v>63628.4662200637</v>
       </c>
-      <c r="D225" s="16" t="n">
+      <c r="D234" s="16" t="n">
         <v>46061.64013659299</v>
       </c>
-      <c r="E225" s="16" t="n">
+      <c r="E234" s="16" t="n">
         <v>23716.59729564138</v>
       </c>
-      <c r="F225" s="16" t="n">
+      <c r="F234" s="16" t="n">
         <v>17566.82608347071</v>
       </c>
-      <c r="G225" s="15" t="inlineStr"/>
-      <c r="H225" s="15" t="inlineStr"/>
-      <c r="I225" s="15" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="15" t="inlineStr">
+      <c r="G234" s="15" t="inlineStr"/>
+      <c r="H234" s="15" t="inlineStr"/>
+      <c r="I234" s="15" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B226" s="15" t="inlineStr"/>
-      <c r="C226" s="16" t="n">
+      <c r="B235" s="15" t="inlineStr"/>
+      <c r="C235" s="16" t="n">
         <v>63628.4662200637</v>
       </c>
-      <c r="D226" s="16" t="n">
+      <c r="D235" s="16" t="n">
         <v>46061.64013659299</v>
       </c>
-      <c r="E226" s="16" t="n">
+      <c r="E235" s="16" t="n">
         <v>23716.59729564138</v>
       </c>
-      <c r="F226" s="16" t="n">
+      <c r="F235" s="16" t="n">
         <v>17566.82608347071</v>
       </c>
-      <c r="G226" s="15" t="inlineStr"/>
-      <c r="H226" s="15" t="inlineStr"/>
-      <c r="I226" s="15" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="15" t="inlineStr">
+      <c r="G235" s="15" t="inlineStr"/>
+      <c r="H235" s="15" t="inlineStr"/>
+      <c r="I235" s="15" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B227" s="15" t="inlineStr"/>
-      <c r="C227" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D227" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E227" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F227" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" s="15" t="inlineStr"/>
-      <c r="H227" s="15" t="inlineStr"/>
-      <c r="I227" s="15" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="17" t="inlineStr">
-        <is>
-          <t>Calandria steam type</t>
-        </is>
-      </c>
-      <c r="B228" s="17" t="inlineStr">
-        <is>
-          <t>Exhaust</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="17" t="inlineStr">
-        <is>
-          <t>Calandria pressure</t>
-        </is>
-      </c>
-      <c r="B229" s="20" t="n">
-        <v>21.696</v>
-      </c>
-      <c r="C229" s="19" t="inlineStr">
-        <is>
-          <t>psia</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="17" t="inlineStr">
-        <is>
-          <t>Calandria steam flow</t>
-        </is>
-      </c>
-      <c r="B230" s="21" t="n">
-        <v>18016.87108692931</v>
-      </c>
-      <c r="C230" s="19" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="17" customHeight="1">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>C CRYSTALLIZERS  [C Crystallizers]</t>
-        </is>
-      </c>
-      <c r="B232" s="5" t="n"/>
-      <c r="C232" s="5" t="n"/>
-      <c r="D232" s="5" t="n"/>
-      <c r="E232" s="5" t="n"/>
-      <c r="F232" s="5" t="n"/>
-      <c r="G232" s="5" t="n"/>
-      <c r="H232" s="5" t="n"/>
-      <c r="I232" s="5" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C233" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D233" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F233" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G233" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H233" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I233" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite In  (T=173.0 °F)</t>
-        </is>
-      </c>
-      <c r="B234" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C234" s="9" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D234" s="9" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E234" s="9" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F234" s="9" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G234" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H234" s="10" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I234" s="9" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="12" t="inlineStr">
-        <is>
-          <t>Massecuite Out  (T=120.0 °F)</t>
-        </is>
-      </c>
-      <c r="B235" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C235" s="13" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D235" s="13" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E235" s="13" t="n">
-        <v>23716.59729564138</v>
-      </c>
-      <c r="F235" s="13" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G235" s="14" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H235" s="14" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I235" s="13" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="17" t="inlineStr">
-        <is>
-          <t>ML purity in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B236" s="17" t="inlineStr">
-        <is>
-          <t>33.0 -&gt; 30.0</t>
-        </is>
-      </c>
-      <c r="C236" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="B236" s="15" t="inlineStr"/>
+      <c r="C236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="15" t="inlineStr"/>
+      <c r="H236" s="15" t="inlineStr"/>
+      <c r="I236" s="15" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="17" t="inlineStr">
         <is>
-          <t>Crystal content in -&gt; out</t>
+          <t>Calandria steam type</t>
         </is>
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>26.4 -&gt; 29.3</t>
-        </is>
-      </c>
-      <c r="C237" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
+          <t>Exhaust</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="17" t="inlineStr">
         <is>
-          <t>Duty</t>
-        </is>
-      </c>
-      <c r="B238" s="21" t="n">
-        <v>1165803.366111661</v>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B238" s="20" t="n">
+        <v>21.696</v>
       </c>
       <c r="C238" s="19" t="inlineStr">
         <is>
-          <t>BTU/hr</t>
+          <t>psia</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="17" t="inlineStr">
         <is>
-          <t>Cooling Water</t>
+          <t>Calandria steam flow</t>
         </is>
       </c>
       <c r="B239" s="21" t="n">
-        <v>58290.16830558303</v>
+        <v>18016.87108692931</v>
       </c>
       <c r="C239" s="19" t="inlineStr">
         <is>
-          <t>lb/hr  (116 gpm, 85 -&gt; 105 °F)</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="17" customHeight="1">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>C REHEATERS  [C Reheaters]</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="n"/>
-      <c r="C241" s="5" t="n"/>
-      <c r="D241" s="5" t="n"/>
-      <c r="E241" s="5" t="n"/>
-      <c r="F241" s="5" t="n"/>
-      <c r="G241" s="5" t="n"/>
-      <c r="H241" s="5" t="n"/>
-      <c r="I241" s="5" t="n"/>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="17" t="inlineStr">
+        <is>
+          <t>Heating surface</t>
+        </is>
+      </c>
+      <c r="B240" s="21" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C240" s="19" t="inlineStr">
+        <is>
+          <t>ft²</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="17" t="inlineStr">
+        <is>
+          <t>dT (calandria - masse)</t>
+        </is>
+      </c>
+      <c r="B241" s="22" t="n">
+        <v>59.32161922113474</v>
+      </c>
+      <c r="C241" s="19" t="inlineStr">
+        <is>
+          <t>°F</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
+      <c r="A242" s="17" t="inlineStr">
+        <is>
+          <t>Overall U (back-calc)</t>
+        </is>
+      </c>
+      <c r="B242" s="22" t="n">
+        <v>24.22384048218605</v>
+      </c>
+      <c r="C242" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr·ft²·°F</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="17" customHeight="1">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>C CRYSTALLIZERS  [C Crystallizers]</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="5" t="n"/>
+      <c r="I244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="B245" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
+      <c r="C245" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="D245" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E245" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G242" s="6" t="inlineStr">
+      <c r="G245" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="H245" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I245" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite In  (T=120.0 °F)</t>
-        </is>
-      </c>
-      <c r="B243" s="8" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite In  (T=173.0 °F)</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C243" s="9" t="n">
+      <c r="C246" s="9" t="n">
         <v>48232.08391266282</v>
       </c>
-      <c r="D243" s="9" t="n">
+      <c r="D246" s="9" t="n">
         <v>46061.64013659299</v>
       </c>
-      <c r="E243" s="9" t="n">
+      <c r="E246" s="9" t="n">
         <v>23716.59729564138</v>
       </c>
-      <c r="F243" s="9" t="n">
+      <c r="F246" s="9" t="n">
         <v>2170.443776069827</v>
       </c>
-      <c r="G243" s="10" t="n">
+      <c r="G246" s="10" t="n">
         <v>95.5</v>
       </c>
-      <c r="H243" s="10" t="n">
+      <c r="H246" s="10" t="n">
         <v>51.48882502948496</v>
       </c>
-      <c r="I243" s="9" t="n">
+      <c r="I246" s="9" t="n">
         <v>508.9394939081455</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="12" t="inlineStr">
-        <is>
-          <t>Massecuite Out  (T=130.0 °F)</t>
-        </is>
-      </c>
-      <c r="B244" s="12" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out  (T=120.0 °F)</t>
+        </is>
+      </c>
+      <c r="B247" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C244" s="13" t="n">
+      <c r="C247" s="13" t="n">
         <v>48232.08391266282</v>
       </c>
-      <c r="D244" s="13" t="n">
+      <c r="D247" s="13" t="n">
         <v>46061.64013659299</v>
       </c>
-      <c r="E244" s="13" t="n">
+      <c r="E247" s="13" t="n">
         <v>23716.59729564138</v>
       </c>
-      <c r="F244" s="13" t="n">
+      <c r="F247" s="13" t="n">
         <v>2170.443776069827</v>
       </c>
-      <c r="G244" s="14" t="n">
+      <c r="G247" s="14" t="n">
         <v>95.5</v>
       </c>
-      <c r="H244" s="14" t="n">
+      <c r="H247" s="14" t="n">
         <v>51.48882502948496</v>
       </c>
-      <c r="I244" s="13" t="n">
+      <c r="I247" s="13" t="n">
         <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="17" t="inlineStr">
-        <is>
-          <t>ML purity in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B245" s="17" t="inlineStr">
-        <is>
-          <t>30.0 -&gt; 30.0</t>
-        </is>
-      </c>
-      <c r="C245" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="17" t="inlineStr">
-        <is>
-          <t>Crystal content in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B246" s="17" t="inlineStr">
-        <is>
-          <t>29.3 -&gt; 29.3</t>
-        </is>
-      </c>
-      <c r="C246" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="17" t="inlineStr">
-        <is>
-          <t>Duty</t>
-        </is>
-      </c>
-      <c r="B247" s="21" t="n">
-        <v>220059.8474932024</v>
-      </c>
-      <c r="C247" s="19" t="inlineStr">
-        <is>
-          <t>BTU/hr</t>
-        </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="17" t="inlineStr">
         <is>
+          <t>ML purity in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B248" s="17" t="inlineStr">
+        <is>
+          <t>33.0 -&gt; 30.0</t>
+        </is>
+      </c>
+      <c r="C248" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="17" t="inlineStr">
+        <is>
+          <t>Crystal content in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B249" s="17" t="inlineStr">
+        <is>
+          <t>26.4 -&gt; 29.3</t>
+        </is>
+      </c>
+      <c r="C249" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="17" t="inlineStr">
+        <is>
+          <t>Duty</t>
+        </is>
+      </c>
+      <c r="B250" s="21" t="n">
+        <v>1165803.366111661</v>
+      </c>
+      <c r="C250" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="17" t="inlineStr">
+        <is>
+          <t>Cooling Water</t>
+        </is>
+      </c>
+      <c r="B251" s="21" t="n">
+        <v>58290.16830558303</v>
+      </c>
+      <c r="C251" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr  (116 gpm, 85 -&gt; 105 °F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="17" customHeight="1">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>C REHEATERS  [C Reheaters]</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D254" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G254" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H254" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I254" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite In  (T=120.0 °F)</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C255" s="9" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D255" s="9" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E255" s="9" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F255" s="9" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G255" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H255" s="10" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I255" s="9" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out  (T=130.0 °F)</t>
+        </is>
+      </c>
+      <c r="B256" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C256" s="13" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D256" s="13" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E256" s="13" t="n">
+        <v>23716.59729564138</v>
+      </c>
+      <c r="F256" s="13" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G256" s="14" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H256" s="14" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I256" s="13" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="17" t="inlineStr">
+        <is>
+          <t>ML purity in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B257" s="17" t="inlineStr">
+        <is>
+          <t>30.0 -&gt; 30.0</t>
+        </is>
+      </c>
+      <c r="C257" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="17" t="inlineStr">
+        <is>
+          <t>Crystal content in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B258" s="17" t="inlineStr">
+        <is>
+          <t>29.3 -&gt; 29.3</t>
+        </is>
+      </c>
+      <c r="C258" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="17" t="inlineStr">
+        <is>
+          <t>Duty</t>
+        </is>
+      </c>
+      <c r="B259" s="21" t="n">
+        <v>220059.8474932024</v>
+      </c>
+      <c r="C259" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="17" t="inlineStr">
+        <is>
           <t>Hot Water</t>
         </is>
       </c>
-      <c r="B248" s="21" t="n">
+      <c r="B260" s="21" t="n">
         <v>14670.65649954683</v>
       </c>
-      <c r="C248" s="19" t="inlineStr">
+      <c r="C260" s="19" t="inlineStr">
         <is>
           <t>lb/hr  (29 gpm, 150 -&gt; 135 °F)</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="17" customHeight="1">
-      <c r="A250" s="4" t="inlineStr">
+    <row r="262" ht="17" customHeight="1">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>C CENTRIFUGALS  [C Centrifugals]</t>
         </is>
       </c>
-      <c r="B250" s="5" t="n"/>
-      <c r="C250" s="5" t="n"/>
-      <c r="D250" s="5" t="n"/>
-      <c r="E250" s="5" t="n"/>
-      <c r="F250" s="5" t="n"/>
-      <c r="G250" s="5" t="n"/>
-      <c r="H250" s="5" t="n"/>
-      <c r="I250" s="5" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="5" t="n"/>
+      <c r="I262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C251" s="6" t="inlineStr">
+      <c r="C263" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D251" s="6" t="inlineStr">
+      <c r="D263" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E263" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F251" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G251" s="6" t="inlineStr">
+      <c r="G263" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H251" s="6" t="inlineStr">
+      <c r="H263" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I251" s="6" t="inlineStr">
+      <c r="I263" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite</t>
-        </is>
-      </c>
-      <c r="B252" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C252" s="9" t="n">
-        <v>48232.08391266282</v>
-      </c>
-      <c r="D252" s="9" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E252" s="9" t="n">
-        <v>23716.59729564139</v>
-      </c>
-      <c r="F252" s="9" t="n">
-        <v>2170.443776069827</v>
-      </c>
-      <c r="G252" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H252" s="10" t="n">
-        <v>51.48882502948496</v>
-      </c>
-      <c r="I252" s="9" t="n">
-        <v>508.9394939081455</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="12" t="inlineStr">
-        <is>
-          <t>Wash Water</t>
-        </is>
-      </c>
-      <c r="B253" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C253" s="13" t="n">
-        <v>5139.960235525126</v>
-      </c>
-      <c r="D253" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E253" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F253" s="13" t="n">
-        <v>5139.960235525126</v>
-      </c>
-      <c r="G253" s="12" t="inlineStr"/>
-      <c r="H253" s="12" t="inlineStr"/>
-      <c r="I253" s="12" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="8" t="inlineStr">
-        <is>
-          <t>Sugar Out</t>
-        </is>
-      </c>
-      <c r="B254" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C254" s="9" t="n">
-        <v>17665.8764236837</v>
-      </c>
-      <c r="D254" s="9" t="n">
-        <v>16782.58260249951</v>
-      </c>
-      <c r="E254" s="9" t="n">
-        <v>13761.71773404961</v>
-      </c>
-      <c r="F254" s="9" t="n">
-        <v>883.2938211841865</v>
-      </c>
-      <c r="G254" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="H254" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="I254" s="9" t="n">
-        <v>186.8514132326083</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="12" t="inlineStr">
-        <is>
-          <t>Molasses Out</t>
-        </is>
-      </c>
-      <c r="B255" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C255" s="13" t="n">
-        <v>35706.16772450424</v>
-      </c>
-      <c r="D255" s="13" t="n">
-        <v>29279.05753409348</v>
-      </c>
-      <c r="E255" s="13" t="n">
-        <v>9954.879561591782</v>
-      </c>
-      <c r="F255" s="13" t="n">
-        <v>6427.110190410764</v>
-      </c>
-      <c r="G255" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="H255" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="I255" s="13" t="n">
-        <v>401.6469367731214</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="15" t="inlineStr">
-        <is>
-          <t>Total In</t>
-        </is>
-      </c>
-      <c r="B256" s="15" t="inlineStr"/>
-      <c r="C256" s="16" t="n">
-        <v>53372.04414818795</v>
-      </c>
-      <c r="D256" s="16" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E256" s="16" t="n">
-        <v>23716.59729564139</v>
-      </c>
-      <c r="F256" s="16" t="n">
-        <v>7310.404011594954</v>
-      </c>
-      <c r="G256" s="15" t="inlineStr"/>
-      <c r="H256" s="15" t="inlineStr"/>
-      <c r="I256" s="15" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="15" t="inlineStr">
-        <is>
-          <t>Total Out</t>
-        </is>
-      </c>
-      <c r="B257" s="15" t="inlineStr"/>
-      <c r="C257" s="16" t="n">
-        <v>53372.04414818795</v>
-      </c>
-      <c r="D257" s="16" t="n">
-        <v>46061.64013659299</v>
-      </c>
-      <c r="E257" s="16" t="n">
-        <v>23716.59729564139</v>
-      </c>
-      <c r="F257" s="16" t="n">
-        <v>7310.404011594954</v>
-      </c>
-      <c r="G257" s="15" t="inlineStr"/>
-      <c r="H257" s="15" t="inlineStr"/>
-      <c r="I257" s="15" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B258" s="15" t="inlineStr"/>
-      <c r="C258" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D258" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E258" s="16" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="F258" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" s="15" t="inlineStr"/>
-      <c r="H258" s="15" t="inlineStr"/>
-      <c r="I258" s="15" t="inlineStr"/>
-    </row>
-    <row r="260" ht="17" customHeight="1">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>C MAGMA  (mingler target 92.0 Bx)</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="n"/>
-      <c r="C260" s="5" t="n"/>
-      <c r="D260" s="5" t="n"/>
-      <c r="E260" s="5" t="n"/>
-      <c r="F260" s="5" t="n"/>
-      <c r="G260" s="5" t="n"/>
-      <c r="H260" s="5" t="n"/>
-      <c r="I260" s="5" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B261" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C261" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D261" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E261" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F261" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G261" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H261" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I261" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="8" t="inlineStr">
-        <is>
-          <t>C Sugar</t>
-        </is>
-      </c>
-      <c r="B262" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C262" s="9" t="n">
-        <v>17665.8764236837</v>
-      </c>
-      <c r="D262" s="9" t="n">
-        <v>16782.58260249951</v>
-      </c>
-      <c r="E262" s="9" t="n">
-        <v>13761.71773404961</v>
-      </c>
-      <c r="F262" s="9" t="n">
-        <v>883.2938211841865</v>
-      </c>
-      <c r="G262" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="H262" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="I262" s="9" t="n">
-        <v>186.8514132326083</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="12" t="inlineStr">
-        <is>
-          <t>Mingler Water</t>
-        </is>
-      </c>
-      <c r="B263" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C263" s="13" t="n">
-        <v>576.0611877288138</v>
-      </c>
-      <c r="D263" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F263" s="13" t="n">
-        <v>576.0611877288138</v>
-      </c>
-      <c r="G263" s="12" t="inlineStr"/>
-      <c r="H263" s="12" t="inlineStr"/>
-      <c r="I263" s="12" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="8" t="inlineStr">
         <is>
+          <t>Massecuite</t>
+        </is>
+      </c>
+      <c r="B264" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="n">
+        <v>48232.08391266282</v>
+      </c>
+      <c r="D264" s="9" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E264" s="9" t="n">
+        <v>23716.59729564139</v>
+      </c>
+      <c r="F264" s="9" t="n">
+        <v>2170.443776069827</v>
+      </c>
+      <c r="G264" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H264" s="10" t="n">
+        <v>51.48882502948496</v>
+      </c>
+      <c r="I264" s="9" t="n">
+        <v>508.9394939081455</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="12" t="inlineStr">
+        <is>
+          <t>Wash Water</t>
+        </is>
+      </c>
+      <c r="B265" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C265" s="13" t="n">
+        <v>5139.960235525126</v>
+      </c>
+      <c r="D265" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" s="13" t="n">
+        <v>5139.960235525126</v>
+      </c>
+      <c r="G265" s="12" t="inlineStr"/>
+      <c r="H265" s="12" t="inlineStr"/>
+      <c r="I265" s="12" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="8" t="inlineStr">
+        <is>
+          <t>Sugar Out</t>
+        </is>
+      </c>
+      <c r="B266" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C266" s="9" t="n">
+        <v>17665.8764236837</v>
+      </c>
+      <c r="D266" s="9" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E266" s="9" t="n">
+        <v>13761.71773404961</v>
+      </c>
+      <c r="F266" s="9" t="n">
+        <v>883.2938211841865</v>
+      </c>
+      <c r="G266" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H266" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I266" s="9" t="n">
+        <v>186.8514132326083</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="12" t="inlineStr">
+        <is>
+          <t>Molasses Out</t>
+        </is>
+      </c>
+      <c r="B267" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C267" s="13" t="n">
+        <v>35706.16772450424</v>
+      </c>
+      <c r="D267" s="13" t="n">
+        <v>29279.05753409348</v>
+      </c>
+      <c r="E267" s="13" t="n">
+        <v>9954.879561591782</v>
+      </c>
+      <c r="F267" s="13" t="n">
+        <v>6427.110190410764</v>
+      </c>
+      <c r="G267" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="H267" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I267" s="13" t="n">
+        <v>401.6469367731214</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B268" s="15" t="inlineStr"/>
+      <c r="C268" s="16" t="n">
+        <v>53372.04414818795</v>
+      </c>
+      <c r="D268" s="16" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E268" s="16" t="n">
+        <v>23716.59729564139</v>
+      </c>
+      <c r="F268" s="16" t="n">
+        <v>7310.404011594954</v>
+      </c>
+      <c r="G268" s="15" t="inlineStr"/>
+      <c r="H268" s="15" t="inlineStr"/>
+      <c r="I268" s="15" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B269" s="15" t="inlineStr"/>
+      <c r="C269" s="16" t="n">
+        <v>53372.04414818795</v>
+      </c>
+      <c r="D269" s="16" t="n">
+        <v>46061.64013659299</v>
+      </c>
+      <c r="E269" s="16" t="n">
+        <v>23716.59729564139</v>
+      </c>
+      <c r="F269" s="16" t="n">
+        <v>7310.404011594954</v>
+      </c>
+      <c r="G269" s="15" t="inlineStr"/>
+      <c r="H269" s="15" t="inlineStr"/>
+      <c r="I269" s="15" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B270" s="15" t="inlineStr"/>
+      <c r="C270" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" s="16" t="n">
+        <v>-3.637978807091713e-12</v>
+      </c>
+      <c r="F270" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" s="15" t="inlineStr"/>
+      <c r="H270" s="15" t="inlineStr"/>
+      <c r="I270" s="15" t="inlineStr"/>
+    </row>
+    <row r="272" ht="17" customHeight="1">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>C MAGMA  (mingler target 92.0 Bx)</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C273" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D273" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E273" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G273" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H273" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I273" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="8" t="inlineStr">
+        <is>
+          <t>C Sugar</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C274" s="9" t="n">
+        <v>17665.8764236837</v>
+      </c>
+      <c r="D274" s="9" t="n">
+        <v>16782.58260249951</v>
+      </c>
+      <c r="E274" s="9" t="n">
+        <v>13761.71773404961</v>
+      </c>
+      <c r="F274" s="9" t="n">
+        <v>883.2938211841865</v>
+      </c>
+      <c r="G274" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H274" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I274" s="9" t="n">
+        <v>186.8514132326083</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="12" t="inlineStr">
+        <is>
+          <t>Mingler Water</t>
+        </is>
+      </c>
+      <c r="B275" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C275" s="13" t="n">
+        <v>576.0611877288138</v>
+      </c>
+      <c r="D275" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="13" t="n">
+        <v>576.0611877288138</v>
+      </c>
+      <c r="G275" s="12" t="inlineStr"/>
+      <c r="H275" s="12" t="inlineStr"/>
+      <c r="I275" s="12" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
+        <is>
           <t>C Magma</t>
         </is>
       </c>
-      <c r="B264" s="8" t="inlineStr">
+      <c r="B276" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C264" s="9" t="n">
+      <c r="C276" s="9" t="n">
         <v>18241.93761141252</v>
       </c>
-      <c r="D264" s="9" t="n">
+      <c r="D276" s="9" t="n">
         <v>16782.58260249951</v>
       </c>
-      <c r="E264" s="9" t="n">
+      <c r="E276" s="9" t="n">
         <v>13761.7177340496</v>
       </c>
-      <c r="F264" s="9" t="n">
+      <c r="F276" s="9" t="n">
         <v>1459.355008913</v>
       </c>
-      <c r="G264" s="10" t="n">
+      <c r="G276" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H264" s="10" t="n">
+      <c r="H276" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="I264" s="9" t="n">
+      <c r="I276" s="9" t="n">
         <v>195.7115313137704</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="15" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B265" s="15" t="inlineStr"/>
-      <c r="C265" s="16" t="n">
+      <c r="B277" s="15" t="inlineStr"/>
+      <c r="C277" s="16" t="n">
         <v>18241.93761141252</v>
       </c>
-      <c r="D265" s="16" t="n">
+      <c r="D277" s="16" t="n">
         <v>16782.58260249951</v>
       </c>
-      <c r="E265" s="16" t="n">
+      <c r="E277" s="16" t="n">
         <v>13761.71773404961</v>
       </c>
-      <c r="F265" s="16" t="n">
+      <c r="F277" s="16" t="n">
         <v>1459.355008913</v>
       </c>
-      <c r="G265" s="15" t="inlineStr"/>
-      <c r="H265" s="15" t="inlineStr"/>
-      <c r="I265" s="15" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="15" t="inlineStr">
+      <c r="G277" s="15" t="inlineStr"/>
+      <c r="H277" s="15" t="inlineStr"/>
+      <c r="I277" s="15" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B266" s="15" t="inlineStr"/>
-      <c r="C266" s="16" t="n">
+      <c r="B278" s="15" t="inlineStr"/>
+      <c r="C278" s="16" t="n">
         <v>18241.93761141252</v>
       </c>
-      <c r="D266" s="16" t="n">
+      <c r="D278" s="16" t="n">
         <v>16782.58260249951</v>
       </c>
-      <c r="E266" s="16" t="n">
+      <c r="E278" s="16" t="n">
         <v>13761.7177340496</v>
       </c>
-      <c r="F266" s="16" t="n">
+      <c r="F278" s="16" t="n">
         <v>1459.355008913</v>
       </c>
-      <c r="G266" s="15" t="inlineStr"/>
-      <c r="H266" s="15" t="inlineStr"/>
-      <c r="I266" s="15" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="15" t="inlineStr">
+      <c r="G278" s="15" t="inlineStr"/>
+      <c r="H278" s="15" t="inlineStr"/>
+      <c r="I278" s="15" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B267" s="15" t="inlineStr"/>
-      <c r="C267" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D267" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="16" t="n">
+      <c r="B279" s="15" t="inlineStr"/>
+      <c r="C279" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" s="16" t="n">
         <v>5.456968210637569e-12</v>
       </c>
-      <c r="F267" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" s="15" t="inlineStr"/>
-      <c r="H267" s="15" t="inlineStr"/>
-      <c r="I267" s="15" t="inlineStr"/>
-    </row>
-    <row r="269" ht="17" customHeight="1">
-      <c r="A269" s="4" t="inlineStr">
+      <c r="F279" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="15" t="inlineStr"/>
+      <c r="H279" s="15" t="inlineStr"/>
+      <c r="I279" s="15" t="inlineStr"/>
+    </row>
+    <row r="281" ht="17" customHeight="1">
+      <c r="A281" s="4" t="inlineStr">
         <is>
           <t>C MAGMA DISTRIBUTION</t>
         </is>
       </c>
-      <c r="B269" s="5" t="n"/>
-      <c r="C269" s="5" t="n"/>
-      <c r="D269" s="5" t="n"/>
-      <c r="E269" s="5" t="n"/>
-      <c r="F269" s="5" t="n"/>
-      <c r="G269" s="5" t="n"/>
-      <c r="H269" s="5" t="n"/>
-      <c r="I269" s="5" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="6" t="inlineStr">
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="5" t="n"/>
+      <c r="I281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="B282" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
+      <c r="C282" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="D282" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E282" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G270" s="6" t="inlineStr">
+      <c r="G282" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="H282" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I282" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="8" t="inlineStr">
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
         <is>
           <t>Magma (total)</t>
         </is>
       </c>
-      <c r="B271" s="8" t="inlineStr">
+      <c r="B283" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C271" s="9" t="n">
+      <c r="C283" s="9" t="n">
         <v>18241.93761141252</v>
       </c>
-      <c r="D271" s="9" t="n">
+      <c r="D283" s="9" t="n">
         <v>16782.58260249951</v>
       </c>
-      <c r="E271" s="9" t="n">
+      <c r="E283" s="9" t="n">
         <v>13761.7177340496</v>
       </c>
-      <c r="F271" s="9" t="n">
+      <c r="F283" s="9" t="n">
         <v>1459.355008913</v>
       </c>
-      <c r="G271" s="10" t="n">
+      <c r="G283" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H271" s="10" t="n">
+      <c r="H283" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="I271" s="9" t="n">
+      <c r="I283" s="9" t="n">
         <v>195.7115313137704</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="12" t="inlineStr">
+    <row r="284">
+      <c r="A284" s="12" t="inlineStr">
         <is>
           <t>C Magma to B Footing</t>
         </is>
       </c>
-      <c r="B272" s="12" t="inlineStr">
+      <c r="B284" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C272" s="13" t="n">
+      <c r="C284" s="13" t="n">
         <v>14593.55008913001</v>
       </c>
-      <c r="D272" s="13" t="n">
+      <c r="D284" s="13" t="n">
         <v>13426.06608199961</v>
       </c>
-      <c r="E272" s="13" t="n">
+      <c r="E284" s="13" t="n">
         <v>11009.37418723968</v>
       </c>
-      <c r="F272" s="13" t="n">
+      <c r="F284" s="13" t="n">
         <v>1167.484007130401</v>
       </c>
-      <c r="G272" s="14" t="n">
+      <c r="G284" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="H272" s="14" t="n">
+      <c r="H284" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="I272" s="13" t="n">
+      <c r="I284" s="13" t="n">
         <v>156.5692250510163</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="8" t="inlineStr">
+    <row r="285">
+      <c r="A285" s="8" t="inlineStr">
         <is>
           <t>C Magma to Remelt</t>
         </is>
       </c>
-      <c r="B273" s="8" t="inlineStr">
+      <c r="B285" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C273" s="9" t="n">
+      <c r="C285" s="9" t="n">
         <v>3648.387522282503</v>
       </c>
-      <c r="D273" s="9" t="n">
+      <c r="D285" s="9" t="n">
         <v>3356.516520499903</v>
       </c>
-      <c r="E273" s="9" t="n">
+      <c r="E285" s="9" t="n">
         <v>2752.34354680992</v>
       </c>
-      <c r="F273" s="9" t="n">
+      <c r="F285" s="9" t="n">
         <v>291.8710017826002</v>
       </c>
-      <c r="G273" s="10" t="n">
+      <c r="G285" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H273" s="10" t="n">
+      <c r="H285" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="I273" s="9" t="n">
+      <c r="I285" s="9" t="n">
         <v>39.14230626275408</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="15" t="inlineStr">
+    <row r="286">
+      <c r="A286" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B274" s="15" t="inlineStr"/>
-      <c r="C274" s="16" t="n">
+      <c r="B286" s="15" t="inlineStr"/>
+      <c r="C286" s="16" t="n">
         <v>18241.93761141252</v>
       </c>
-      <c r="D274" s="16" t="n">
+      <c r="D286" s="16" t="n">
         <v>16782.58260249951</v>
       </c>
-      <c r="E274" s="16" t="n">
+      <c r="E286" s="16" t="n">
         <v>13761.7177340496</v>
       </c>
-      <c r="F274" s="16" t="n">
+      <c r="F286" s="16" t="n">
         <v>1459.355008913</v>
       </c>
-      <c r="G274" s="15" t="inlineStr"/>
-      <c r="H274" s="15" t="inlineStr"/>
-      <c r="I274" s="15" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="15" t="inlineStr">
+      <c r="G286" s="15" t="inlineStr"/>
+      <c r="H286" s="15" t="inlineStr"/>
+      <c r="I286" s="15" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B275" s="15" t="inlineStr"/>
-      <c r="C275" s="16" t="n">
+      <c r="B287" s="15" t="inlineStr"/>
+      <c r="C287" s="16" t="n">
         <v>18241.93761141252</v>
       </c>
-      <c r="D275" s="16" t="n">
+      <c r="D287" s="16" t="n">
         <v>16782.58260249951</v>
       </c>
-      <c r="E275" s="16" t="n">
+      <c r="E287" s="16" t="n">
         <v>13761.7177340496</v>
       </c>
-      <c r="F275" s="16" t="n">
+      <c r="F287" s="16" t="n">
         <v>1459.355008913</v>
       </c>
-      <c r="G275" s="15" t="inlineStr"/>
-      <c r="H275" s="15" t="inlineStr"/>
-      <c r="I275" s="15" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="15" t="inlineStr">
+      <c r="G287" s="15" t="inlineStr"/>
+      <c r="H287" s="15" t="inlineStr"/>
+      <c r="I287" s="15" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B276" s="15" t="inlineStr"/>
-      <c r="C276" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D276" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E276" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" s="15" t="inlineStr"/>
-      <c r="H276" s="15" t="inlineStr"/>
-      <c r="I276" s="15" t="inlineStr"/>
-    </row>
-    <row r="278" ht="17" customHeight="1">
-      <c r="A278" s="4" t="inlineStr">
+      <c r="B288" s="15" t="inlineStr"/>
+      <c r="C288" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" s="15" t="inlineStr"/>
+      <c r="H288" s="15" t="inlineStr"/>
+      <c r="I288" s="15" t="inlineStr"/>
+    </row>
+    <row r="290" ht="17" customHeight="1">
+      <c r="A290" s="4" t="inlineStr">
         <is>
           <t>C REMELT  (target 65.0 Bx)</t>
         </is>
       </c>
-      <c r="B278" s="5" t="n"/>
-      <c r="C278" s="5" t="n"/>
-      <c r="D278" s="5" t="n"/>
-      <c r="E278" s="5" t="n"/>
-      <c r="F278" s="5" t="n"/>
-      <c r="G278" s="5" t="n"/>
-      <c r="H278" s="5" t="n"/>
-      <c r="I278" s="5" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="6" t="inlineStr">
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5" t="n"/>
+      <c r="I290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B279" s="6" t="inlineStr">
+      <c r="B291" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C279" s="6" t="inlineStr">
+      <c r="C291" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D279" s="6" t="inlineStr">
+      <c r="D291" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E291" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F279" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G279" s="6" t="inlineStr">
+      <c r="G291" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H279" s="6" t="inlineStr">
+      <c r="H291" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I279" s="6" t="inlineStr">
+      <c r="I291" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="8" t="inlineStr">
-        <is>
-          <t>C Magma (to Remelt)</t>
-        </is>
-      </c>
-      <c r="B280" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C280" s="9" t="n">
-        <v>3648.387522282503</v>
-      </c>
-      <c r="D280" s="9" t="n">
-        <v>3356.516520499903</v>
-      </c>
-      <c r="E280" s="9" t="n">
-        <v>2752.34354680992</v>
-      </c>
-      <c r="F280" s="9" t="n">
-        <v>291.8710017826002</v>
-      </c>
-      <c r="G280" s="10" t="n">
-        <v>92</v>
-      </c>
-      <c r="H280" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="I280" s="9" t="n">
-        <v>39.14230626275408</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="12" t="inlineStr">
-        <is>
-          <t>Remelt Water</t>
-        </is>
-      </c>
-      <c r="B281" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C281" s="13" t="n">
-        <v>1515.484047717348</v>
-      </c>
-      <c r="D281" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E281" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" s="13" t="n">
-        <v>1515.484047717348</v>
-      </c>
-      <c r="G281" s="12" t="inlineStr"/>
-      <c r="H281" s="12" t="inlineStr"/>
-      <c r="I281" s="12" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="8" t="inlineStr">
-        <is>
-          <t>C Remelt</t>
-        </is>
-      </c>
-      <c r="B282" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C282" s="9" t="n">
-        <v>5163.871569999851</v>
-      </c>
-      <c r="D282" s="9" t="n">
-        <v>3356.516520499903</v>
-      </c>
-      <c r="E282" s="9" t="n">
-        <v>2752.34354680992</v>
-      </c>
-      <c r="F282" s="9" t="n">
-        <v>1807.355049499949</v>
-      </c>
-      <c r="G282" s="10" t="n">
-        <v>64.99999999999999</v>
-      </c>
-      <c r="H282" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="I282" s="9" t="n">
-        <v>62.88892869832576</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="15" t="inlineStr">
-        <is>
-          <t>Total In</t>
-        </is>
-      </c>
-      <c r="B283" s="15" t="inlineStr"/>
-      <c r="C283" s="16" t="n">
-        <v>5163.871569999851</v>
-      </c>
-      <c r="D283" s="16" t="n">
-        <v>3356.516520499903</v>
-      </c>
-      <c r="E283" s="16" t="n">
-        <v>2752.34354680992</v>
-      </c>
-      <c r="F283" s="16" t="n">
-        <v>1807.355049499948</v>
-      </c>
-      <c r="G283" s="15" t="inlineStr"/>
-      <c r="H283" s="15" t="inlineStr"/>
-      <c r="I283" s="15" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="15" t="inlineStr">
-        <is>
-          <t>Total Out</t>
-        </is>
-      </c>
-      <c r="B284" s="15" t="inlineStr"/>
-      <c r="C284" s="16" t="n">
-        <v>5163.871569999851</v>
-      </c>
-      <c r="D284" s="16" t="n">
-        <v>3356.516520499903</v>
-      </c>
-      <c r="E284" s="16" t="n">
-        <v>2752.34354680992</v>
-      </c>
-      <c r="F284" s="16" t="n">
-        <v>1807.355049499949</v>
-      </c>
-      <c r="G284" s="15" t="inlineStr"/>
-      <c r="H284" s="15" t="inlineStr"/>
-      <c r="I284" s="15" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B285" s="15" t="inlineStr"/>
-      <c r="C285" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D285" s="16" t="n">
-        <v>4.547473508864641e-13</v>
-      </c>
-      <c r="E285" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F285" s="16" t="n">
-        <v>-4.547473508864641e-13</v>
-      </c>
-      <c r="G285" s="15" t="inlineStr"/>
-      <c r="H285" s="15" t="inlineStr"/>
-      <c r="I285" s="15" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="17" t="inlineStr">
-        <is>
-          <t>Target remelt brix</t>
-        </is>
-      </c>
-      <c r="B286" s="22" t="n">
-        <v>65</v>
-      </c>
-      <c r="C286" s="19" t="inlineStr">
-        <is>
-          <t>Bx</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="17" customHeight="1">
-      <c r="A288" s="4" t="inlineStr">
-        <is>
-          <t>PAN VAPOR CONDENSERS  (one per pan)</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="n"/>
-      <c r="C288" s="5" t="n"/>
-      <c r="D288" s="5" t="n"/>
-      <c r="E288" s="5" t="n"/>
-      <c r="F288" s="5" t="n"/>
-      <c r="G288" s="5" t="n"/>
-      <c r="H288" s="5" t="n"/>
-      <c r="I288" s="5" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="6" t="inlineStr">
-        <is>
-          <t>Condenser</t>
-        </is>
-      </c>
-      <c r="B289" s="6" t="inlineStr">
-        <is>
-          <t>Vapor (lb/hr)</t>
-        </is>
-      </c>
-      <c r="C289" s="6" t="inlineStr">
-        <is>
-          <t>Sat T (°F)</t>
-        </is>
-      </c>
-      <c r="D289" s="6" t="inlineStr">
-        <is>
-          <t>h_fg (BTU/lb)</t>
-        </is>
-      </c>
-      <c r="E289" s="6" t="inlineStr">
-        <is>
-          <t>Heat (MM BTU/hr)</t>
-        </is>
-      </c>
-      <c r="F289" s="6" t="inlineStr">
-        <is>
-          <t>Inj Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G289" s="6" t="inlineStr">
-        <is>
-          <t>Inj Water (GPM)</t>
-        </is>
-      </c>
-      <c r="H289" s="6" t="inlineStr">
-        <is>
-          <t>Water Out (°F)</t>
-        </is>
-      </c>
-      <c r="I289" s="6" t="inlineStr">
-        <is>
-          <t>Total Out (lb/hr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="8" t="inlineStr">
-        <is>
-          <t>A Pans</t>
-        </is>
-      </c>
-      <c r="B290" s="9" t="n">
-        <v>60869.76880576191</v>
-      </c>
-      <c r="C290" s="10" t="n">
-        <v>143.355890609762</v>
-      </c>
-      <c r="D290" s="10" t="n">
-        <v>1011.249247318053</v>
-      </c>
-      <c r="E290" s="23" t="n">
-        <v>61.85885673327943</v>
-      </c>
-      <c r="F290" s="9" t="n">
-        <v>1279241.390309365</v>
-      </c>
-      <c r="G290" s="9" t="n">
-        <v>2556.437630514318</v>
-      </c>
-      <c r="H290" s="10" t="n">
-        <v>138.355890609762</v>
-      </c>
-      <c r="I290" s="9" t="n">
-        <v>1340111.159115126</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="12" t="inlineStr">
-        <is>
-          <t>B Pans</t>
-        </is>
-      </c>
-      <c r="B291" s="13" t="n">
-        <v>24647.61519176989</v>
-      </c>
-      <c r="C291" s="14" t="n">
-        <v>133.0828737186033</v>
-      </c>
-      <c r="D291" s="14" t="n">
-        <v>1017.228576695272</v>
-      </c>
-      <c r="E291" s="24" t="n">
-        <v>25.19549659641569</v>
-      </c>
-      <c r="F291" s="13" t="n">
-        <v>661596.5166543564</v>
-      </c>
-      <c r="G291" s="13" t="n">
-        <v>1322.135325048674</v>
-      </c>
-      <c r="H291" s="14" t="n">
-        <v>128.0828737186033</v>
-      </c>
-      <c r="I291" s="13" t="n">
-        <v>686244.1318461263</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="8" t="inlineStr">
         <is>
-          <t>Grain Pans</t>
-        </is>
-      </c>
-      <c r="B292" s="9" t="n">
-        <v>2418.240656970975</v>
-      </c>
-      <c r="C292" s="10" t="n">
-        <v>129.059477265374</v>
-      </c>
-      <c r="D292" s="10" t="n">
-        <v>1019.563890979194</v>
-      </c>
-      <c r="E292" s="23" t="n">
-        <v>2.477642056830265</v>
+          <t>C Magma (to Remelt)</t>
+        </is>
+      </c>
+      <c r="B292" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C292" s="9" t="n">
+        <v>3648.387522282503</v>
+      </c>
+      <c r="D292" s="9" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E292" s="9" t="n">
+        <v>2752.34354680992</v>
       </c>
       <c r="F292" s="9" t="n">
-        <v>72744.5708436963</v>
-      </c>
-      <c r="G292" s="9" t="n">
-        <v>145.3728434126625</v>
+        <v>291.8710017826002</v>
+      </c>
+      <c r="G292" s="10" t="n">
+        <v>92</v>
       </c>
       <c r="H292" s="10" t="n">
-        <v>124.059477265374</v>
+        <v>82</v>
       </c>
       <c r="I292" s="9" t="n">
-        <v>75162.81150066727</v>
+        <v>39.14230626275408</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="12" t="inlineStr">
         <is>
+          <t>Remelt Water</t>
+        </is>
+      </c>
+      <c r="B293" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C293" s="13" t="n">
+        <v>1515.484047717348</v>
+      </c>
+      <c r="D293" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" s="13" t="n">
+        <v>1515.484047717348</v>
+      </c>
+      <c r="G293" s="12" t="inlineStr"/>
+      <c r="H293" s="12" t="inlineStr"/>
+      <c r="I293" s="12" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="8" t="inlineStr">
+        <is>
+          <t>C Remelt</t>
+        </is>
+      </c>
+      <c r="B294" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C294" s="9" t="n">
+        <v>5163.871569999851</v>
+      </c>
+      <c r="D294" s="9" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E294" s="9" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F294" s="9" t="n">
+        <v>1807.355049499949</v>
+      </c>
+      <c r="G294" s="10" t="n">
+        <v>64.99999999999999</v>
+      </c>
+      <c r="H294" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="I294" s="9" t="n">
+        <v>62.88892869832576</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B295" s="15" t="inlineStr"/>
+      <c r="C295" s="16" t="n">
+        <v>5163.871569999851</v>
+      </c>
+      <c r="D295" s="16" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E295" s="16" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F295" s="16" t="n">
+        <v>1807.355049499948</v>
+      </c>
+      <c r="G295" s="15" t="inlineStr"/>
+      <c r="H295" s="15" t="inlineStr"/>
+      <c r="I295" s="15" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B296" s="15" t="inlineStr"/>
+      <c r="C296" s="16" t="n">
+        <v>5163.871569999851</v>
+      </c>
+      <c r="D296" s="16" t="n">
+        <v>3356.516520499903</v>
+      </c>
+      <c r="E296" s="16" t="n">
+        <v>2752.34354680992</v>
+      </c>
+      <c r="F296" s="16" t="n">
+        <v>1807.355049499949</v>
+      </c>
+      <c r="G296" s="15" t="inlineStr"/>
+      <c r="H296" s="15" t="inlineStr"/>
+      <c r="I296" s="15" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B297" s="15" t="inlineStr"/>
+      <c r="C297" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" s="16" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="E297" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" s="16" t="n">
+        <v>-4.547473508864641e-13</v>
+      </c>
+      <c r="G297" s="15" t="inlineStr"/>
+      <c r="H297" s="15" t="inlineStr"/>
+      <c r="I297" s="15" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="17" t="inlineStr">
+        <is>
+          <t>Target remelt brix</t>
+        </is>
+      </c>
+      <c r="B298" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="C298" s="19" t="inlineStr">
+        <is>
+          <t>Bx</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="17" customHeight="1">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>PAN VAPOR CONDENSERS  (one per pan)</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="5" t="n"/>
+      <c r="I300" s="5" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>Condenser</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>Vapor (lb/hr)</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
+        <is>
+          <t>Sat T (°F)</t>
+        </is>
+      </c>
+      <c r="D301" s="6" t="inlineStr">
+        <is>
+          <t>h_fg (BTU/lb)</t>
+        </is>
+      </c>
+      <c r="E301" s="6" t="inlineStr">
+        <is>
+          <t>Heat (MM BTU/hr)</t>
+        </is>
+      </c>
+      <c r="F301" s="6" t="inlineStr">
+        <is>
+          <t>Inj Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G301" s="6" t="inlineStr">
+        <is>
+          <t>Inj Water (GPM)</t>
+        </is>
+      </c>
+      <c r="H301" s="6" t="inlineStr">
+        <is>
+          <t>Water Out (°F)</t>
+        </is>
+      </c>
+      <c r="I301" s="6" t="inlineStr">
+        <is>
+          <t>Total Out (lb/hr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>A Pans</t>
+        </is>
+      </c>
+      <c r="B302" s="9" t="n">
+        <v>60869.76880576191</v>
+      </c>
+      <c r="C302" s="10" t="n">
+        <v>143.355890609762</v>
+      </c>
+      <c r="D302" s="10" t="n">
+        <v>1011.249247318053</v>
+      </c>
+      <c r="E302" s="23" t="n">
+        <v>61.85885673327943</v>
+      </c>
+      <c r="F302" s="9" t="n">
+        <v>1279241.390309365</v>
+      </c>
+      <c r="G302" s="9" t="n">
+        <v>2556.437630514318</v>
+      </c>
+      <c r="H302" s="10" t="n">
+        <v>138.355890609762</v>
+      </c>
+      <c r="I302" s="9" t="n">
+        <v>1340111.159115126</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="12" t="inlineStr">
+        <is>
+          <t>B Pans</t>
+        </is>
+      </c>
+      <c r="B303" s="13" t="n">
+        <v>24647.61519176989</v>
+      </c>
+      <c r="C303" s="14" t="n">
+        <v>133.0828737186033</v>
+      </c>
+      <c r="D303" s="14" t="n">
+        <v>1017.228576695272</v>
+      </c>
+      <c r="E303" s="24" t="n">
+        <v>25.19549659641569</v>
+      </c>
+      <c r="F303" s="13" t="n">
+        <v>661596.5166543564</v>
+      </c>
+      <c r="G303" s="13" t="n">
+        <v>1322.135325048674</v>
+      </c>
+      <c r="H303" s="14" t="n">
+        <v>128.0828737186033</v>
+      </c>
+      <c r="I303" s="13" t="n">
+        <v>686244.1318461263</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="8" t="inlineStr">
+        <is>
+          <t>Grain Pans</t>
+        </is>
+      </c>
+      <c r="B304" s="9" t="n">
+        <v>2418.240656970975</v>
+      </c>
+      <c r="C304" s="10" t="n">
+        <v>129.059477265374</v>
+      </c>
+      <c r="D304" s="10" t="n">
+        <v>1019.563890979194</v>
+      </c>
+      <c r="E304" s="23" t="n">
+        <v>2.477642056830265</v>
+      </c>
+      <c r="F304" s="9" t="n">
+        <v>72744.5708436963</v>
+      </c>
+      <c r="G304" s="9" t="n">
+        <v>145.3728434126625</v>
+      </c>
+      <c r="H304" s="10" t="n">
+        <v>124.059477265374</v>
+      </c>
+      <c r="I304" s="9" t="n">
+        <v>75162.81150066727</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="12" t="inlineStr">
+        <is>
           <t>C Pans</t>
         </is>
       </c>
-      <c r="B293" s="13" t="n">
+      <c r="B305" s="13" t="n">
         <v>15396.38230740088</v>
       </c>
-      <c r="C293" s="14" t="n">
+      <c r="C305" s="14" t="n">
         <v>119.6832047961655</v>
       </c>
-      <c r="D293" s="14" t="n">
+      <c r="D305" s="14" t="n">
         <v>1024.996584701115</v>
       </c>
-      <c r="E293" s="24" t="n">
+      <c r="E305" s="24" t="n">
         <v>15.85822119337558</v>
       </c>
-      <c r="F293" s="13" t="n">
+      <c r="F305" s="13" t="n">
         <v>642470.1056582071</v>
       </c>
-      <c r="G293" s="13" t="n">
+      <c r="G305" s="13" t="n">
         <v>1283.913080851733</v>
       </c>
-      <c r="H293" s="14" t="n">
+      <c r="H305" s="14" t="n">
         <v>114.6832047961655</v>
       </c>
-      <c r="I293" s="13" t="n">
+      <c r="I305" s="13" t="n">
         <v>657866.487965608</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="15" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B294" s="16" t="n">
+      <c r="B306" s="16" t="n">
         <v>103332.0069619037</v>
       </c>
-      <c r="C294" s="15" t="inlineStr"/>
-      <c r="D294" s="15" t="inlineStr"/>
-      <c r="E294" s="25" t="n">
+      <c r="C306" s="15" t="inlineStr"/>
+      <c r="D306" s="15" t="inlineStr"/>
+      <c r="E306" s="25" t="n">
         <v>105.390216579901</v>
       </c>
-      <c r="F294" s="16" t="n">
+      <c r="F306" s="16" t="n">
         <v>2656052.583465625</v>
       </c>
-      <c r="G294" s="16" t="n">
+      <c r="G306" s="16" t="n">
         <v>5307.858879827387</v>
       </c>
-      <c r="H294" s="15" t="inlineStr"/>
-      <c r="I294" s="16" t="n">
+      <c r="H306" s="15" t="inlineStr"/>
+      <c r="I306" s="16" t="n">
         <v>2759384.590427528</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="17" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="17" t="inlineStr">
         <is>
           <t>Injection water supply temp</t>
         </is>
       </c>
-      <c r="B295" s="22" t="n">
+      <c r="B307" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="C295" s="19" t="inlineStr">
+      <c r="C307" s="19" t="inlineStr">
         <is>
           <t>°F</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="26" t="inlineStr">
+    <row r="308">
+      <c r="A308" s="26" t="inlineStr">
         <is>
           <t>Note: if using CoolingTowerSystem, ignore these injection water demands - they are re-solved there at the delivered water temp.</t>
         </is>
       </c>
-      <c r="B296" s="17" t="inlineStr"/>
-    </row>
-    <row r="298" ht="17" customHeight="1">
-      <c r="A298" s="4" t="inlineStr">
+      <c r="B308" s="17" t="inlineStr"/>
+    </row>
+    <row r="310" ht="17" customHeight="1">
+      <c r="A310" s="4" t="inlineStr">
         <is>
           <t>CONDENSATE RETURN</t>
         </is>
       </c>
-      <c r="B298" s="5" t="n"/>
-      <c r="C298" s="5" t="n"/>
-      <c r="D298" s="5" t="n"/>
-      <c r="E298" s="5" t="n"/>
-      <c r="F298" s="5" t="n"/>
-      <c r="G298" s="5" t="n"/>
-      <c r="H298" s="5" t="n"/>
-      <c r="I298" s="5" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="17" t="inlineStr">
+      <c r="B310" s="5" t="n"/>
+      <c r="C310" s="5" t="n"/>
+      <c r="D310" s="5" t="n"/>
+      <c r="E310" s="5" t="n"/>
+      <c r="F310" s="5" t="n"/>
+      <c r="G310" s="5" t="n"/>
+      <c r="H310" s="5" t="n"/>
+      <c r="I310" s="5" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="17" t="inlineStr">
         <is>
           <t>Clean condensate (Exhaust steam pans)</t>
         </is>
       </c>
-      <c r="B299" s="21" t="n">
+      <c r="B311" s="21" t="n">
         <v>117180.8790713368</v>
       </c>
-      <c r="C299" s="19" t="inlineStr">
+      <c r="C311" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" s="17" t="inlineStr">
+    <row r="312">
+      <c r="A312" s="17" t="inlineStr">
         <is>
           <t>Dirty condensate (V1-V4 steam pans)</t>
         </is>
       </c>
-      <c r="B300" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C300" s="19" t="inlineStr">
+      <c r="B312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C312" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" s="17" t="inlineStr">
+    <row r="313">
+      <c r="A313" s="17" t="inlineStr">
         <is>
           <t>Total condensate</t>
         </is>
       </c>
-      <c r="B301" s="21" t="n">
+      <c r="B313" s="21" t="n">
         <v>117180.8790713368</v>
       </c>
-      <c r="C301" s="19" t="inlineStr">
+      <c r="C313" s="19" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
@@ -6454,32 +6634,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A196:I196"/>
+    <mergeCell ref="A183:I183"/>
     <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A177:I177"/>
-    <mergeCell ref="A158:I158"/>
-    <mergeCell ref="A136:I136"/>
-    <mergeCell ref="A145:I145"/>
+    <mergeCell ref="A174:I174"/>
+    <mergeCell ref="A164:I164"/>
+    <mergeCell ref="A192:I192"/>
+    <mergeCell ref="A139:I139"/>
+    <mergeCell ref="A272:I272"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A298:I298"/>
+    <mergeCell ref="A129:I129"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A269:I269"/>
-    <mergeCell ref="A278:I278"/>
-    <mergeCell ref="A219:I219"/>
-    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A290:I290"/>
+    <mergeCell ref="A253:I253"/>
+    <mergeCell ref="A244:I244"/>
+    <mergeCell ref="A262:I262"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A288:I288"/>
+    <mergeCell ref="A202:I202"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A232:I232"/>
-    <mergeCell ref="A186:I186"/>
-    <mergeCell ref="A260:I260"/>
-    <mergeCell ref="A250:I250"/>
+    <mergeCell ref="A211:I211"/>
+    <mergeCell ref="A310:I310"/>
+    <mergeCell ref="A148:I148"/>
+    <mergeCell ref="A300:I300"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A241:I241"/>
-    <mergeCell ref="A168:I168"/>
-    <mergeCell ref="A205:I205"/>
+    <mergeCell ref="A281:I281"/>
+    <mergeCell ref="A228:I228"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -6487,7 +6667,7 @@
     <brk id="42" min="0" max="16383" man="1"/>
     <brk id="70" min="0" max="16383" man="1"/>
     <brk id="110" min="0" max="16383" man="1"/>
-    <brk id="203" min="0" max="16383" man="1"/>
+    <brk id="209" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
